--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.2%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.6%</t>
+          <t>-518.7%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>105.8%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-142.1%</t>
+          <t>-139.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-200.8%</t>
+          <t>-189.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-57.8%</t>
         </is>
       </c>
     </row>
@@ -46378,10 +46378,10 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.035137844223268</v>
+        <v>-4.00456586806756</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.024008435245066</v>
+        <v>1.036237225707349</v>
       </c>
       <c r="F1949" t="n">
         <v>0.05675407570190971</v>
@@ -46401,10 +46401,10 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.062918242124621</v>
+        <v>-4.032346265968913</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.024393477853064</v>
+        <v>1.036622268315347</v>
       </c>
       <c r="F1950" t="n">
         <v>0.02897367780055665</v>
@@ -46424,10 +46424,10 @@
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.1459195231499</v>
+        <v>-4.115347546994192</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8295486854436056</v>
+        <v>0.8417774759058887</v>
       </c>
       <c r="F1951" t="n">
         <v>0.01040279327338289</v>
@@ -46447,10 +46447,10 @@
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.254533601593231</v>
+        <v>-4.223961625437523</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9062527147854789</v>
+        <v>0.9184815052477617</v>
       </c>
       <c r="F1952" t="n">
         <v>0.01040279327338289</v>
@@ -46470,10 +46470,10 @@
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.219124563345088</v>
+        <v>-4.18855258718938</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9349293561870589</v>
+        <v>0.9471581466493419</v>
       </c>
       <c r="F1953" t="n">
         <v>0.01040279327338289</v>
@@ -46493,10 +46493,10 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.180740900786937</v>
+        <v>-4.150168924631229</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9477022625526881</v>
+        <v>0.9599310530149712</v>
       </c>
       <c r="F1954" t="n">
         <v>0.04878645583153407</v>
@@ -46516,10 +46516,10 @@
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.003624570751771</v>
+        <v>-3.973052594596063</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.015277823412057</v>
+        <v>1.02750661387434</v>
       </c>
       <c r="F1955" t="n">
         <v>0.04878645583153407</v>
@@ -46539,10 +46539,10 @@
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.048716815585316</v>
+        <v>-4.018144839429609</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9979243172405516</v>
+        <v>1.010153107702835</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.01310958733785572</v>
@@ -46562,10 +46562,10 @@
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.869341394346549</v>
+        <v>-3.838769418190841</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.063461461042473</v>
+        <v>1.075690251504756</v>
       </c>
       <c r="F1957" t="n">
         <v>0.143667170832863</v>
@@ -46585,10 +46585,10 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.914355607867155</v>
+        <v>-3.883783631711447</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.02626323096582</v>
+        <v>1.038492021428103</v>
       </c>
       <c r="F1958" t="n">
         <v>0.1133182755182583</v>
@@ -46608,10 +46608,10 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.18136011813959</v>
+        <v>-4.150788141983883</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9251529891957919</v>
+        <v>0.937381779658075</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.08104476252469023</v>
@@ -46631,10 +46631,10 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.282557899576763</v>
+        <v>-4.251985923421056</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8838777985174242</v>
+        <v>0.8961065889797073</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.1494535760700094</v>
@@ -46654,10 +46654,10 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.27604693296245</v>
+        <v>-4.245474956806743</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.884082146717466</v>
+        <v>0.8963109371797491</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.1494535760700094</v>
@@ -46677,10 +46677,10 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.257008805255153</v>
+        <v>-4.226436829099446</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.88822211700863</v>
+        <v>0.9004509074709128</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.207637187401204</v>
@@ -46700,10 +46700,10 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.288135436405772</v>
+        <v>-4.257563460250064</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.053353333487063</v>
+        <v>1.065582123949346</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.207637187401204</v>
@@ -46723,10 +46723,10 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.302002197739689</v>
+        <v>-4.271430221583982</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.048639957939629</v>
+        <v>1.060868748401913</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2454951041350269</v>
@@ -46746,10 +46746,10 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.25719802619976</v>
+        <v>-4.226626050044052</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.072570156952527</v>
+        <v>1.08479894741481</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2454951041350269</v>
@@ -46769,10 +46769,10 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.109455055964757</v>
+        <v>-4.078883079809049</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.21081999283855</v>
+        <v>1.223048783300833</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.07768774690014374</v>
@@ -46792,10 +46792,10 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.211469738495978</v>
+        <v>-4.180897762340271</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.172807741357543</v>
+        <v>1.185036531819826</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.07768774690014374</v>
@@ -46815,10 +46815,10 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.205317032443194</v>
+        <v>-4.174745056287486</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.175931172170315</v>
+        <v>1.188159962632598</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.07153504084735945</v>
@@ -46838,10 +46838,10 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.222126330593696</v>
+        <v>-4.191554354437988</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.168287929650224</v>
+        <v>1.180516720112507</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.08834433899786109</v>
@@ -46861,10 +46861,10 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.159828331817573</v>
+        <v>-4.129256355661866</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.259542682957494</v>
+        <v>1.271771473419777</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.08834433899786109</v>
@@ -46884,10 +46884,10 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.958038134152416</v>
+        <v>-3.927466157996708</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.048839634412955</v>
+        <v>1.061068424875238</v>
       </c>
       <c r="F1971" t="n">
         <v>0.1096738531712933</v>
@@ -46907,10 +46907,10 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.884660037063679</v>
+        <v>-3.854088060907972</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.148481105570625</v>
+        <v>1.160709896032908</v>
       </c>
       <c r="F1972" t="n">
         <v>0.1830519502600298</v>
@@ -46930,10 +46930,10 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.982400581688653</v>
+        <v>-3.951828605532946</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.124012623836679</v>
+        <v>1.136241414298962</v>
       </c>
       <c r="F1973" t="n">
         <v>0.1671626721270497</v>
@@ -46953,10 +46953,10 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.158738341811583</v>
+        <v>-4.128166365655876</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.052013500612179</v>
+        <v>1.064242291074462</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.009175087995879738</v>
@@ -46976,10 +46976,10 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.082316295379656</v>
+        <v>-4.051744319223949</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.081073937224878</v>
+        <v>1.093302727687161</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.009175087995879738</v>
@@ -46999,10 +46999,10 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.037943163741088</v>
+        <v>-4.00737118758538</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.098686057315742</v>
+        <v>1.110914847778025</v>
       </c>
       <c r="F1976" t="n">
         <v>0.03519804364268886</v>
@@ -47022,10 +47022,10 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.91510894285392</v>
+        <v>-3.884536966698213</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.142213539809199</v>
+        <v>1.154442330271482</v>
       </c>
       <c r="F1977" t="n">
         <v>0.03519804364268886</v>
@@ -47045,10 +47045,10 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.867453212292864</v>
+        <v>-3.836881236137157</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.167657589061426</v>
+        <v>1.179886379523709</v>
       </c>
       <c r="F1978" t="n">
         <v>0.08285377420374451</v>
@@ -47068,10 +47068,10 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.76693505379411</v>
+        <v>-3.736363077638402</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.212757225835652</v>
+        <v>1.224986016297936</v>
       </c>
       <c r="F1979" t="n">
         <v>0.1833719327024991</v>
@@ -47091,10 +47091,10 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.827601644196499</v>
+        <v>-3.797029668040791</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.175245262150569</v>
+        <v>1.187474052612852</v>
       </c>
       <c r="F1980" t="n">
         <v>0.1016736159839654</v>
@@ -47114,10 +47114,10 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.782763242588101</v>
+        <v>-3.752191266432393</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.197278325404557</v>
+        <v>1.20950711586684</v>
       </c>
       <c r="F1981" t="n">
         <v>0.1062170489288349</v>
@@ -47137,10 +47137,10 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.883521878345099</v>
+        <v>-3.852949902189392</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.161135810732836</v>
+        <v>1.173364601195118</v>
       </c>
       <c r="F1982" t="n">
         <v>0.01739148020182946</v>
@@ -47160,10 +47160,10 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.839319041259199</v>
+        <v>-3.808747065103491</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.184696548095033</v>
+        <v>1.196925338557316</v>
       </c>
       <c r="F1983" t="n">
         <v>0.0615943172877299</v>
@@ -47183,10 +47183,10 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.876298068922642</v>
+        <v>-3.845726092766935</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.168314937498903</v>
+        <v>1.180543727961186</v>
       </c>
       <c r="F1984" t="n">
         <v>0.09856821907906044</v>
@@ -47206,10 +47206,10 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.896356147787482</v>
+        <v>-3.865784171631775</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.211539471136007</v>
+        <v>1.22376826159829</v>
       </c>
       <c r="F1985" t="n">
         <v>0.09856821907906044</v>
@@ -47229,10 +47229,10 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.856425474609592</v>
+        <v>-3.825853498453884</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.225952445001416</v>
+        <v>1.238181235463699</v>
       </c>
       <c r="F1986" t="n">
         <v>0.1384988922569508</v>
@@ -47252,10 +47252,10 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.805393381887064</v>
+        <v>-3.774821405731356</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.241313510328697</v>
+        <v>1.25354230079098</v>
       </c>
       <c r="F1987" t="n">
         <v>0.1895309849794787</v>
@@ -47275,10 +47275,10 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.740169200759858</v>
+        <v>-3.709597224604151</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.284590586872284</v>
+        <v>1.296819377334567</v>
       </c>
       <c r="F1988" t="n">
         <v>0.2547551661066844</v>
@@ -47298,10 +47298,10 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.702742180688725</v>
+        <v>-3.672170204533017</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.295522367200018</v>
+        <v>1.307751157662301</v>
       </c>
       <c r="F1989" t="n">
         <v>0.260006704135866</v>
@@ -47321,10 +47321,10 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.722853836723433</v>
+        <v>-3.692281860567725</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.288734497117375</v>
+        <v>1.300963287579658</v>
       </c>
       <c r="F1990" t="n">
         <v>0.2710340491332852</v>
@@ -47344,10 +47344,10 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.669109022296228</v>
+        <v>-3.638537046140521</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.470790193909468</v>
+        <v>1.483018984371751</v>
       </c>
       <c r="F1991" t="n">
         <v>0.2810973585737472</v>
@@ -47367,10 +47367,10 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.645317453690086</v>
+        <v>-3.614745477534378</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.600419730569742</v>
+        <v>1.612648521032025</v>
       </c>
       <c r="F1992" t="n">
         <v>0.3048889271798895</v>
@@ -47390,10 +47390,10 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.619233369426278</v>
+        <v>-3.58866139327057</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.602561340289124</v>
+        <v>1.614790130751407</v>
       </c>
       <c r="F1993" t="n">
         <v>0.3048889271798895</v>
@@ -47413,10 +47413,10 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.541102188577331</v>
+        <v>-3.510530212421624</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.632007008212482</v>
+        <v>1.644235798674765</v>
       </c>
       <c r="F1994" t="n">
         <v>0.379065738063574</v>
@@ -47436,10 +47436,10 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.532209727184048</v>
+        <v>-3.501637751028341</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.653118398496587</v>
+        <v>1.66534718895887</v>
       </c>
       <c r="F1995" t="n">
         <v>0.379065738063574</v>
@@ -47459,10 +47459,10 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.700685844153926</v>
+        <v>-3.670113867998218</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.57758299911322</v>
+        <v>1.589811789575503</v>
       </c>
       <c r="F1996" t="n">
         <v>0.3511179023469932</v>
@@ -47482,10 +47482,10 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.002886315292343</v>
+        <v>-2.972314339136635</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.837972507845715</v>
+        <v>1.850201298307998</v>
       </c>
       <c r="F1997" t="n">
         <v>0.2807698429765825</v>
@@ -47505,10 +47505,10 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.98016521160919</v>
+        <v>-2.949593235453483</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.837724971815881</v>
+        <v>1.849953762278163</v>
       </c>
       <c r="F1998" t="n">
         <v>0.2807698429765825</v>
@@ -47528,10 +47528,10 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.978440168319146</v>
+        <v>-2.947868192163439</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.997321114983067</v>
+        <v>2.00954990544535</v>
       </c>
       <c r="F1999" t="n">
         <v>0.2824948862666263</v>
@@ -47551,10 +47551,10 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.133221175097401</v>
+        <v>-3.102649198941694</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.972486534765411</v>
+        <v>1.984715325227695</v>
       </c>
       <c r="F2000" t="n">
         <v>0.2491272122121502</v>
@@ -47574,10 +47574,10 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.081785841712742</v>
+        <v>-3.051213865557034</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.98973602410882</v>
+        <v>2.001964814571104</v>
       </c>
       <c r="F2001" t="n">
         <v>0.3005625455968098</v>
@@ -47597,10 +47597,10 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.054834617386254</v>
+        <v>-3.024262641230546</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.010522667484157</v>
+        <v>2.02275145794644</v>
       </c>
       <c r="F2002" t="n">
         <v>0.315442891624529</v>
@@ -47620,10 +47620,10 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.19078762544257</v>
+        <v>-3.160215649286862</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.140244596406591</v>
+        <v>2.152473386868873</v>
       </c>
       <c r="F2003" t="n">
         <v>0.315442891624529</v>
@@ -47643,10 +47643,10 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.213195743247442</v>
+        <v>-3.182623767091735</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.123398044187635</v>
+        <v>2.135626834649918</v>
       </c>
       <c r="F2004" t="n">
         <v>0.315442891624529</v>
@@ -47666,10 +47666,10 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.361201510726842</v>
+        <v>-3.330629534571134</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.066249736745513</v>
+        <v>2.078478527207795</v>
       </c>
       <c r="F2005" t="n">
         <v>0.2287158827609875</v>
@@ -47689,10 +47689,10 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.370642436615372</v>
+        <v>-3.340070460459664</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.118727084111947</v>
+        <v>2.130955874574231</v>
       </c>
       <c r="F2006" t="n">
         <v>0.3511430003043789</v>
@@ -47712,10 +47712,10 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.369355673075815</v>
+        <v>-3.338783696920108</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.122132884073071</v>
+        <v>2.134361674535354</v>
       </c>
       <c r="F2007" t="n">
         <v>0.3524297638439355</v>
@@ -47735,10 +47735,10 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.370912727065106</v>
+        <v>-3.340340750909399</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.11962187537113</v>
+        <v>2.131850665833412</v>
       </c>
       <c r="F2008" t="n">
         <v>0.3524297638439355</v>
@@ -47758,10 +47758,10 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.378184612588571</v>
+        <v>-3.347612636432864</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.111533350764606</v>
+        <v>2.123762141226889</v>
       </c>
       <c r="F2009" t="n">
         <v>0.3451578783204708</v>
@@ -47781,10 +47781,10 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.37634359353032</v>
+        <v>-3.345771617374612</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.110703768598059</v>
+        <v>2.122932559060342</v>
       </c>
       <c r="F2010" t="n">
         <v>0.3464261049919392</v>
@@ -47804,10 +47804,10 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.38325229903</v>
+        <v>-3.352680322874293</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.121013693264105</v>
+        <v>2.133242483726388</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3464261049919392</v>
@@ -47827,10 +47827,10 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.38481394184486</v>
+        <v>-3.354241965689153</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.120389036138161</v>
+        <v>2.132617826600445</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3464261049919392</v>
@@ -47850,10 +47850,10 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.412714728954333</v>
+        <v>-3.382142752798626</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.107752762421375</v>
+        <v>2.119981552883657</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3118291808490044</v>
@@ -47873,10 +47873,10 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.415747726467007</v>
+        <v>-3.3851757503113</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.103304007393503</v>
+        <v>2.115532797855787</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3087961833363305</v>
@@ -47896,10 +47896,10 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.435809047743514</v>
+        <v>-3.405237071587806</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.161985438473405</v>
+        <v>2.174214228935687</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2887348620598235</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.762133300129983</v>
+        <v>3.393898527912991</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.570566595684864</v>
+        <v>-3.571075065929091</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.248394138298711</v>
+        <v>2.248190750201021</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2317688464838368</v>
+        <v>0.3416622516236978</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.816038508776707</v>
+        <v>3.881974551860623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-68.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.7%</t>
+          <t>-515.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.4%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>104.8%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.8%</t>
+          <t>-200.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-64.2%</t>
         </is>
       </c>
     </row>
@@ -47919,16 +47919,16 @@
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.571075065929091</v>
+        <v>-3.538342569767444</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.248190750201021</v>
+        <v>2.261283748665679</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3416622516236978</v>
+        <v>0.2351067767257327</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.881974551860623</v>
+        <v>3.818041266921844</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>120.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-659.5%</t>
+          <t>-624.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-64.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>464.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-515.4%</t>
+          <t>-483.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-250.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-137.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-278.6%</t>
+          <t>-243.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-200.5%</t>
+          <t>-154.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-167.6%</t>
+          <t>-146.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.2%</t>
+          <t>-36.5%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-0.7763135644067872</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.806198599874567</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>1.339501676855488</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.920781456064323</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.066445231012219</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.690012149831317</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>1.363583471595668</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.935096749507353</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.274449289365296</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.611702671044011</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>1.363583471595668</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.939988894061278</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.837301804426076</v>
+        <v>-1.485861710253271</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.381643121357687</v>
+        <v>2.522219159026809</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8007309565348886</v>
+        <v>1.152171050707693</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.597358841362798</v>
+        <v>3.80822289786648</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.203370531570728</v>
+        <v>-1.851930437397923</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.228299929806275</v>
+        <v>2.368875967475397</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4346622293902359</v>
+        <v>0.7861023235630406</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.370801904382455</v>
+        <v>3.581665960886138</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.411861313022413</v>
+        <v>-2.060421218849608</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.165241906964369</v>
+        <v>2.305817944633492</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2261714479385515</v>
+        <v>0.5776115421113561</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.266045725250213</v>
+        <v>3.476909781753896</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.659062497787635</v>
+        <v>-2.307622403614829</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.074460183466849</v>
+        <v>2.215036221135971</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2463248014373639</v>
+        <v>0.5977648956101685</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.286236487758069</v>
+        <v>3.497100544261752</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.151447525811732</v>
+        <v>-2.800007431638926</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.878612564300943</v>
+        <v>2.019188601970065</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2460602265867328</v>
+        <v>0.1053798675860718</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.991911862987343</v>
+        <v>3.202775919491026</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.536627916741804</v>
+        <v>-3.185187822568999</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.723082946741777</v>
+        <v>1.863658984410899</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2460602265867328</v>
+        <v>0.1053798675860718</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.990454401800207</v>
+        <v>3.201318458303889</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.786498596756386</v>
+        <v>-3.43505850258358</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.624903798190561</v>
+        <v>1.765479835859683</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2097975067562696</v>
+        <v>0.1416425874165351</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.013981157153101</v>
+        <v>3.224845213656784</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.993010373643407</v>
+        <v>-3.641570279470602</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.53840514609201</v>
+        <v>1.678981183761132</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4163092836432911</v>
+        <v>-0.06486918947048642</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.886180149677146</v>
+        <v>3.097044206180828</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.312354448723909</v>
+        <v>-3.960914354551103</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.412440442760069</v>
+        <v>1.553016480429191</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4163092836432911</v>
+        <v>-0.06486918947048642</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.887953076377405</v>
+        <v>3.098817132881088</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.744160241873696</v>
+        <v>-4.39272014770089</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.226051012967558</v>
+        <v>1.36662705063668</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5527267800845581</v>
+        <v>-0.2012866859117534</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.792435465980049</v>
+        <v>3.003299522483732</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.978854236006248</v>
+        <v>-4.627414141833443</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.120458190316628</v>
+        <v>1.26103422798575</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5463905128553029</v>
+        <v>-0.1949504186824982</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.784522001319693</v>
+        <v>2.995386057823376</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.314516883236701</v>
+        <v>-4.963076789063895</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9847737230804121</v>
+        <v>1.125349760749534</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6143214983442078</v>
+        <v>-0.262881404171403</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.742344001682315</v>
+        <v>2.953208058185998</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.678143128137014</v>
+        <v>-5.326703033964209</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8458107853545282</v>
+        <v>0.9863868230236501</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7125431352113336</v>
+        <v>-0.3611030410385289</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.689898579796282</v>
+        <v>2.900762636299964</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.043270510775761</v>
+        <v>-5.691830416602955</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6990143473048609</v>
+        <v>0.8395903849739828</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.008853919510346</v>
+        <v>-0.6574138253375414</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.511366624222705</v>
+        <v>2.722230680726388</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.45185928795644</v>
+        <v>-6.100419193783634</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5343403804473486</v>
+        <v>0.6749164181164704</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.264974901929057</v>
+        <v>2.47583895843274</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.728435388272272</v>
+        <v>-6.376995294099467</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.418895372792476</v>
+        <v>0.5594714104615979</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.260160334400518</v>
+        <v>2.4710243909042</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.14482726255927</v>
+        <v>-6.793387168386464</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2503326736865543</v>
+        <v>0.3909087113556762</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.258154385009395</v>
+        <v>2.469018441513078</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.389098663286339</v>
+        <v>-7.037658569113534</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1628828040644055</v>
+        <v>0.3034588417335273</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.268413075678074</v>
+        <v>2.479277132181757</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.5943496825231</v>
+        <v>-7.242909588350294</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.07688196151539683</v>
+        <v>0.2174579991845187</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.264512640823769</v>
+        <v>2.475376697327452</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.757929560707483</v>
+        <v>-7.406489466534677</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.009854930296644415</v>
+        <v>0.1504309679657663</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.06600260251822</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.26291756087877</v>
+        <v>2.473781617382453</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.054590902517681</v>
+        <v>-7.703150808344875</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1050306304982267</v>
+        <v>0.0355454071708956</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.134745738252098</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.225450655367651</v>
+        <v>2.436314711871334</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.241310610826984</v>
+        <v>-7.889870516654177</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.183744818356351</v>
+        <v>-0.04316878068722874</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.134745738252098</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.221424350833249</v>
+        <v>2.432288407336931</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.624311999569615</v>
+        <v>-8.272871905396809</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3370474751749875</v>
+        <v>-0.1964714375058652</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.134745738252098</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.221322249511664</v>
+        <v>2.432186306015347</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.80618179055465</v>
+        <v>-8.454741696381843</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4072238755975714</v>
+        <v>-0.2666478379284487</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.668055623409938</v>
+        <v>-1.316615529237134</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.114771890892073</v>
+        <v>2.325635947395756</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.165712113058651</v>
+        <v>-8.814272018885845</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5456857013011218</v>
+        <v>-0.4051096636319991</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.668055623409938</v>
+        <v>-1.316615529237134</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.120122194190123</v>
+        <v>2.330986250693806</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.216061176512873</v>
+        <v>-8.864621082340067</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5579093067256333</v>
+        <v>-0.4173332690565106</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.71840468686416</v>
+        <v>-1.366964592691356</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.097828776074768</v>
+        <v>2.30869283257845</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.313680453934269</v>
+        <v>-8.962240359761463</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5939152670724228</v>
+        <v>-0.4533392294033001</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.816023964285557</v>
+        <v>-1.464583870112752</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.042298960243699</v>
+        <v>2.253163016747382</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.461206541939912</v>
+        <v>-9.109766447767106</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6500321459531078</v>
+        <v>-0.509456108283985</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.9635500522912</v>
+        <v>-1.612109958118396</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.956676863761885</v>
+        <v>2.167540920265568</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.665464717269776</v>
+        <v>-9.314024623096969</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7262222189664107</v>
+        <v>-0.585646181297288</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.091188996905189</v>
+        <v>-1.739748902732385</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.885606694112134</v>
+        <v>2.096470750615817</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.699117555778249</v>
+        <v>-9.347677461605443</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.735200799885364</v>
+        <v>-0.5946247622162413</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.191602364822227</v>
+        <v>-1.840162270649422</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.829841227846347</v>
+        <v>2.04070528435003</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.6256477241108</v>
+        <v>-9.274207629937994</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6904411657249634</v>
+        <v>-0.5498651280558406</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.118132533154778</v>
+        <v>-1.766692438981973</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.889294828340238</v>
+        <v>2.10015888484392</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.800772141497344</v>
+        <v>-9.449332047324537</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7459357119320638</v>
+        <v>-0.6053596742629415</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.293256950541322</v>
+        <v>-1.941816856368517</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.798775398655828</v>
+        <v>2.009639455159511</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.03522423551183</v>
+        <v>-9.683784141339027</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8469357144394558</v>
+        <v>-0.7063596767703331</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.293256950541322</v>
+        <v>-1.941816856368517</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.791556233754232</v>
+        <v>2.002420290257915</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.13959896653828</v>
+        <v>-9.788158872365473</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8953577976240106</v>
+        <v>-0.7547817599548878</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.397631681567768</v>
+        <v>-2.046191587394963</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.722259204364389</v>
+        <v>1.933123260868071</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.19238512213861</v>
+        <v>-9.8409450279658</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9153564700255847</v>
+        <v>-0.7747804323564624</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.493307168150165</v>
+        <v>-2.14186707397736</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.665969702253507</v>
+        <v>1.876833758757189</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.3184219155069</v>
+        <v>-9.966981821334089</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9630774587437858</v>
+        <v>-0.8225014210746635</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.116615451167617</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.683814404568467</v>
+        <v>1.89467846107215</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.26135014361097</v>
+        <v>-9.909910049438158</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9362584142990125</v>
+        <v>-0.7956823766298902</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.116615451167617</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.687804740254867</v>
+        <v>1.89866879675855</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.40302198533509</v>
+        <v>-10.05158189116228</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9944023778874023</v>
+        <v>-0.85382634021828</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.116615451167617</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.686329513356126</v>
+        <v>1.897193569859809</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.35343114091025</v>
+        <v>-10.00199104673744</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9595126299525965</v>
+        <v>-0.8189365922834742</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.418464700915588</v>
+        <v>-2.067024606742784</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.731137430175898</v>
+        <v>1.942001486679581</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.34062374790548</v>
+        <v>-9.98918365373267</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9674408063973696</v>
+        <v>-0.8268647687282473</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.46732047592449</v>
+        <v>-2.115880381751685</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.688772831523875</v>
+        <v>1.899636888027558</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.11477859518607</v>
+        <v>-9.763338501013259</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8675236722733977</v>
+        <v>-0.726947634604274</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.425393800337326</v>
+        <v>-2.073953706164521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.723507909912382</v>
+        <v>1.934371966416065</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.990199938848475</v>
+        <v>-9.638759844675667</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8165530651823016</v>
+        <v>-0.6759770275131785</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.425393800337326</v>
+        <v>-2.073953706164521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.72464705446844</v>
+        <v>1.935511110972123</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.04309522689276</v>
+        <v>-9.691655132719953</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8350774062379083</v>
+        <v>-0.6945013685687851</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.42043845424888</v>
+        <v>-2.068998360076075</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.730254036283616</v>
+        <v>1.941118092787299</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.97096205160488</v>
+        <v>-9.619521957432072</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8004904318841195</v>
+        <v>-0.6599143942149963</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.42043845424888</v>
+        <v>-2.068998360076075</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.735987740522252</v>
+        <v>1.946851797025936</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.899595658995233</v>
+        <v>-9.548155564822425</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7816811372341261</v>
+        <v>-0.6411050995650025</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.349072061639232</v>
+        <v>-1.997631967466427</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.769070313694176</v>
+        <v>1.979934370197859</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.806136625010009</v>
+        <v>-9.4546965308372</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7541810049529438</v>
+        <v>-0.6136049672838202</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.349072061639232</v>
+        <v>-1.997631967466427</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.759186832381268</v>
+        <v>1.970050888884951</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.538894824141611</v>
+        <v>-9.187454729968803</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6491188451049585</v>
+        <v>-0.5085428074358349</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.349072061639232</v>
+        <v>-1.997631967466427</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.757352271881895</v>
+        <v>1.968216328385577</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.44098778546512</v>
+        <v>-9.089547691292312</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6102563446078229</v>
+        <v>-0.4696803069386997</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.281086311778675</v>
+        <v>-1.929646217605871</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.797843406824768</v>
+        <v>2.008707463328451</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.417034244489162</v>
+        <v>-9.065594150316354</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6000064220719463</v>
+        <v>-0.4594303844028227</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.257132770802718</v>
+        <v>-1.905692676629913</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.812884037555836</v>
+        <v>2.023748094059519</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.152974306166366</v>
+        <v>-8.801534211993557</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5076427629045797</v>
+        <v>-0.367066725235456</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.993072832479921</v>
+        <v>-1.641632738307117</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.958059684387762</v>
+        <v>2.168923740891444</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.445894682661528</v>
+        <v>-8.09445458848872</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2275979471629457</v>
+        <v>-0.08702190949382205</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.993072832479921</v>
+        <v>-1.641632738307117</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.955272650727461</v>
+        <v>2.166136707231143</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.405710384295338</v>
+        <v>-8.054270290122529</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2111806039286281</v>
+        <v>-0.07060456625950451</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.952888534113731</v>
+        <v>-1.601448439940926</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.979726853635016</v>
+        <v>2.190590910138699</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.242310513355974</v>
+        <v>-7.890870419183167</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1464538343321258</v>
+        <v>-0.005877796663002588</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.789488663174368</v>
+        <v>-1.438048569001563</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.077133597419391</v>
+        <v>2.287997653923074</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.008829291126375</v>
+        <v>-7.657389196953568</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.04513691660243335</v>
+        <v>0.09543912106668895</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.55600744094477</v>
+        <v>-1.204567346771965</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.225146759595003</v>
+        <v>2.436010816098685</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.85916290011886</v>
+        <v>-7.507722805946053</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.01183742948761335</v>
+        <v>0.1524134671567361</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.463103949702234</v>
+        <v>-1.111663855529429</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.277996644027565</v>
+        <v>2.488860700531248</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.726887426487973</v>
+        <v>-7.375447332315167</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.06011510568699485</v>
+        <v>0.2006911433561176</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.330828476071347</v>
+        <v>-0.9793883818985423</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.352729414953123</v>
+        <v>2.563593471456806</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.571149093928232</v>
+        <v>-7.219708999755425</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1252254993985282</v>
+        <v>0.265801537067651</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.175090143511606</v>
+        <v>-0.8236500493388007</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.448987475176605</v>
+        <v>2.659851531680288</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.322149295244651</v>
+        <v>-6.970709201071844</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2377317600956195</v>
+        <v>0.3783077977647422</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.175090143511606</v>
+        <v>-0.8236500493388007</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.461893816400264</v>
+        <v>2.672757872903947</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.427739285017755</v>
+        <v>-7.076299190844948</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.06751983458715927</v>
+        <v>0.2080958722562816</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.28068013328471</v>
+        <v>-0.9292400391119051</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.270563892937183</v>
+        <v>2.481427949440866</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.446474187136352</v>
+        <v>-7.095034092963545</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1085702156168065</v>
+        <v>0.2491462532859292</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.286276142944841</v>
+        <v>-0.9348360487720364</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.31575062901819</v>
+        <v>2.526614685521873</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.298534145728753</v>
+        <v>-6.947094051555946</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.04786730949167861</v>
+        <v>0.1884433471608014</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.265955227036284</v>
+        <v>-0.9145151328634789</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.208064255875157</v>
+        <v>2.41892831237884</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.245564623474764</v>
+        <v>-6.894124529301958</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.06034113213979619</v>
+        <v>0.2009171698089185</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.212985704782295</v>
+        <v>-0.86154561060949</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.231131982974072</v>
+        <v>2.441996039477755</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.202016216704074</v>
+        <v>-6.850576122531267</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.07079988275297922</v>
+        <v>0.2113759204221015</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.212985704782295</v>
+        <v>-0.86154561060949</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.224171370878979</v>
+        <v>2.435035427382662</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.959867823250216</v>
+        <v>-6.608427729077409</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1821215945156656</v>
+        <v>0.3226976321847879</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.212985704782295</v>
+        <v>-0.86154561060949</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.238633725260122</v>
+        <v>2.449497781763805</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.851608686127694</v>
+        <v>-6.500168591954887</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2199573698238693</v>
+        <v>0.3605334074929916</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.212985704782295</v>
+        <v>-0.86154561060949</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.233165845719317</v>
+        <v>2.444029902223</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.728317551310563</v>
+        <v>-6.376877457137756</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2667719177612984</v>
+        <v>0.4073479554304211</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.089694569965165</v>
+        <v>-0.7382544757923595</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.304638620620172</v>
+        <v>2.515502677123855</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.70716835240712</v>
+        <v>-6.355728258234313</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2829325755600007</v>
+        <v>0.4235086132291235</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.068545371061721</v>
+        <v>-0.7171052768889161</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.325029118199564</v>
+        <v>2.535893174703247</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.463402910423675</v>
+        <v>-6.111962816250869</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3762194607004292</v>
+        <v>0.516795498369552</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.068545371061721</v>
+        <v>-0.7171052768889161</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.320809826546614</v>
+        <v>2.531673883050297</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.361640090146381</v>
+        <v>-6.010199995973574</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4190489027313631</v>
+        <v>0.5596249404004858</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.7038862084964874</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.330865581502088</v>
+        <v>2.541729638005771</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.111789696197306</v>
+        <v>-5.760349602024499</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5117311352946952</v>
+        <v>0.6523071729638179</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.7038862084964874</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.32360765648579</v>
+        <v>2.534471712989473</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.935897603729874</v>
+        <v>-5.584457509557067</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5856870958023168</v>
+        <v>0.7262631334714396</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.7038862084964874</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.327206780006438</v>
+        <v>2.538070836510121</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.76445114070741</v>
+        <v>-5.413011046534604</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6675931870658558</v>
+        <v>0.8081692247349785</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8838798396468294</v>
+        <v>-0.5324397454740243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.44340216387447</v>
+        <v>2.654266220378153</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.690161574969071</v>
+        <v>-5.338721480796265</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6963294909774884</v>
+        <v>0.8369055286466112</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8095902739084901</v>
+        <v>-0.458150179735685</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.48699638093377</v>
+        <v>2.697860437437454</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.626525832735137</v>
+        <v>-5.27508573856233</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7264785889253798</v>
+        <v>0.8670546265945021</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7459545316745556</v>
+        <v>-0.3945144375017505</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.529872627328448</v>
+        <v>2.740736683832131</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.515099073409217</v>
+        <v>-5.16365897923641</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7522435514395434</v>
+        <v>0.8928195891086661</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7459545316745556</v>
+        <v>-0.3945144375017505</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.511066886112244</v>
+        <v>2.721930942615927</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.274668576604356</v>
+        <v>-4.92322848243155</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8501588267863647</v>
+        <v>0.9907348644554874</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5055240348696953</v>
+        <v>-0.1540839406968902</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.657068260820038</v>
+        <v>2.867932317323721</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.202426008433162</v>
+        <v>-4.850985914260355</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8829851678896627</v>
+        <v>1.023561205558785</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5055240348696953</v>
+        <v>-0.1540839406968902</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.660997574654858</v>
+        <v>2.871861631158541</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.149427686151774</v>
+        <v>-4.797987591978967</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9048630807195579</v>
+        <v>1.045439118388681</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4501877758677565</v>
+        <v>-0.09874768169495135</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.694877913973361</v>
+        <v>2.905741970477044</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.040622800672047</v>
+        <v>-4.68918270649924</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9453831061314424</v>
+        <v>1.085959143800565</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4501877758677565</v>
+        <v>-0.09874768169495135</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.691875985193355</v>
+        <v>2.902740041697038</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.820602002635036</v>
+        <v>-4.46916190846223</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.034970462356861</v>
+        <v>1.175546500025983</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3089679307997762</v>
+        <v>0.04247216337302889</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.778186929244757</v>
+        <v>2.98905098574844</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.687734313571759</v>
+        <v>-4.336294219398952</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.104011720783995</v>
+        <v>1.244587758453118</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3089679307997762</v>
+        <v>0.04247216337302889</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.79408111204658</v>
+        <v>3.004945168550263</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.56756123020726</v>
+        <v>-4.216121136034453</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.153226798570096</v>
+        <v>1.293802836239219</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1887948474352773</v>
+        <v>0.1626452467375278</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.867330806505581</v>
+        <v>3.078194863009264</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.422889085107522</v>
+        <v>-4.071448990934716</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.221183759171431</v>
+        <v>1.361759796840554</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.04412270233553989</v>
+        <v>0.3073173918372653</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.964222196126864</v>
+        <v>3.175086252630547</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.482763912465215</v>
+        <v>-4.131323818292408</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.18327131962978</v>
+        <v>1.323847357298903</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.103997529693232</v>
+        <v>0.2474425644795731</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.914334791113674</v>
+        <v>3.125198847617357</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.362943681554378</v>
+        <v>-4.011503587381571</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246488581228324</v>
+        <v>1.387064618897446</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.103997529693232</v>
+        <v>0.2474425644795731</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.929623960347883</v>
+        <v>3.140488016851566</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.365413388016184</v>
+        <v>-4.013973293843377</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153144897966043</v>
+        <v>1.293720935635165</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1064672361550382</v>
+        <v>0.244972858017767</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.835786335793241</v>
+        <v>3.046650392296924</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.910673599960965</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.433783574340194</v>
+        <v>-4.082343480167387</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.13680374591114</v>
+        <v>1.277379783580263</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.2542485570539819</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.852358677689672</v>
+        <v>3.063222734193355</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.901110308592857</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.447571627187241</v>
+        <v>-4.096131533014434</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.121725233404213</v>
+        <v>1.262301271073336</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.2542485570539819</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.842795386321563</v>
+        <v>3.053659442825246</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.725819873633244</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.478564786515946</v>
+        <v>-4.12712469234314</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9340375347131178</v>
+        <v>1.074613572382241</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.2542485570539819</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.66750495136195</v>
+        <v>2.878369007865633</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.730387105625031</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.303090526723476</v>
+        <v>-3.95165043255067</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.008794470621893</v>
+        <v>1.149370508291016</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.2542485570539819</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.672072183353738</v>
+        <v>2.882936239857421</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.706129134386238</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.414026779364725</v>
+        <v>-4.062586685191919</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.940161998326601</v>
+        <v>1.080738035995723</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.2542485570539819</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.647814212114945</v>
+        <v>2.858678268618628</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.709260519606144</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.380363233892443</v>
+        <v>-4.028923139719637</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9567588017354194</v>
+        <v>1.097334839404542</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.2879121025262638</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.671143724618219</v>
+        <v>2.882007781121902</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.719432906038276</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.32051061468872</v>
+        <v>-3.969070520515913</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9908722358490409</v>
+        <v>1.131448273518164</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.2879121025262638</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.681316111050352</v>
+        <v>2.892180167554035</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.714379176612137</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.234267151662342</v>
+        <v>-3.882827057489536</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.020315891633452</v>
+        <v>1.160891929302575</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.2879121025262638</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.676262381624212</v>
+        <v>2.887126438127895</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.706154952056662</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.279573971061322</v>
+        <v>-3.928133876888515</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9939689393183859</v>
+        <v>1.134544976987509</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1043381546557722</v>
+        <v>0.247101939517033</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.643552059263199</v>
+        <v>2.854416115766882</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.706706825089764</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.308607075763623</v>
+        <v>-3.957166981590817</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9829075704705672</v>
+        <v>1.12348360813969</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1043381546557722</v>
+        <v>0.247101939517033</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.6441039322963</v>
+        <v>2.854967988799984</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.635979516981129</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.215796594312764</v>
+        <v>-3.864356500139958</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9493044549422767</v>
+        <v>1.089880492611399</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.01152767320491282</v>
+        <v>0.3399124209678923</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.629062913058182</v>
+        <v>2.839926969561865</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.63785299290573</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.260186063642191</v>
+        <v>-3.908745969469385</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9334221431351064</v>
+        <v>1.073998180804229</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.05591714253434049</v>
+        <v>0.2955229516384646</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.604302707385126</v>
+        <v>2.815166763888809</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.632928701417453</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.147514845405941</v>
+        <v>-3.796074751233135</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9735663389413296</v>
+        <v>1.114142376610452</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.05675407570190971</v>
+        <v>0.4081941698747149</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.666981146838599</v>
+        <v>2.877845203342282</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.00456586806756</v>
+        <v>-3.653125773894754</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.036237225707349</v>
+        <v>1.176813263376471</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.05675407570190971</v>
+        <v>0.4081941698747149</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.672472442669267</v>
+        <v>2.88333649917295</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.032346265968913</v>
+        <v>-3.680906171796107</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.036622268315347</v>
+        <v>1.177198305984469</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.02897367780055665</v>
+        <v>0.3804137719733618</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667301405696994</v>
+        <v>2.878165462200677</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.115347546994192</v>
+        <v>-3.763907452821386</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8417774759058887</v>
+        <v>0.982353513575011</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.361842887446188</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.494514594981343</v>
+        <v>2.705378651485026</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.223961625437523</v>
+        <v>-3.872521531264717</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9184815052477617</v>
+        <v>1.059057542916884</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.361842887446188</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.614664255700548</v>
+        <v>2.825528312204232</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.18855258718938</v>
+        <v>-3.837112493016575</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9471581466493419</v>
+        <v>1.087734184318464</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.361842887446188</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.629177281802871</v>
+        <v>2.840041338306555</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.150168924631229</v>
+        <v>-3.798728830458423</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9599310530149712</v>
+        <v>1.100507090684093</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.4002265500043392</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.649626920680131</v>
+        <v>2.860490977183814</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.973052594596063</v>
+        <v>-3.621612500423257</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.02750661387434</v>
+        <v>1.168082651543462</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.4002265500043392</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.646355949525433</v>
+        <v>2.857220006029116</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.018144839429609</v>
+        <v>-3.666704745256803</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.010153107702835</v>
+        <v>1.150729145371957</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01310958733785572</v>
+        <v>0.3383305068349494</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609901715385712</v>
+        <v>2.820765771889395</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.838769418190841</v>
+        <v>-3.487329324018035</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.075690251504756</v>
+        <v>1.216266289173878</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.143667170832863</v>
+        <v>0.495107265005668</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.697754745594558</v>
+        <v>2.908618802098241</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.883783631711447</v>
+        <v>-3.532343537538642</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.038492021428103</v>
+        <v>1.179068059097226</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1133182755182583</v>
+        <v>0.4647583696910634</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660352863737385</v>
+        <v>2.871216920241068</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.150788141983883</v>
+        <v>-3.799348047811077</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.937381779658075</v>
+        <v>1.077957817327197</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08104476252469023</v>
+        <v>0.2703953316481149</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549426603250561</v>
+        <v>2.760290659754244</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.251985923421056</v>
+        <v>-3.90054582924825</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8961065889797073</v>
+        <v>1.03668262664883</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1494535760700094</v>
+        <v>0.2019865181027957</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.507585237019871</v>
+        <v>2.718449293523554</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.245474956806743</v>
+        <v>-3.894034862633937</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8963109371797491</v>
+        <v>1.036886974848871</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1494535760700094</v>
+        <v>0.2019865181027957</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.505185198574188</v>
+        <v>2.716049255077871</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.226436829099446</v>
+        <v>-3.87499673492664</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9004509074709128</v>
+        <v>1.041026945140035</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.207637187401204</v>
+        <v>0.1438029067716011</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.466799750983717</v>
+        <v>2.6776638074874</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.257563460250064</v>
+        <v>-3.906123366077258</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.065582123949346</v>
+        <v>1.206158161618469</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.207637187401204</v>
+        <v>0.1438029067716011</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.644381619922397</v>
+        <v>2.85524567642608</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.271430221583982</v>
+        <v>-3.919990127411175</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.060868748401913</v>
+        <v>1.201444786071035</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2454951041350269</v>
+        <v>0.1059449900377782</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.622500198868237</v>
+        <v>2.83336425537192</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.226626050044052</v>
+        <v>-3.875185955871245</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.08479894741481</v>
+        <v>1.225374985083933</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2454951041350269</v>
+        <v>0.1059449900377782</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.628508729265163</v>
+        <v>2.839372785768846</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.078883079809049</v>
+        <v>-3.727442985636243</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.223048783300833</v>
+        <v>1.363624820969956</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.07768774690014374</v>
+        <v>0.2737523472726613</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.808345791398114</v>
+        <v>3.019209847901797</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.180897762340271</v>
+        <v>-3.829457668167464</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.185036531819826</v>
+        <v>1.325612569488948</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.07768774690014374</v>
+        <v>0.2737523472726613</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.811139412929595</v>
+        <v>3.022003469433278</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.174745056287486</v>
+        <v>-3.82330496211468</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.188159962632598</v>
+        <v>1.328736000301721</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.07153504084735945</v>
+        <v>0.2799050533254456</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.815493384952924</v>
+        <v>3.026357441456607</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.191554354437988</v>
+        <v>-3.840114260265181</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.180516720112507</v>
+        <v>1.32109275778163</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.08834433899786109</v>
+        <v>0.263095755174944</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.804488282802734</v>
+        <v>3.015352339306417</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.129256355661866</v>
+        <v>-3.777816261489059</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.271771473419777</v>
+        <v>1.4123475110889</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.08834433899786109</v>
+        <v>0.263095755174944</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.870823836599555</v>
+        <v>3.081687893103238</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.927466157996708</v>
+        <v>-3.576026063823901</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.061068424875238</v>
+        <v>1.201644462544361</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1096738531712933</v>
+        <v>0.4611139473440984</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.698215624290445</v>
+        <v>2.909079680794128</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.854088060907972</v>
+        <v>-3.502647966735165</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.160709896032908</v>
+        <v>1.301285933702031</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1830519502600298</v>
+        <v>0.5344920444328349</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.812532714865863</v>
+        <v>3.023396771369546</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.951828605532946</v>
+        <v>-3.600388511360139</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.136241414298962</v>
+        <v>1.276817451968085</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1671626721270497</v>
+        <v>0.5186027662998547</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.817626884102118</v>
+        <v>3.028490940605801</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.128166365655876</v>
+        <v>-3.776726271483068</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.064242291074462</v>
+        <v>1.204818328743585</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.009175087995879738</v>
+        <v>0.3422650061769253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.710360208853032</v>
+        <v>2.921224265356715</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.051744319223949</v>
+        <v>-3.700304225051142</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.093302727687161</v>
+        <v>1.233878765356284</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.009175087995879738</v>
+        <v>0.3422650061769253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.70885182689296</v>
+        <v>2.919715883396643</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.00737118758538</v>
+        <v>-3.655931093412573</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.110914847778025</v>
+        <v>1.251490885447148</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.03519804364268886</v>
+        <v>0.3866381378154939</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.735338573311538</v>
+        <v>2.946202629815221</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.884536966698213</v>
+        <v>-3.533096872525406</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.154442330271482</v>
+        <v>1.295018367940605</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.03519804364268886</v>
+        <v>0.3866381378154939</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.729732367450128</v>
+        <v>2.940596423953811</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.836881236137157</v>
+        <v>-3.48544114196435</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.179886379523709</v>
+        <v>1.320462417192831</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.08285377420374451</v>
+        <v>0.4342938683765495</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.764707562814566</v>
+        <v>2.975571619318249</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.736363077638402</v>
+        <v>-3.384922983465596</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.224986016297936</v>
+        <v>1.365562053967058</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1833719327024991</v>
+        <v>0.534812026875304</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.829910831288543</v>
+        <v>3.040774887792226</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.797029668040791</v>
+        <v>-3.445589573867985</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.187474052612852</v>
+        <v>1.328050090281975</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1016736159839654</v>
+        <v>0.4531137101567704</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.767646513733296</v>
+        <v>2.978510570236979</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.752191266432393</v>
+        <v>-3.400751172259587</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.20950711586684</v>
+        <v>1.350083153535963</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1062170489288349</v>
+        <v>0.4576571431016399</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.774470276110846</v>
+        <v>2.985334332614529</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.852949902189392</v>
+        <v>-3.501509808016585</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.173364601195118</v>
+        <v>1.313940638864241</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.01739148020182946</v>
+        <v>0.3688315743746344</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.725335874505721</v>
+        <v>2.936199931009404</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.808747065103491</v>
+        <v>-3.457306970930685</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.196925338557316</v>
+        <v>1.337501376226438</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.0615943172877299</v>
+        <v>0.4130344114605349</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.757737179285098</v>
+        <v>2.968601235788781</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.845726092766935</v>
+        <v>-3.494285998594128</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.180543727961186</v>
+        <v>1.321119765630309</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.09856821907906044</v>
+        <v>0.4500083132518654</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.778331520829144</v>
+        <v>2.989195577332826</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.865784171631775</v>
+        <v>-3.514344077458968</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.22376826159829</v>
+        <v>1.364344299267412</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.09856821907906044</v>
+        <v>0.4500083132518654</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.829579286012184</v>
+        <v>3.040443342515866</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.825853498453884</v>
+        <v>-3.474413404281078</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.238181235463699</v>
+        <v>1.378757273132822</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1384988922569508</v>
+        <v>0.4899389864297558</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.851978394513171</v>
+        <v>3.062842451016854</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.774821405731356</v>
+        <v>-3.42338131155855</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.25354230079098</v>
+        <v>1.394118338460103</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1895309849794787</v>
+        <v>0.5409710791522837</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.877545878384958</v>
+        <v>3.088409934888641</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.709597224604151</v>
+        <v>-3.358157130431344</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.296819377334567</v>
+        <v>1.43739541500369</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2547551661066844</v>
+        <v>0.6061952602794893</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.933867791153986</v>
+        <v>3.144731847657669</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.672170204533017</v>
+        <v>-3.32073011036021</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.307751157662301</v>
+        <v>1.448327195331424</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.260006704135866</v>
+        <v>0.611446798308671</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.932979686270775</v>
+        <v>3.143843742774458</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.692281860567725</v>
+        <v>-3.340841766394919</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.300963287579658</v>
+        <v>1.441539325248781</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2710340491332852</v>
+        <v>0.6224741433060902</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.940852885600467</v>
+        <v>3.15171694210415</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.638537046140521</v>
+        <v>-3.287096951967714</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.483018984371751</v>
+        <v>1.623595022040873</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2810973585737472</v>
+        <v>0.6325374527465522</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.107448642285955</v>
+        <v>3.318312698789638</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.614745477534378</v>
+        <v>-3.263305383361572</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.612648521032025</v>
+        <v>1.753224558701148</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.3048889271798895</v>
+        <v>0.6563290213526944</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.241836492667458</v>
+        <v>3.452700549171141</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.58866139327057</v>
+        <v>-3.237221299097764</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.614790130751407</v>
+        <v>1.75536616842053</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.3048889271798895</v>
+        <v>0.6563290213526944</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.233544468681317</v>
+        <v>3.444408525185</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.510530212421624</v>
+        <v>-3.159090118248817</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.644235798674765</v>
+        <v>1.784811836343888</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.379065738063574</v>
+        <v>0.730505832236379</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.276243750795307</v>
+        <v>3.48710780729899</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.501637751028341</v>
+        <v>-3.150197656855534</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.66534718895887</v>
+        <v>1.805923226627993</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.379065738063574</v>
+        <v>0.730505832236379</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.293798156522098</v>
+        <v>3.504662213025781</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.670113867998218</v>
+        <v>-3.318673773825412</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.589811789575503</v>
+        <v>1.730387827244625</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3511179023469932</v>
+        <v>0.7025579965197982</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.268884502496733</v>
+        <v>3.479748559000416</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.972314339136635</v>
+        <v>-2.620874244963828</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.850201298307998</v>
+        <v>1.99077733597712</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2807698429765825</v>
+        <v>0.6322099371493874</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.207945364062349</v>
+        <v>3.418809420566032</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.949593235453483</v>
+        <v>-2.598153141280676</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.849953762278163</v>
+        <v>1.990529799947286</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2807698429765825</v>
+        <v>0.6322099371493874</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.198609386559253</v>
+        <v>3.409473443062936</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.947868192163439</v>
+        <v>-2.596428097990632</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.00954990544535</v>
+        <v>2.150125943114473</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2824948862666263</v>
+        <v>0.6339349804394312</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.358550538384449</v>
+        <v>3.569414594888132</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.102649198941694</v>
+        <v>-2.751209104768887</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.984715325227695</v>
+        <v>2.125291362896817</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2491272122121502</v>
+        <v>0.600567306384955</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.37560775644541</v>
+        <v>3.586471812949092</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.051213865557034</v>
+        <v>-2.699773771384228</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.001964814571104</v>
+        <v>2.142540852240226</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.3005625455968098</v>
+        <v>0.6520026397696147</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.403144312465751</v>
+        <v>3.614008368969434</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.024262641230546</v>
+        <v>-2.67282254705774</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.02275145794644</v>
+        <v>2.163327495615563</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.315442891624529</v>
+        <v>0.6668829857973338</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.422078673727124</v>
+        <v>3.632942730230806</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.160215649286862</v>
+        <v>-2.808775555114056</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.152473386868873</v>
+        <v>2.293049424537996</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.315442891624529</v>
+        <v>0.6668829857973338</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.606181805872084</v>
+        <v>3.817045862375767</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.182623767091735</v>
+        <v>-2.831183672918928</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.135626834649918</v>
+        <v>2.276202872319041</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.315442891624529</v>
+        <v>0.6668829857973338</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.598298500775077</v>
+        <v>3.80916255727876</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.330629534571134</v>
+        <v>-2.979189440398327</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.078478527207795</v>
+        <v>2.219054564876918</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2287158827609875</v>
+        <v>0.5801559769337924</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.548316295006589</v>
+        <v>3.759180351510272</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.340070460459664</v>
+        <v>-2.988630366286857</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.130955874574231</v>
+        <v>2.271531912243353</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3511430003043789</v>
+        <v>0.7025830944771838</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.678026283254471</v>
+        <v>3.888890339758154</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.338783696920108</v>
+        <v>-2.987343602747301</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.134361674535354</v>
+        <v>2.274937712204477</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3524297638439355</v>
+        <v>0.7038698580167404</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.681689435923506</v>
+        <v>3.892553492427189</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.340340750909399</v>
+        <v>-2.988900656736592</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.131850665833412</v>
+        <v>2.272426703502536</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3524297638439355</v>
+        <v>0.7038698580167404</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.679801248817281</v>
+        <v>3.890665305320964</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.347612636432864</v>
+        <v>-2.996172542260057</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.123762141226889</v>
+        <v>2.264338178896012</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3451578783204708</v>
+        <v>0.6965979724932756</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.670258347106065</v>
+        <v>3.881122403609747</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.345771617374612</v>
+        <v>-2.994331523201806</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.122932559060342</v>
+        <v>2.263508596729465</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.697866199164744</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.669453293319098</v>
+        <v>3.880317349822781</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.352680322874293</v>
+        <v>-3.001240228701486</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.133242483726388</v>
+        <v>2.273818521395511</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.697866199164744</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.682526700185017</v>
+        <v>3.893390756688699</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.354241965689153</v>
+        <v>-3.002801871516346</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.132617826600445</v>
+        <v>2.273193864269567</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.697866199164744</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.682526700185017</v>
+        <v>3.893390756688699</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.382142752798626</v>
+        <v>-3.030702658625819</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.119981552883657</v>
+        <v>2.26055759055278</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3118291808490044</v>
+        <v>0.6632692750218092</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.660292586826258</v>
+        <v>3.87115664332994</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.3851757503113</v>
+        <v>-3.033735656138493</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.115532797855787</v>
+        <v>2.256108835524909</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3087961833363305</v>
+        <v>0.6602362775091353</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.655237232295852</v>
+        <v>3.866101288799535</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.405237071587806</v>
+        <v>-3.053796977415</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.174214228935687</v>
+        <v>2.31479026660481</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2887348620598235</v>
+        <v>0.6401749562326282</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.709906399120452</v>
+        <v>3.920770455624135</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.393898527912991</v>
+        <v>3.900969397761619</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.538342569767444</v>
+        <v>-3.215750947545854</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.261283748665679</v>
+        <v>2.390320397554316</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2351067767257327</v>
+        <v>0.6963897928771982</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.818041266921844</v>
+        <v>4.094811076612723</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-624.3%</t>
+          <t>-659.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-67.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>464.2%</t>
+          <t>456.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-483.1%</t>
+          <t>-494.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-250.1%</t>
+          <t>-264.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-137.2%</t>
+          <t>-141.8%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-243.5%</t>
+          <t>-278.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-267.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-184.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,21 +1447,21 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-146.5%</t>
+          <t>-167.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-73.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2016"/>
+  <dimension ref="A1:G2017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7763135644067872</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.806198599874567</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.339501676855488</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.920781456064323</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.066445231012219</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.690012149831317</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.363583471595668</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.935096749507353</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.274449289365296</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.611702671044011</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.363583471595668</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.939988894061278</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.485861710253271</v>
+        <v>-1.837301804426076</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.522219159026809</v>
+        <v>2.381643121357687</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.152171050707693</v>
+        <v>0.8007309565348886</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.80822289786648</v>
+        <v>3.597358841362798</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.851930437397923</v>
+        <v>-2.203370531570728</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.368875967475397</v>
+        <v>2.228299929806275</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7861023235630406</v>
+        <v>0.4346622293902359</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.581665960886138</v>
+        <v>3.370801904382455</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.060421218849608</v>
+        <v>-2.411861313022413</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.305817944633492</v>
+        <v>2.165241906964369</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5776115421113561</v>
+        <v>0.2261714479385515</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.476909781753896</v>
+        <v>3.266045725250213</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.307622403614829</v>
+        <v>-2.659062497787635</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.215036221135971</v>
+        <v>2.074460183466849</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.5977648956101685</v>
+        <v>0.2463248014373639</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.497100544261752</v>
+        <v>3.286236487758069</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.800007431638926</v>
+        <v>-3.151447525811732</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.019188601970065</v>
+        <v>1.878612564300943</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1053798675860718</v>
+        <v>-0.2460602265867328</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.202775919491026</v>
+        <v>2.991911862987343</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.185187822568999</v>
+        <v>-3.536627916741804</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.863658984410899</v>
+        <v>1.723082946741777</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1053798675860718</v>
+        <v>-0.2460602265867328</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.201318458303889</v>
+        <v>2.990454401800207</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.43505850258358</v>
+        <v>-3.786498596756386</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.765479835859683</v>
+        <v>1.624903798190561</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.1416425874165351</v>
+        <v>-0.2097975067562696</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.224845213656784</v>
+        <v>3.013981157153101</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.641570279470602</v>
+        <v>-3.993010373643407</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.678981183761132</v>
+        <v>1.53840514609201</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.06486918947048642</v>
+        <v>-0.4163092836432911</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.097044206180828</v>
+        <v>2.886180149677146</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.960914354551103</v>
+        <v>-4.312354448723909</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.553016480429191</v>
+        <v>1.412440442760069</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.06486918947048642</v>
+        <v>-0.4163092836432911</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.098817132881088</v>
+        <v>2.887953076377405</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.39272014770089</v>
+        <v>-4.744160241873696</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.36662705063668</v>
+        <v>1.226051012967558</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2012866859117534</v>
+        <v>-0.5527267800845581</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.003299522483732</v>
+        <v>2.792435465980049</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.627414141833443</v>
+        <v>-4.978854236006248</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.26103422798575</v>
+        <v>1.120458190316628</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1949504186824982</v>
+        <v>-0.5463905128553029</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.995386057823376</v>
+        <v>2.784522001319693</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.963076789063895</v>
+        <v>-5.314516883236701</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.125349760749534</v>
+        <v>0.9847737230804121</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.262881404171403</v>
+        <v>-0.6143214983442078</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.953208058185998</v>
+        <v>2.742344001682315</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.326703033964209</v>
+        <v>-5.678143128137014</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9863868230236501</v>
+        <v>0.8458107853545282</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3611030410385289</v>
+        <v>-0.7125431352113336</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.900762636299964</v>
+        <v>2.689898579796282</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.691830416602955</v>
+        <v>-6.043270510775761</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8395903849739828</v>
+        <v>0.6990143473048609</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6574138253375414</v>
+        <v>-1.008853919510346</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.722230680726388</v>
+        <v>2.511366624222705</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.100419193783634</v>
+        <v>-6.45185928795644</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6749164181164704</v>
+        <v>0.5343403804473486</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.47583895843274</v>
+        <v>2.264974901929057</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.376995294099467</v>
+        <v>-6.728435388272272</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5594714104615979</v>
+        <v>0.418895372792476</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.4710243909042</v>
+        <v>2.260160334400518</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.793387168386464</v>
+        <v>-7.14482726255927</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3909087113556762</v>
+        <v>0.2503326736865543</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.469018441513078</v>
+        <v>2.258154385009395</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.037658569113534</v>
+        <v>-7.389098663286339</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3034588417335273</v>
+        <v>0.1628828040644055</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.479277132181757</v>
+        <v>2.268413075678074</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.242909588350294</v>
+        <v>-7.5943496825231</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2174579991845187</v>
+        <v>0.07688196151539683</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.475376697327452</v>
+        <v>2.264512640823769</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.406489466534677</v>
+        <v>-7.757929560707483</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1504309679657663</v>
+        <v>0.009854930296644415</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.06600260251822</v>
+        <v>-1.417442696691025</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.473781617382453</v>
+        <v>2.26291756087877</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.703150808344875</v>
+        <v>-8.054590902517681</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.0355454071708956</v>
+        <v>-0.1050306304982267</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.134745738252098</v>
+        <v>-1.486185832424903</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.436314711871334</v>
+        <v>2.225450655367651</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.889870516654177</v>
+        <v>-8.241310610826984</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.04316878068722874</v>
+        <v>-0.183744818356351</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.134745738252098</v>
+        <v>-1.486185832424903</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.432288407336931</v>
+        <v>2.221424350833249</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.272871905396809</v>
+        <v>-8.624311999569615</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1964714375058652</v>
+        <v>-0.3370474751749875</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.134745738252098</v>
+        <v>-1.486185832424903</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.432186306015347</v>
+        <v>2.221322249511664</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.454741696381843</v>
+        <v>-8.80618179055465</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2666478379284487</v>
+        <v>-0.4072238755975714</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.316615529237134</v>
+        <v>-1.668055623409938</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.325635947395756</v>
+        <v>2.114771890892073</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.814272018885845</v>
+        <v>-9.165712113058651</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4051096636319991</v>
+        <v>-0.5456857013011218</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.316615529237134</v>
+        <v>-1.668055623409938</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.330986250693806</v>
+        <v>2.120122194190123</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.864621082340067</v>
+        <v>-9.216061176512873</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4173332690565106</v>
+        <v>-0.5579093067256333</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.366964592691356</v>
+        <v>-1.71840468686416</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.30869283257845</v>
+        <v>2.097828776074768</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.962240359761463</v>
+        <v>-9.313680453934269</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4533392294033001</v>
+        <v>-0.5939152670724228</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.464583870112752</v>
+        <v>-1.816023964285557</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.253163016747382</v>
+        <v>2.042298960243699</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.109766447767106</v>
+        <v>-9.461206541939912</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.509456108283985</v>
+        <v>-0.6500321459531078</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.612109958118396</v>
+        <v>-1.9635500522912</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.167540920265568</v>
+        <v>1.956676863761885</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.314024623096969</v>
+        <v>-9.665464717269776</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.585646181297288</v>
+        <v>-0.7262222189664107</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.739748902732385</v>
+        <v>-2.091188996905189</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.096470750615817</v>
+        <v>1.885606694112134</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.347677461605443</v>
+        <v>-9.699117555778249</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5946247622162413</v>
+        <v>-0.735200799885364</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.840162270649422</v>
+        <v>-2.191602364822227</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.04070528435003</v>
+        <v>1.829841227846347</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.274207629937994</v>
+        <v>-9.6256477241108</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5498651280558406</v>
+        <v>-0.6904411657249634</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.766692438981973</v>
+        <v>-2.118132533154778</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.10015888484392</v>
+        <v>1.889294828340238</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.449332047324537</v>
+        <v>-9.800772141497344</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6053596742629415</v>
+        <v>-0.7459357119320638</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.941816856368517</v>
+        <v>-2.293256950541322</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.009639455159511</v>
+        <v>1.798775398655828</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.683784141339027</v>
+        <v>-10.03522423551183</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7063596767703331</v>
+        <v>-0.8469357144394558</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.941816856368517</v>
+        <v>-2.293256950541322</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.002420290257915</v>
+        <v>1.791556233754232</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.788158872365473</v>
+        <v>-10.13959896653828</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7547817599548878</v>
+        <v>-0.8953577976240106</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.046191587394963</v>
+        <v>-2.397631681567768</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.933123260868071</v>
+        <v>1.722259204364389</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.8409450279658</v>
+        <v>-10.19238512213861</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7747804323564624</v>
+        <v>-0.9153564700255847</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.14186707397736</v>
+        <v>-2.493307168150165</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.876833758757189</v>
+        <v>1.665969702253507</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.966981821334089</v>
+        <v>-10.3184219155069</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.8225014210746635</v>
+        <v>-0.9630774587437858</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.116615451167617</v>
+        <v>-2.468055545340422</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.89467846107215</v>
+        <v>1.683814404568467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.909910049438158</v>
+        <v>-10.26135014361097</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7956823766298902</v>
+        <v>-0.9362584142990125</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.116615451167617</v>
+        <v>-2.468055545340422</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.89866879675855</v>
+        <v>1.687804740254867</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.05158189116228</v>
+        <v>-10.40302198533509</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.85382634021828</v>
+        <v>-0.9944023778874023</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.116615451167617</v>
+        <v>-2.468055545340422</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.897193569859809</v>
+        <v>1.686329513356126</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.00199104673744</v>
+        <v>-10.35343114091025</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.8189365922834742</v>
+        <v>-0.9595126299525965</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.067024606742784</v>
+        <v>-2.418464700915588</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.942001486679581</v>
+        <v>1.731137430175898</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.98918365373267</v>
+        <v>-10.34062374790548</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8268647687282473</v>
+        <v>-0.9674408063973696</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.115880381751685</v>
+        <v>-2.46732047592449</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.899636888027558</v>
+        <v>1.688772831523875</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.763338501013259</v>
+        <v>-10.11477859518607</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.726947634604274</v>
+        <v>-0.8675236722733977</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.073953706164521</v>
+        <v>-2.425393800337326</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.934371966416065</v>
+        <v>1.723507909912382</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.638759844675667</v>
+        <v>-9.990199938848475</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6759770275131785</v>
+        <v>-0.8165530651823016</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.073953706164521</v>
+        <v>-2.425393800337326</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.935511110972123</v>
+        <v>1.72464705446844</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.691655132719953</v>
+        <v>-10.04309522689276</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6945013685687851</v>
+        <v>-0.8350774062379083</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.068998360076075</v>
+        <v>-2.42043845424888</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.941118092787299</v>
+        <v>1.730254036283616</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.619521957432072</v>
+        <v>-9.97096205160488</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6599143942149963</v>
+        <v>-0.8004904318841195</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.068998360076075</v>
+        <v>-2.42043845424888</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.946851797025936</v>
+        <v>1.735987740522252</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.548155564822425</v>
+        <v>-9.899595658995233</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6411050995650025</v>
+        <v>-0.7816811372341261</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.997631967466427</v>
+        <v>-2.349072061639232</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.979934370197859</v>
+        <v>1.769070313694176</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.4546965308372</v>
+        <v>-9.806136625010009</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6136049672838202</v>
+        <v>-0.7541810049529438</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.997631967466427</v>
+        <v>-2.349072061639232</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.970050888884951</v>
+        <v>1.759186832381268</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.187454729968803</v>
+        <v>-9.538894824141611</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5085428074358349</v>
+        <v>-0.6491188451049585</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.997631967466427</v>
+        <v>-2.349072061639232</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.968216328385577</v>
+        <v>1.757352271881895</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.089547691292312</v>
+        <v>-9.44098778546512</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4696803069386997</v>
+        <v>-0.6102563446078229</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.929646217605871</v>
+        <v>-2.281086311778675</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.008707463328451</v>
+        <v>1.797843406824768</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.065594150316354</v>
+        <v>-9.417034244489162</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4594303844028227</v>
+        <v>-0.6000064220719463</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.905692676629913</v>
+        <v>-2.257132770802718</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.023748094059519</v>
+        <v>1.812884037555836</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.801534211993557</v>
+        <v>-9.152974306166366</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.367066725235456</v>
+        <v>-0.5076427629045797</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.641632738307117</v>
+        <v>-1.993072832479921</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.168923740891444</v>
+        <v>1.958059684387762</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.09445458848872</v>
+        <v>-8.445894682661528</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.08702190949382205</v>
+        <v>-0.2275979471629457</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.641632738307117</v>
+        <v>-1.993072832479921</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.166136707231143</v>
+        <v>1.955272650727461</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.054270290122529</v>
+        <v>-8.405710384295338</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.07060456625950451</v>
+        <v>-0.2111806039286281</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.601448439940926</v>
+        <v>-1.952888534113731</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.190590910138699</v>
+        <v>1.979726853635016</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.890870419183167</v>
+        <v>-8.242310513355974</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.005877796663002588</v>
+        <v>-0.1464538343321258</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.438048569001563</v>
+        <v>-1.789488663174368</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.287997653923074</v>
+        <v>2.077133597419391</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.657389196953568</v>
+        <v>-8.008829291126375</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.09543912106668895</v>
+        <v>-0.04513691660243335</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.204567346771965</v>
+        <v>-1.55600744094477</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.436010816098685</v>
+        <v>2.225146759595003</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.507722805946053</v>
+        <v>-7.85916290011886</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1524134671567361</v>
+        <v>0.01183742948761335</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.111663855529429</v>
+        <v>-1.463103949702234</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.488860700531248</v>
+        <v>2.277996644027565</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.375447332315167</v>
+        <v>-7.726887426487973</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2006911433561176</v>
+        <v>0.06011510568699485</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9793883818985423</v>
+        <v>-1.330828476071347</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.563593471456806</v>
+        <v>2.352729414953123</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.219708999755425</v>
+        <v>-7.571149093928232</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.265801537067651</v>
+        <v>0.1252254993985282</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.8236500493388007</v>
+        <v>-1.175090143511606</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.659851531680288</v>
+        <v>2.448987475176605</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.970709201071844</v>
+        <v>-7.322149295244651</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3783077977647422</v>
+        <v>0.2377317600956195</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.8236500493388007</v>
+        <v>-1.175090143511606</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.672757872903947</v>
+        <v>2.461893816400264</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.076299190844948</v>
+        <v>-7.427739285017755</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2080958722562816</v>
+        <v>0.06751983458715927</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9292400391119051</v>
+        <v>-1.28068013328471</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.481427949440866</v>
+        <v>2.270563892937183</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.095034092963545</v>
+        <v>-7.446474187136352</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2491462532859292</v>
+        <v>0.1085702156168065</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9348360487720364</v>
+        <v>-1.286276142944841</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.526614685521873</v>
+        <v>2.31575062901819</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.947094051555946</v>
+        <v>-7.298534145728753</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1884433471608014</v>
+        <v>0.04786730949167861</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9145151328634789</v>
+        <v>-1.265955227036284</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.41892831237884</v>
+        <v>2.208064255875157</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.894124529301958</v>
+        <v>-7.245564623474764</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2009171698089185</v>
+        <v>0.06034113213979619</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.86154561060949</v>
+        <v>-1.212985704782295</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.441996039477755</v>
+        <v>2.231131982974072</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.850576122531267</v>
+        <v>-7.202016216704074</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2113759204221015</v>
+        <v>0.07079988275297922</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.86154561060949</v>
+        <v>-1.212985704782295</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.435035427382662</v>
+        <v>2.224171370878979</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.608427729077409</v>
+        <v>-6.959867823250216</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3226976321847879</v>
+        <v>0.1821215945156656</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.86154561060949</v>
+        <v>-1.212985704782295</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.449497781763805</v>
+        <v>2.238633725260122</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.500168591954887</v>
+        <v>-6.851608686127694</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3605334074929916</v>
+        <v>0.2199573698238693</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.86154561060949</v>
+        <v>-1.212985704782295</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.444029902223</v>
+        <v>2.233165845719317</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.376877457137756</v>
+        <v>-6.728317551310563</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4073479554304211</v>
+        <v>0.2667719177612984</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7382544757923595</v>
+        <v>-1.089694569965165</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.515502677123855</v>
+        <v>2.304638620620172</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.355728258234313</v>
+        <v>-6.70716835240712</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4235086132291235</v>
+        <v>0.2829325755600007</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7171052768889161</v>
+        <v>-1.068545371061721</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.535893174703247</v>
+        <v>2.325029118199564</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.111962816250869</v>
+        <v>-6.463402910423675</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.516795498369552</v>
+        <v>0.3762194607004292</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7171052768889161</v>
+        <v>-1.068545371061721</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.531673883050297</v>
+        <v>2.320809826546614</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.010199995973574</v>
+        <v>-6.208096370408748</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5596249404004858</v>
+        <v>0.4804663906264164</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7038862084964874</v>
+        <v>-0.9758555951826148</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.541729638005771</v>
+        <v>2.378548005994094</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.760349602024499</v>
+        <v>-5.958245976459673</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6523071729638179</v>
+        <v>0.5731486231897485</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7038862084964874</v>
+        <v>-0.9758555951826148</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.534471712989473</v>
+        <v>2.371290080977796</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.584457509557067</v>
+        <v>-5.78235388399224</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7262631334714396</v>
+        <v>0.6471045836973706</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7038862084964874</v>
+        <v>-0.9758555951826148</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.538070836510121</v>
+        <v>2.374889204498445</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.413011046534604</v>
+        <v>-5.610907420969776</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8081692247349785</v>
+        <v>0.7290106749609095</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5324397454740243</v>
+        <v>-0.8044091321601516</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.654266220378153</v>
+        <v>2.491084588366477</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.338721480796265</v>
+        <v>-5.536617855231437</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8369055286466112</v>
+        <v>0.7577469788725422</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.458150179735685</v>
+        <v>-0.7301195664218123</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.697860437437454</v>
+        <v>2.534678805425777</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.27508573856233</v>
+        <v>-5.472982112997503</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8670546265945021</v>
+        <v>0.7878960768204331</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3945144375017505</v>
+        <v>-0.6664838241878778</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.740736683832131</v>
+        <v>2.577555051820455</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.16365897923641</v>
+        <v>-5.361555353671583</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8928195891086661</v>
+        <v>0.8136610393345967</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3945144375017505</v>
+        <v>-0.6664838241878778</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.721930942615927</v>
+        <v>2.558749310604251</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.92322848243155</v>
+        <v>-5.121124856866722</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9907348644554874</v>
+        <v>0.9115763146814184</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1540839406968902</v>
+        <v>-0.4260533273830175</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.867932317323721</v>
+        <v>2.704750685312044</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.850985914260355</v>
+        <v>-5.048882288695528</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.023561205558785</v>
+        <v>0.9444026557847165</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1540839406968902</v>
+        <v>-0.4260533273830175</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.871861631158541</v>
+        <v>2.708679999146864</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.797987591978967</v>
+        <v>-4.99588396641414</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.045439118388681</v>
+        <v>0.9662805686146116</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.09874768169495135</v>
+        <v>-0.3707170683810787</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.905741970477044</v>
+        <v>2.742560338465368</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.68918270649924</v>
+        <v>-4.887079080934413</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.085959143800565</v>
+        <v>1.006800594026496</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.09874768169495135</v>
+        <v>-0.3707170683810787</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.902740041697038</v>
+        <v>2.739558409685361</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.46916190846223</v>
+        <v>-4.667058282897402</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.175546500025983</v>
+        <v>1.096387950251914</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.04247216337302889</v>
+        <v>-0.2294972233130984</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.98905098574844</v>
+        <v>2.825869353736764</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.336294219398952</v>
+        <v>-4.534190593834125</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.244587758453118</v>
+        <v>1.165429208679049</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.04247216337302889</v>
+        <v>-0.2294972233130984</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.004945168550263</v>
+        <v>2.841763536538587</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.216121136034453</v>
+        <v>-4.414017510469626</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.293802836239219</v>
+        <v>1.21464428646515</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1626452467375278</v>
+        <v>-0.1093241399485995</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.078194863009264</v>
+        <v>2.915013230997588</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.071448990934716</v>
+        <v>-4.269345365369889</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.361759796840554</v>
+        <v>1.282601247066485</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3073173918372653</v>
+        <v>0.03534800515113795</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.175086252630547</v>
+        <v>3.01190462061887</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.131323818292408</v>
+        <v>-4.329220192727581</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323847357298903</v>
+        <v>1.244688807524834</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2474425644795731</v>
+        <v>-0.02452682220655417</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.125198847617357</v>
+        <v>2.962017215605681</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.011503587381571</v>
+        <v>-4.209399961816744</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.387064618897446</v>
+        <v>1.307906069123377</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2474425644795731</v>
+        <v>-0.02452682220655417</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.140488016851566</v>
+        <v>2.97730638483989</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.013973293843377</v>
+        <v>-4.21186966827855</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.293720935635165</v>
+        <v>1.214562385861096</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.244972858017767</v>
+        <v>-0.02699652866836033</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.046650392296924</v>
+        <v>2.883468760285247</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.910673599960965</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.082343480167387</v>
+        <v>-4.28023985460256</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.277379783580263</v>
+        <v>1.198221233806194</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2542485570539819</v>
+        <v>-0.01772082963214539</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.063222734193355</v>
+        <v>2.900041102181679</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.901110308592857</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.096131533014434</v>
+        <v>-4.294027907449607</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.262301271073336</v>
+        <v>1.183142721299267</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2542485570539819</v>
+        <v>-0.01772082963214539</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.053659442825246</v>
+        <v>2.89047781081357</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.725819873633244</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.12712469234314</v>
+        <v>-4.325021066778312</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.074613572382241</v>
+        <v>0.9954550226081713</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2542485570539819</v>
+        <v>-0.01772082963214539</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.878369007865633</v>
+        <v>2.715187375853957</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.730387105625031</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.95165043255067</v>
+        <v>-4.149546806985843</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.149370508291016</v>
+        <v>1.070211958516947</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2542485570539819</v>
+        <v>-0.01772082963214539</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.882936239857421</v>
+        <v>2.719754607845744</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.706129134386238</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.062586685191919</v>
+        <v>-4.260483059627092</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.080738035995723</v>
+        <v>1.001579486221654</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2542485570539819</v>
+        <v>-0.01772082963214539</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.858678268618628</v>
+        <v>2.695496636606951</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.709260519606144</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.028923139719637</v>
+        <v>-4.226819514154809</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.097334839404542</v>
+        <v>1.018176289630473</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2879121025262638</v>
+        <v>0.01594271584013646</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.882007781121902</v>
+        <v>2.718826149110226</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.719432906038276</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.969070520515913</v>
+        <v>-4.166966894951086</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.131448273518164</v>
+        <v>1.052289723744094</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2879121025262638</v>
+        <v>0.01594271584013646</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.892180167554035</v>
+        <v>2.728998535542358</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.714379176612137</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.882827057489536</v>
+        <v>-4.080723431924708</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.160891929302575</v>
+        <v>1.081733379528506</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2879121025262638</v>
+        <v>0.01594271584013646</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.887126438127895</v>
+        <v>2.723944806116219</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.706154952056662</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.928133876888515</v>
+        <v>-4.126030251323688</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.134544976987509</v>
+        <v>1.05538642721344</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.247101939517033</v>
+        <v>-0.02486744716909434</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.854416115766882</v>
+        <v>2.691234483755206</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.706706825089764</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.957166981590817</v>
+        <v>-4.155063356025989</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.12348360813969</v>
+        <v>1.044325058365621</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.247101939517033</v>
+        <v>-0.02486744716909434</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.854967988799984</v>
+        <v>2.691786356788307</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.635979516981129</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.864356500139958</v>
+        <v>-4.06225287457513</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.089880492611399</v>
+        <v>1.01072194283733</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3399124209678923</v>
+        <v>0.06794303428176501</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.839926969561865</v>
+        <v>2.676745337550189</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.63785299290573</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.908745969469385</v>
+        <v>-4.106642343904557</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.073998180804229</v>
+        <v>0.9948396310301599</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2955229516384646</v>
+        <v>0.02355356495233735</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.815166763888809</v>
+        <v>2.651985131877133</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.632928701417453</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.796074751233135</v>
+        <v>-3.993971125668307</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.114142376610452</v>
+        <v>1.034983826836383</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4081941698747149</v>
+        <v>0.1362247831885876</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.877845203342282</v>
+        <v>2.714663571330606</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.653125773894754</v>
+        <v>-3.881594124485634</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.176813263376471</v>
+        <v>1.085425923140119</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4081941698747149</v>
+        <v>0.1362247831885876</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.88333649917295</v>
+        <v>2.720154867161273</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.680906171796107</v>
+        <v>-3.909374522386988</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.177198305984469</v>
+        <v>1.085810965748117</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3804137719733618</v>
+        <v>0.1084443852872345</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.878165462200677</v>
+        <v>2.714983830189</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.763907452821386</v>
+        <v>-3.992375803412266</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.982353513575011</v>
+        <v>0.8909661733386589</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.361842887446188</v>
+        <v>0.08987350076006073</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.705378651485026</v>
+        <v>2.542197019473349</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.872521531264717</v>
+        <v>-4.100989881855598</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.059057542916884</v>
+        <v>0.9676702026805319</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.361842887446188</v>
+        <v>0.08987350076006073</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.825528312204232</v>
+        <v>2.662346680192555</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.837112493016575</v>
+        <v>-4.065580843607455</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.087734184318464</v>
+        <v>0.9963468440821122</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.361842887446188</v>
+        <v>0.08987350076006073</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.840041338306555</v>
+        <v>2.676859706294878</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.798728830458423</v>
+        <v>-4.027197181049304</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.100507090684093</v>
+        <v>1.009119750447741</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4002265500043392</v>
+        <v>0.1282571633182119</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.860490977183814</v>
+        <v>2.697309345172137</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.621612500423257</v>
+        <v>-3.850080851014138</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.168082651543462</v>
+        <v>1.07669531130711</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4002265500043392</v>
+        <v>0.1282571633182119</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.857220006029116</v>
+        <v>2.69403837401744</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.666704745256803</v>
+        <v>-3.895173095847683</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.150729145371957</v>
+        <v>1.059341805135605</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3383305068349494</v>
+        <v>0.06636112014882212</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.820765771889395</v>
+        <v>2.657584139877719</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.487329324018035</v>
+        <v>-3.715797674608916</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.216266289173878</v>
+        <v>1.124878948937526</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.495107265005668</v>
+        <v>0.2231378783195408</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.908618802098241</v>
+        <v>2.745437170086565</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.532343537538642</v>
+        <v>-3.760811888129522</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.179068059097226</v>
+        <v>1.087680718860874</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4647583696910634</v>
+        <v>0.1927889830049362</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.871216920241068</v>
+        <v>2.708035288229392</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.799348047811077</v>
+        <v>-4.027816398401957</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.077957817327197</v>
+        <v>0.9865704770908452</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2703953316481149</v>
+        <v>-0.00157405503801239</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.760290659754244</v>
+        <v>2.597109027742568</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.90054582924825</v>
+        <v>-4.12901417983913</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.03668262664883</v>
+        <v>0.9452952864124775</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2019865181027957</v>
+        <v>-0.06998286858333158</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.718449293523554</v>
+        <v>2.555267661511878</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.894034862633937</v>
+        <v>-4.122503213224817</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.036886974848871</v>
+        <v>0.9454996346125193</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2019865181027957</v>
+        <v>-0.06998286858333158</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.716049255077871</v>
+        <v>2.552867623066195</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.87499673492664</v>
+        <v>-4.10346508551752</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.041026945140035</v>
+        <v>0.949639604903683</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1438029067716011</v>
+        <v>-0.1281664799145261</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.6776638074874</v>
+        <v>2.514482175475723</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.906123366077258</v>
+        <v>-4.134591716668139</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.206158161618469</v>
+        <v>1.114770821382116</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1438029067716011</v>
+        <v>-0.1281664799145261</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.85524567642608</v>
+        <v>2.692064044414404</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.919990127411175</v>
+        <v>-4.148458478002056</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.201444786071035</v>
+        <v>1.110057445834683</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1059449900377782</v>
+        <v>-0.1660243966483491</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.83336425537192</v>
+        <v>2.670182623360243</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.875185955871245</v>
+        <v>-4.103654306462126</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.225374985083933</v>
+        <v>1.133987644847581</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1059449900377782</v>
+        <v>-0.1660243966483491</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.839372785768846</v>
+        <v>2.676191153757169</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.727442985636243</v>
+        <v>-3.955911336227124</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.363624820969956</v>
+        <v>1.272237480733603</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2737523472726613</v>
+        <v>0.001782960586534099</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.019209847901797</v>
+        <v>2.856028215890121</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.829457668167464</v>
+        <v>-4.057926018758345</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.325612569488948</v>
+        <v>1.234225229252596</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2737523472726613</v>
+        <v>0.001782960586534099</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.022003469433278</v>
+        <v>2.858821837421602</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.82330496211468</v>
+        <v>-4.051773312705561</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.328736000301721</v>
+        <v>1.237348660065368</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2799050533254456</v>
+        <v>0.007935666639318384</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.026357441456607</v>
+        <v>2.863175809444931</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.840114260265181</v>
+        <v>-4.068582610856063</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.32109275778163</v>
+        <v>1.229705417545278</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.263095755174944</v>
+        <v>-0.008873631511183255</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.015352339306417</v>
+        <v>2.85217070729474</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.777816261489059</v>
+        <v>-4.006284612079941</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.4123475110889</v>
+        <v>1.320960170852547</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.263095755174944</v>
+        <v>-0.008873631511183255</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.081687893103238</v>
+        <v>2.918506261091561</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.576026063823901</v>
+        <v>-3.804494414414783</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.201644462544361</v>
+        <v>1.110257122308008</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4611139473440984</v>
+        <v>0.1891445606579711</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.909079680794128</v>
+        <v>2.745898048782452</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.502647966735165</v>
+        <v>-3.731116317326047</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.301285933702031</v>
+        <v>1.209898593465678</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5344920444328349</v>
+        <v>0.2625226577467077</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.023396771369546</v>
+        <v>2.860215139357869</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.600388511360139</v>
+        <v>-3.828856861951021</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.276817451968085</v>
+        <v>1.185430111731732</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5186027662998547</v>
+        <v>0.2466333796137275</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.028490940605801</v>
+        <v>2.865309308594124</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.776726271483068</v>
+        <v>-4.005194622073951</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.204818328743585</v>
+        <v>1.113430988507232</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3422650061769253</v>
+        <v>0.0702956194907981</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.921224265356715</v>
+        <v>2.758042633345039</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.700304225051142</v>
+        <v>-3.928772575642024</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.233878765356284</v>
+        <v>1.142491425119931</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3422650061769253</v>
+        <v>0.0702956194907981</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.919715883396643</v>
+        <v>2.756534251384967</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.655931093412573</v>
+        <v>-3.884399444003455</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.251490885447148</v>
+        <v>1.160103545210795</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3866381378154939</v>
+        <v>0.1146687511293667</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.946202629815221</v>
+        <v>2.783020997803544</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.533096872525406</v>
+        <v>-3.761565223116288</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.295018367940605</v>
+        <v>1.203631027704253</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3866381378154939</v>
+        <v>0.1146687511293667</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.940596423953811</v>
+        <v>2.777414791942135</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.48544114196435</v>
+        <v>-3.713909492555232</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.320462417192831</v>
+        <v>1.229075076956479</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4342938683765495</v>
+        <v>0.1623244816904224</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.975571619318249</v>
+        <v>2.812389987306573</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.384922983465596</v>
+        <v>-3.613391334056478</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.365562053967058</v>
+        <v>1.274174713730706</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.534812026875304</v>
+        <v>0.2628426401891769</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.040774887792226</v>
+        <v>2.87759325578055</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.445589573867985</v>
+        <v>-3.674057924458867</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.328050090281975</v>
+        <v>1.236662750045622</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4531137101567704</v>
+        <v>0.1811443234706432</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.978510570236979</v>
+        <v>2.815328938225302</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.400751172259587</v>
+        <v>-3.629219522850469</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.350083153535963</v>
+        <v>1.25869581329961</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4576571431016399</v>
+        <v>0.1856877564155127</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.985334332614529</v>
+        <v>2.822152700602853</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.501509808016585</v>
+        <v>-3.729978158607467</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.313940638864241</v>
+        <v>1.222553298627889</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3688315743746344</v>
+        <v>0.0968621876885073</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.936199931009404</v>
+        <v>2.773018298997727</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.457306970930685</v>
+        <v>-3.600526521266284</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.337501376226438</v>
+        <v>1.280213556092199</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4130344114605349</v>
+        <v>0.2263138250296908</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.968601235788781</v>
+        <v>2.856568883930275</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.494285998594128</v>
+        <v>-3.637505548929727</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.321119765630309</v>
+        <v>1.26383194549607</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4500083132518654</v>
+        <v>0.2632877268210213</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.989195577332826</v>
+        <v>2.87716322547432</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.514344077458968</v>
+        <v>-3.657563627794567</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.364344299267412</v>
+        <v>1.307056479133173</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4500083132518654</v>
+        <v>0.2632877268210213</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.040443342515866</v>
+        <v>2.92841099065736</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.474413404281078</v>
+        <v>-3.617632954616677</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.378757273132822</v>
+        <v>1.321469452998582</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.4899389864297558</v>
+        <v>0.3032183999989116</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.062842451016854</v>
+        <v>2.950810099158347</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.42338131155855</v>
+        <v>-3.566600861894149</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.394118338460103</v>
+        <v>1.336830518325864</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.5409710791522837</v>
+        <v>0.3542504927214396</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.088409934888641</v>
+        <v>2.976377583030134</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.358157130431344</v>
+        <v>-3.501376680766943</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.43739541500369</v>
+        <v>1.380107594869451</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.6061952602794893</v>
+        <v>0.4194746738486452</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.144731847657669</v>
+        <v>3.032699495799162</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.32073011036021</v>
+        <v>-3.463949660695809</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.448327195331424</v>
+        <v>1.391039375197185</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.611446798308671</v>
+        <v>0.4247262118778269</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.143843742774458</v>
+        <v>3.031811390915952</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.340841766394919</v>
+        <v>-3.484061316730517</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.441539325248781</v>
+        <v>1.384251505114542</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.6224741433060902</v>
+        <v>0.4357535568752461</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.15171694210415</v>
+        <v>3.039684590245644</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.287096951967714</v>
+        <v>-3.430316502303313</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.623595022040873</v>
+        <v>1.566307201906634</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.6325374527465522</v>
+        <v>0.445816866315708</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.318312698789638</v>
+        <v>3.206280346931131</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.263305383361572</v>
+        <v>-3.40652493369717</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.753224558701148</v>
+        <v>1.695936738566909</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.6563290213526944</v>
+        <v>0.4696084349218503</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.452700549171141</v>
+        <v>3.340668197312634</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.237221299097764</v>
+        <v>-3.380440849433362</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.75536616842053</v>
+        <v>1.698078348286291</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.6563290213526944</v>
+        <v>0.4696084349218503</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.444408525185</v>
+        <v>3.332376173326493</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.159090118248817</v>
+        <v>-3.302309668584416</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.784811836343888</v>
+        <v>1.727524016209649</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.730505832236379</v>
+        <v>0.5437852458055349</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.48710780729899</v>
+        <v>3.375075455440483</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.150197656855534</v>
+        <v>-3.293417207191133</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.805923226627993</v>
+        <v>1.748635406493753</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.730505832236379</v>
+        <v>0.5437852458055349</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.504662213025781</v>
+        <v>3.392629861167275</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.318673773825412</v>
+        <v>-3.46189332416101</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.730387827244625</v>
+        <v>1.673100007110386</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.7025579965197982</v>
+        <v>0.5158374100889541</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.479748559000416</v>
+        <v>3.36771620714191</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.620874244963828</v>
+        <v>-2.764093795299427</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.99077733597712</v>
+        <v>1.933489515842882</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.6322099371493874</v>
+        <v>0.4454893507185434</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.418809420566032</v>
+        <v>3.306777068707525</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.598153141280676</v>
+        <v>-2.741372691616275</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.990529799947286</v>
+        <v>1.933241979813047</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.6322099371493874</v>
+        <v>0.4454893507185434</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.409473443062936</v>
+        <v>3.29744109120443</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.596428097990632</v>
+        <v>-2.739647648326231</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.150125943114473</v>
+        <v>2.092838122980234</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6339349804394312</v>
+        <v>0.4472143940085871</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.569414594888132</v>
+        <v>3.457382243029625</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.751209104768887</v>
+        <v>-2.894428655104486</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.125291362896817</v>
+        <v>2.068003542762578</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.600567306384955</v>
+        <v>0.413846719954111</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.586471812949092</v>
+        <v>3.474439461090586</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.699773771384228</v>
+        <v>-2.842993321719826</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.142540852240226</v>
+        <v>2.085253032105987</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6520026397696147</v>
+        <v>0.4652820533387707</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.614008368969434</v>
+        <v>3.501976017110927</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.67282254705774</v>
+        <v>-2.816042097393338</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.163327495615563</v>
+        <v>2.106039675481324</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6668829857973338</v>
+        <v>0.4801623993664899</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.632942730230806</v>
+        <v>3.5209103783723</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.808775555114056</v>
+        <v>-2.951995105449654</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.293049424537996</v>
+        <v>2.235761604403757</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6668829857973338</v>
+        <v>0.4801623993664899</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.817045862375767</v>
+        <v>3.70501351051726</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.831183672918928</v>
+        <v>-2.974403223254527</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.276202872319041</v>
+        <v>2.218915052184801</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6668829857973338</v>
+        <v>0.4801623993664899</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.80916255727876</v>
+        <v>3.697130205420253</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.979189440398327</v>
+        <v>-3.122408990733926</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.219054564876918</v>
+        <v>2.161766744742679</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5801559769337924</v>
+        <v>0.3934353905029484</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.759180351510272</v>
+        <v>3.647147999651766</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.988630366286857</v>
+        <v>-3.131849916622456</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.271531912243353</v>
+        <v>2.214244092109114</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7025830944771838</v>
+        <v>0.5158625080463398</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.888890339758154</v>
+        <v>3.776857987899648</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.987343602747301</v>
+        <v>-3.1305631530829</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.274937712204477</v>
+        <v>2.217649892070238</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7038698580167404</v>
+        <v>0.5171492715858964</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.892553492427189</v>
+        <v>3.780521140568682</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.988900656736592</v>
+        <v>-3.132120207072191</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.272426703502536</v>
+        <v>2.215138883368296</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7038698580167404</v>
+        <v>0.5171492715858964</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.890665305320964</v>
+        <v>3.778632953462457</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.996172542260057</v>
+        <v>-3.139392092595656</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.264338178896012</v>
+        <v>2.207050358761773</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6965979724932756</v>
+        <v>0.5098773860624317</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.881122403609747</v>
+        <v>3.769090051751241</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.994331523201806</v>
+        <v>-3.137551073537404</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.263508596729465</v>
+        <v>2.206220776595226</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.697866199164744</v>
+        <v>0.5111456127339001</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.880317349822781</v>
+        <v>3.768284997964274</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.001240228701486</v>
+        <v>-3.144459779037085</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.273818521395511</v>
+        <v>2.216530701261272</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.697866199164744</v>
+        <v>0.5111456127339001</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.893390756688699</v>
+        <v>3.781358404830193</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.002801871516346</v>
+        <v>-3.146021421851945</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.273193864269567</v>
+        <v>2.215906044135328</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.697866199164744</v>
+        <v>0.5111456127339001</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.893390756688699</v>
+        <v>3.781358404830193</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.030702658625819</v>
+        <v>-3.173922208961418</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.26055759055278</v>
+        <v>2.203269770418541</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6632692750218092</v>
+        <v>0.4765486885909653</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.87115664332994</v>
+        <v>3.759124291471434</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.033735656138493</v>
+        <v>-3.176955206474092</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.256108835524909</v>
+        <v>2.19882101539067</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6602362775091353</v>
+        <v>0.4735156910782914</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.866101288799535</v>
+        <v>3.754068936941029</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.053796977415</v>
+        <v>-3.197016527750598</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.31479026660481</v>
+        <v>2.257502446470571</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6401749562326282</v>
+        <v>0.4534543698017844</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.920770455624135</v>
+        <v>3.808738103765628</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,45 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.900969397761619</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.215750947545854</v>
+        <v>-3.330122025930236</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.390320397554316</v>
+        <v>2.344571966200563</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6963897928771982</v>
+        <v>0.3998262844676936</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.094811076612723</v>
+        <v>3.91687297156702</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="2" t="n">
+        <v>45479</v>
+      </c>
+      <c r="B2017" t="n">
+        <v>3.73627658564216</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>3.727702399782926</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>-3.330122025930236</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>2.344571966200563</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>0.3998262844676936</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>3.720766196769294</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-494.6%</t>
+          <t>-508.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.8%</t>
+          <t>-147.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-267.5%</t>
+          <t>-121.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-184.0%</t>
+          <t>-188.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-67.5%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.208096370408748</v>
+        <v>-6.361640090146381</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4804663906264164</v>
+        <v>0.4190489027313631</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.9758555951826148</v>
+        <v>-1.055326302669293</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.378548005994094</v>
+        <v>2.330865581502088</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.958245976459673</v>
+        <v>-6.111789696197306</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5731486231897485</v>
+        <v>0.5117311352946952</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.9758555951826148</v>
+        <v>-1.055326302669293</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.371290080977796</v>
+        <v>2.32360765648579</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.78235388399224</v>
+        <v>-5.935897603729874</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6471045836973706</v>
+        <v>0.5856870958023168</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.9758555951826148</v>
+        <v>-1.055326302669293</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.374889204498445</v>
+        <v>2.327206780006438</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.610907420969776</v>
+        <v>-5.76445114070741</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7290106749609095</v>
+        <v>0.6675931870658558</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8044091321601516</v>
+        <v>-0.8838798396468294</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.491084588366477</v>
+        <v>2.44340216387447</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.536617855231437</v>
+        <v>-5.690161574969071</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7577469788725422</v>
+        <v>0.6963294909774884</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7301195664218123</v>
+        <v>-0.8095902739084901</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534678805425777</v>
+        <v>2.48699638093377</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.472982112997503</v>
+        <v>-5.626525832735137</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7878960768204331</v>
+        <v>0.7264785889253798</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6664838241878778</v>
+        <v>-0.7459545316745556</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.577555051820455</v>
+        <v>2.529872627328448</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.361555353671583</v>
+        <v>-5.515099073409217</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8136610393345967</v>
+        <v>0.7522435514395434</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6664838241878778</v>
+        <v>-0.7459545316745556</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558749310604251</v>
+        <v>2.511066886112244</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.121124856866722</v>
+        <v>-5.274668576604356</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9115763146814184</v>
+        <v>0.8501588267863647</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4260533273830175</v>
+        <v>-0.5055240348696953</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704750685312044</v>
+        <v>2.657068260820038</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.048882288695528</v>
+        <v>-5.202426008433162</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9444026557847165</v>
+        <v>0.8829851678896627</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4260533273830175</v>
+        <v>-0.5055240348696953</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708679999146864</v>
+        <v>2.660997574654858</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.99588396641414</v>
+        <v>-5.149427686151774</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9662805686146116</v>
+        <v>0.9048630807195579</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3707170683810787</v>
+        <v>-0.4501877758677565</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.742560338465368</v>
+        <v>2.694877913973361</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.887079080934413</v>
+        <v>-5.040622800672047</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.006800594026496</v>
+        <v>0.9453831061314424</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3707170683810787</v>
+        <v>-0.4501877758677565</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.739558409685361</v>
+        <v>2.691875985193355</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.667058282897402</v>
+        <v>-4.820602002635036</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.096387950251914</v>
+        <v>1.034970462356861</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2294972233130984</v>
+        <v>-0.3089679307997762</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.825869353736764</v>
+        <v>2.778186929244757</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.534190593834125</v>
+        <v>-4.687734313571759</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.165429208679049</v>
+        <v>1.104011720783995</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2294972233130984</v>
+        <v>-0.3089679307997762</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.841763536538587</v>
+        <v>2.79408111204658</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.414017510469626</v>
+        <v>-4.56756123020726</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21464428646515</v>
+        <v>1.153226798570096</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1093241399485995</v>
+        <v>-0.1887948474352773</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.915013230997588</v>
+        <v>2.867330806505581</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.269345365369889</v>
+        <v>-4.422889085107522</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282601247066485</v>
+        <v>1.221183759171431</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.03534800515113795</v>
+        <v>-0.04412270233553989</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.01190462061887</v>
+        <v>2.964222196126864</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.329220192727581</v>
+        <v>-4.482763912465215</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.244688807524834</v>
+        <v>1.18327131962978</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.02452682220655417</v>
+        <v>-0.103997529693232</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.962017215605681</v>
+        <v>2.914334791113674</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.209399961816744</v>
+        <v>-4.362943681554378</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307906069123377</v>
+        <v>1.246488581228324</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.02452682220655417</v>
+        <v>-0.103997529693232</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.97730638483989</v>
+        <v>2.929623960347883</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.21186966827855</v>
+        <v>-4.365413388016184</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214562385861096</v>
+        <v>1.153144897966043</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.02699652866836033</v>
+        <v>-0.1064672361550382</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.883468760285247</v>
+        <v>2.835786335793241</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.910673599960965</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.28023985460256</v>
+        <v>-4.433783574340194</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198221233806194</v>
+        <v>1.13680374591114</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.01772082963214539</v>
+        <v>-0.09719153711882322</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.900041102181679</v>
+        <v>2.852358677689672</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.901110308592857</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.294027907449607</v>
+        <v>-4.447571627187241</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.183142721299267</v>
+        <v>1.121725233404213</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.01772082963214539</v>
+        <v>-0.09719153711882322</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.89047781081357</v>
+        <v>2.842795386321563</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.725819873633244</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.325021066778312</v>
+        <v>-4.478564786515946</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9954550226081713</v>
+        <v>0.9340375347131178</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.01772082963214539</v>
+        <v>-0.09719153711882322</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.715187375853957</v>
+        <v>2.66750495136195</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.730387105625031</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.149546806985843</v>
+        <v>-4.303090526723476</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.070211958516947</v>
+        <v>1.008794470621893</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.01772082963214539</v>
+        <v>-0.09719153711882322</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.719754607845744</v>
+        <v>2.672072183353738</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.706129134386238</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.260483059627092</v>
+        <v>-4.414026779364725</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.001579486221654</v>
+        <v>0.940161998326601</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.01772082963214539</v>
+        <v>-0.09719153711882322</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.695496636606951</v>
+        <v>2.647814212114945</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.709260519606144</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.226819514154809</v>
+        <v>-4.380363233892443</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.018176289630473</v>
+        <v>0.9567588017354194</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.01594271584013646</v>
+        <v>-0.06352799164654138</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.718826149110226</v>
+        <v>2.671143724618219</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.719432906038276</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.166966894951086</v>
+        <v>-4.32051061468872</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.052289723744094</v>
+        <v>0.9908722358490409</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.01594271584013646</v>
+        <v>-0.06352799164654138</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.728998535542358</v>
+        <v>2.681316111050352</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.714379176612137</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.080723431924708</v>
+        <v>-4.234267151662342</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.081733379528506</v>
+        <v>1.020315891633452</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.01594271584013646</v>
+        <v>-0.06352799164654138</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.723944806116219</v>
+        <v>2.676262381624212</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.706154952056662</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.126030251323688</v>
+        <v>-4.279573971061322</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.05538642721344</v>
+        <v>0.9939689393183859</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.02486744716909434</v>
+        <v>-0.1043381546557722</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.691234483755206</v>
+        <v>2.643552059263199</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.706706825089764</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.155063356025989</v>
+        <v>-4.308607075763623</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.044325058365621</v>
+        <v>0.9829075704705672</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.02486744716909434</v>
+        <v>-0.1043381546557722</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.691786356788307</v>
+        <v>2.6441039322963</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.635979516981129</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.06225287457513</v>
+        <v>-4.215796594312764</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.01072194283733</v>
+        <v>0.9493044549422767</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.06794303428176501</v>
+        <v>-0.01152767320491282</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.676745337550189</v>
+        <v>2.629062913058182</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.63785299290573</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.106642343904557</v>
+        <v>-4.260186063642191</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9948396310301599</v>
+        <v>0.9334221431351064</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.02355356495233735</v>
+        <v>-0.05591714253434049</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.651985131877133</v>
+        <v>2.604302707385126</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.632928701417453</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.993971125668307</v>
+        <v>-4.147514845405941</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.034983826836383</v>
+        <v>0.9735663389413296</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1362247831885876</v>
+        <v>0.05675407570190971</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.714663571330606</v>
+        <v>2.666981146838599</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.881594124485634</v>
+        <v>-4.035137844223268</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.085425923140119</v>
+        <v>1.024008435245066</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1362247831885876</v>
+        <v>0.05675407570190971</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.720154867161273</v>
+        <v>2.672472442669267</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.909374522386988</v>
+        <v>-4.062918242124621</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.085810965748117</v>
+        <v>1.024393477853064</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.1084443852872345</v>
+        <v>0.02897367780055665</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.714983830189</v>
+        <v>2.667301405696994</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.992375803412266</v>
+        <v>-4.1459195231499</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8909661733386589</v>
+        <v>0.8295486854436056</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.08987350076006073</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.542197019473349</v>
+        <v>2.494514594981343</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.100989881855598</v>
+        <v>-4.254533601593231</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9676702026805319</v>
+        <v>0.9062527147854789</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.08987350076006073</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.662346680192555</v>
+        <v>2.614664255700548</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.065580843607455</v>
+        <v>-4.219124563345088</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9963468440821122</v>
+        <v>0.9349293561870589</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.08987350076006073</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.676859706294878</v>
+        <v>2.629177281802871</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.027197181049304</v>
+        <v>-4.180740900786937</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.009119750447741</v>
+        <v>0.9477022625526881</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.1282571633182119</v>
+        <v>0.04878645583153407</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.697309345172137</v>
+        <v>2.649626920680131</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.850080851014138</v>
+        <v>-4.003624570751771</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.07669531130711</v>
+        <v>1.015277823412057</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.1282571633182119</v>
+        <v>0.04878645583153407</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.69403837401744</v>
+        <v>2.646355949525433</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.895173095847683</v>
+        <v>-4.048716815585316</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.059341805135605</v>
+        <v>0.9979243172405516</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.06636112014882212</v>
+        <v>-0.01310958733785572</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.657584139877719</v>
+        <v>2.609901715385712</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.715797674608916</v>
+        <v>-3.869341394346549</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.124878948937526</v>
+        <v>1.063461461042473</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.2231378783195408</v>
+        <v>0.143667170832863</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.745437170086565</v>
+        <v>2.697754745594558</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.760811888129522</v>
+        <v>-3.914355607867155</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.087680718860874</v>
+        <v>1.02626323096582</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1927889830049362</v>
+        <v>0.1133182755182583</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.708035288229392</v>
+        <v>2.660352863737385</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.027816398401957</v>
+        <v>-4.18136011813959</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9865704770908452</v>
+        <v>0.9251529891957919</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.00157405503801239</v>
+        <v>-0.08104476252469023</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.597109027742568</v>
+        <v>2.549426603250561</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12901417983913</v>
+        <v>-4.282557899576763</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9452952864124775</v>
+        <v>0.8838777985174242</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.06998286858333158</v>
+        <v>-0.1494535760700094</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.555267661511878</v>
+        <v>2.507585237019871</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.122503213224817</v>
+        <v>-4.27604693296245</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9454996346125193</v>
+        <v>0.884082146717466</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.06998286858333158</v>
+        <v>-0.1494535760700094</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.552867623066195</v>
+        <v>2.505185198574188</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.10346508551752</v>
+        <v>-4.257008805255153</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.949639604903683</v>
+        <v>0.88822211700863</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.1281664799145261</v>
+        <v>-0.207637187401204</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.514482175475723</v>
+        <v>2.466799750983717</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.134591716668139</v>
+        <v>-4.288135436405772</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.114770821382116</v>
+        <v>1.053353333487063</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.1281664799145261</v>
+        <v>-0.207637187401204</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.692064044414404</v>
+        <v>2.644381619922397</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.148458478002056</v>
+        <v>-4.206776694201717</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.110057445834683</v>
+        <v>1.086730159354818</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.1660243966483491</v>
+        <v>-0.1262784451971496</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.670182623360243</v>
+        <v>2.694030194230963</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.103654306462126</v>
+        <v>-4.161972522661787</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.133987644847581</v>
+        <v>1.110660358367716</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.1660243966483491</v>
+        <v>-0.1262784451971496</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.676191153757169</v>
+        <v>2.700038724627889</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.955911336227124</v>
+        <v>-4.014229552426785</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.272237480733603</v>
+        <v>1.248910194253739</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.001782960586534099</v>
+        <v>0.04152891203773357</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.856028215890121</v>
+        <v>2.879875786760841</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.057926018758345</v>
+        <v>-4.116244234958006</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.234225229252596</v>
+        <v>1.210897942772732</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.001782960586534099</v>
+        <v>0.04152891203773357</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.858821837421602</v>
+        <v>2.882669408292322</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.051773312705561</v>
+        <v>-4.110091528905222</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.237348660065368</v>
+        <v>1.214021373585504</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.007935666639318384</v>
+        <v>0.04768161809051785</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.863175809444931</v>
+        <v>2.887023380315651</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.068582610856063</v>
+        <v>-4.126900827055723</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.229705417545278</v>
+        <v>1.206378131065413</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.008873631511183255</v>
+        <v>0.03087231994001621</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85217070729474</v>
+        <v>2.87601827816546</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.006284612079941</v>
+        <v>-4.064602828279601</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.320960170852547</v>
+        <v>1.297632884372683</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.008873631511183255</v>
+        <v>0.03087231994001621</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.918506261091561</v>
+        <v>2.942353831962281</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.804494414414783</v>
+        <v>-3.862812630614443</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.110257122308008</v>
+        <v>1.086929835828144</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1891445606579711</v>
+        <v>0.2288905121091706</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.745898048782452</v>
+        <v>2.769745619653171</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.731116317326047</v>
+        <v>-3.789434533525707</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.209898593465678</v>
+        <v>1.186571306985814</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2625226577467077</v>
+        <v>0.3022686091979072</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.860215139357869</v>
+        <v>2.884062710228589</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.828856861951021</v>
+        <v>-3.887175078150681</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.185430111731732</v>
+        <v>1.162102825251868</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2466333796137275</v>
+        <v>0.286379331064927</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.865309308594124</v>
+        <v>2.889156879464844</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.005194622073951</v>
+        <v>-4.063512838273611</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.113430988507232</v>
+        <v>1.090103702027368</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.0702956194907981</v>
+        <v>0.1100415709419976</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.758042633345039</v>
+        <v>2.781890204215758</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.928772575642024</v>
+        <v>-3.987090791841684</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.142491425119931</v>
+        <v>1.119164138640067</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.0702956194907981</v>
+        <v>0.1100415709419976</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.756534251384967</v>
+        <v>2.780381822255687</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.884399444003455</v>
+        <v>-3.942717660203115</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.160103545210795</v>
+        <v>1.136776258730931</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.1146687511293667</v>
+        <v>0.1544147025805662</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.783020997803544</v>
+        <v>2.806868568674264</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.761565223116288</v>
+        <v>-3.819883439315948</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.203631027704253</v>
+        <v>1.180303741224388</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.1146687511293667</v>
+        <v>0.1544147025805662</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.777414791942135</v>
+        <v>2.801262362812855</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.713909492555232</v>
+        <v>-3.772227708754892</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.229075076956479</v>
+        <v>1.205747790476615</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.1623244816904224</v>
+        <v>0.2020704331416218</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.812389987306573</v>
+        <v>2.836237558177292</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.613391334056478</v>
+        <v>-3.671709550256137</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.274174713730706</v>
+        <v>1.250847427250841</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.2628426401891769</v>
+        <v>0.3025885916403764</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.87759325578055</v>
+        <v>2.90144082665127</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.674057924458867</v>
+        <v>-3.732376140658527</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.236662750045622</v>
+        <v>1.213335463565758</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1811443234706432</v>
+        <v>0.2208902749218427</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.815328938225302</v>
+        <v>2.839176509096022</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.629219522850469</v>
+        <v>-3.687537739050128</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.25869581329961</v>
+        <v>1.235368526819746</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1856877564155127</v>
+        <v>0.2254337078667122</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.822152700602853</v>
+        <v>2.846000271473572</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.729978158607467</v>
+        <v>-3.788296374807127</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.222553298627889</v>
+        <v>1.199226012148024</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.0968621876885073</v>
+        <v>0.1366081391397068</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.773018298997727</v>
+        <v>2.796865869868447</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.600526521266284</v>
+        <v>-3.744093537721227</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.280213556092199</v>
+        <v>1.222786749510222</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2263138250296908</v>
+        <v>0.1808109762256072</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.856568883930275</v>
+        <v>2.829267174647824</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.637505548929727</v>
+        <v>-3.78107256538467</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.26383194549607</v>
+        <v>1.206405138914092</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.2632877268210213</v>
+        <v>0.2177848780169377</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.87716322547432</v>
+        <v>2.84986151619187</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.657563627794567</v>
+        <v>-3.80113064424951</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.307056479133173</v>
+        <v>1.249629672551196</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.2632877268210213</v>
+        <v>0.2177848780169377</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.92841099065736</v>
+        <v>2.90110928137491</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.617632954616677</v>
+        <v>-3.76119997107162</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.321469452998582</v>
+        <v>1.264042646416605</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.3032183999989116</v>
+        <v>0.2577155511948281</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.950810099158347</v>
+        <v>2.923508389875897</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.566600861894149</v>
+        <v>-3.710167878349091</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.336830518325864</v>
+        <v>1.279403711743886</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.3542504927214396</v>
+        <v>0.308747643917356</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.976377583030134</v>
+        <v>2.949075873747684</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.501376680766943</v>
+        <v>-3.644943697221886</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.380107594869451</v>
+        <v>1.322680788287473</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4194746738486452</v>
+        <v>0.3739718250445617</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.032699495799162</v>
+        <v>3.005397786516712</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.463949660695809</v>
+        <v>-3.607516677150752</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.391039375197185</v>
+        <v>1.333612568615207</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4247262118778269</v>
+        <v>0.3792233630737433</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.031811390915952</v>
+        <v>3.004509681633502</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.484061316730517</v>
+        <v>-3.627628333185461</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.384251505114542</v>
+        <v>1.326824698532564</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.4357535568752461</v>
+        <v>0.3902507080711625</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.039684590245644</v>
+        <v>3.012382880963194</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.430316502303313</v>
+        <v>-3.573883518758256</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.566307201906634</v>
+        <v>1.508880395324657</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.445816866315708</v>
+        <v>0.4003140175116245</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.206280346931131</v>
+        <v>3.178978637648681</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.40652493369717</v>
+        <v>-3.550091950152114</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.695936738566909</v>
+        <v>1.638509931984931</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.4696084349218503</v>
+        <v>0.4241055861177668</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340668197312634</v>
+        <v>3.313366488030184</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.380440849433362</v>
+        <v>-3.524007865888306</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.698078348286291</v>
+        <v>1.640651541704313</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.4696084349218503</v>
+        <v>0.4241055861177668</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.332376173326493</v>
+        <v>3.305074464044043</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.302309668584416</v>
+        <v>-3.445876685039359</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.727524016209649</v>
+        <v>1.670097209627671</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5437852458055349</v>
+        <v>0.4982823970014514</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.375075455440483</v>
+        <v>3.347773746158033</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.293417207191133</v>
+        <v>-3.436984223646076</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.748635406493753</v>
+        <v>1.691208599911776</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5437852458055349</v>
+        <v>0.4982823970014514</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.392629861167275</v>
+        <v>3.365328151884825</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.46189332416101</v>
+        <v>-3.605460340615954</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.673100007110386</v>
+        <v>1.615673200528409</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5158374100889541</v>
+        <v>0.4703345612848706</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.36771620714191</v>
+        <v>3.34041449785946</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.764093795299427</v>
+        <v>-2.90766081175437</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.933489515842882</v>
+        <v>1.876062709260904</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.4454893507185434</v>
+        <v>0.3999865019144599</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.306777068707525</v>
+        <v>3.279475359425075</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.741372691616275</v>
+        <v>-2.884939708071218</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.933241979813047</v>
+        <v>1.875815173231069</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.4454893507185434</v>
+        <v>0.3999865019144599</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.29744109120443</v>
+        <v>3.27013938192198</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.739647648326231</v>
+        <v>-2.883214664781174</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.092838122980234</v>
+        <v>2.035411316398256</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.4472143940085871</v>
+        <v>0.4017115452045036</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.457382243029625</v>
+        <v>3.430080533747175</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.894428655104486</v>
+        <v>-3.037995671559429</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.068003542762578</v>
+        <v>2.0105767361806</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.413846719954111</v>
+        <v>0.3683438711500275</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.474439461090586</v>
+        <v>3.447137751808136</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.842993321719826</v>
+        <v>-2.986560338174769</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.085253032105987</v>
+        <v>2.027826225524009</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.4652820533387707</v>
+        <v>0.4197792045346872</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.501976017110927</v>
+        <v>3.474674307828477</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.816042097393338</v>
+        <v>-2.959609113848281</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.106039675481324</v>
+        <v>2.048612868899347</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.4801623993664899</v>
+        <v>0.4346595505624063</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.5209103783723</v>
+        <v>3.49360866908985</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.951995105449654</v>
+        <v>-3.095562121904598</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.235761604403757</v>
+        <v>2.17833479782178</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.4801623993664899</v>
+        <v>0.4346595505624063</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.70501351051726</v>
+        <v>3.67771180123481</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.974403223254527</v>
+        <v>-3.11797023970947</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.218915052184801</v>
+        <v>2.161488245602824</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.4801623993664899</v>
+        <v>0.4346595505624063</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.697130205420253</v>
+        <v>3.669828496137803</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.122408990733926</v>
+        <v>-3.265976007188869</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.161766744742679</v>
+        <v>2.104339938160702</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.3934353905029484</v>
+        <v>0.3479325416988649</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.647147999651766</v>
+        <v>3.619846290369316</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.131849916622456</v>
+        <v>-3.275416933077399</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.214244092109114</v>
+        <v>2.156817285527136</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5158625080463398</v>
+        <v>0.4703596592422563</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.776857987899648</v>
+        <v>3.749556278617197</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.1305631530829</v>
+        <v>-3.274130169537843</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.217649892070238</v>
+        <v>2.16022308548826</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5171492715858964</v>
+        <v>0.4716464227818129</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.780521140568682</v>
+        <v>3.753219431286233</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.132120207072191</v>
+        <v>-3.275687223527134</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.215138883368296</v>
+        <v>2.157712076786319</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5171492715858964</v>
+        <v>0.4716464227818129</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.778632953462457</v>
+        <v>3.751331244180008</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.139392092595656</v>
+        <v>-3.282959109050599</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.207050358761773</v>
+        <v>2.149623552179795</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5098773860624317</v>
+        <v>0.4643745372583482</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.769090051751241</v>
+        <v>3.741788342468791</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.137551073537404</v>
+        <v>-3.281118089992348</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.206220776595226</v>
+        <v>2.148793970013248</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5111456127339001</v>
+        <v>0.4656427639298166</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.768284997964274</v>
+        <v>3.740983288681824</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.144459779037085</v>
+        <v>-3.288026795492028</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.216530701261272</v>
+        <v>2.159103894679294</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5111456127339001</v>
+        <v>0.4656427639298166</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.781358404830193</v>
+        <v>3.754056695547743</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.146021421851945</v>
+        <v>-3.289588438306888</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.215906044135328</v>
+        <v>2.15847923755335</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5111456127339001</v>
+        <v>0.4656427639298166</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.781358404830193</v>
+        <v>3.754056695547743</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.173922208961418</v>
+        <v>-3.317489225416361</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.203269770418541</v>
+        <v>2.145842963836563</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4765486885909653</v>
+        <v>0.4310458397868818</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.759124291471434</v>
+        <v>3.731822582188984</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.176955206474092</v>
+        <v>-3.320522222929035</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.19882101539067</v>
+        <v>2.141394208808692</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4735156910782914</v>
+        <v>0.4280128422742079</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.754068936941029</v>
+        <v>3.726767227658578</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.197016527750598</v>
+        <v>-3.340583544205542</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.257502446470571</v>
+        <v>2.200075639888594</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4534543698017844</v>
+        <v>0.4079515209977009</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.808738103765628</v>
+        <v>3.781436394483178</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.330122025930236</v>
+        <v>-3.47368904238518</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.344571966200563</v>
+        <v>2.287145159618585</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3998262844676936</v>
+        <v>0.35432343566361</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.91687297156702</v>
+        <v>3.889571262284571</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.73627658564216</v>
+        <v>3.811549600226988</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.727702399782926</v>
+        <v>3.792349827964879</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.330122025930236</v>
+        <v>-3.47368904238518</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.344571966200563</v>
+        <v>2.287145159618585</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3998262844676936</v>
+        <v>0.35432343566361</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.720766196769294</v>
+        <v>3.785413624951246</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-508.9%</t>
+          <t>-505.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-146.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.6%</t>
+          <t>-225.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-188.6%</t>
+          <t>-192.9%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.206776694201717</v>
+        <v>-4.176646056079591</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.086730159354818</v>
+        <v>1.098782414603669</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.1262784451971496</v>
+        <v>-0.1693877506727122</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.694030194230963</v>
+        <v>2.668164610945626</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.161972522661787</v>
+        <v>-4.131841884539661</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.110660358367716</v>
+        <v>1.122712613616567</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.1262784451971496</v>
+        <v>-0.1693877506727122</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.700038724627889</v>
+        <v>2.674173141342552</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.014229552426785</v>
+        <v>-3.984098914304659</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.248910194253739</v>
+        <v>1.26096244950259</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.04152891203773357</v>
+        <v>-0.001580393437829009</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.879875786760841</v>
+        <v>2.854010203475503</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.116244234958006</v>
+        <v>-4.086113596835879</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.210897942772732</v>
+        <v>1.222950198021582</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.04152891203773357</v>
+        <v>-0.001580393437829009</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.882669408292322</v>
+        <v>2.856803825006984</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.110091528905222</v>
+        <v>-4.079960890783095</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.214021373585504</v>
+        <v>1.226073628834354</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.04768161809051785</v>
+        <v>0.004572312614955276</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.887023380315651</v>
+        <v>2.861157797030313</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.126900827055723</v>
+        <v>-4.096770188933597</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.206378131065413</v>
+        <v>1.218430386314264</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.03087231994001621</v>
+        <v>-0.01223698553554636</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.87601827816546</v>
+        <v>2.850152694880122</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.064602828279601</v>
+        <v>-4.034472190157475</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.297632884372683</v>
+        <v>1.309685139621534</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.03087231994001621</v>
+        <v>-0.01223698553554636</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.942353831962281</v>
+        <v>2.916488248676943</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.862812630614443</v>
+        <v>-3.832681992492317</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.086929835828144</v>
+        <v>1.098982091076995</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.2288905121091706</v>
+        <v>0.185781206633608</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.769745619653171</v>
+        <v>2.743880036367834</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.789434533525707</v>
+        <v>-3.75930389540358</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.186571306985814</v>
+        <v>1.198623562234665</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3022686091979072</v>
+        <v>0.2591593037223446</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.884062710228589</v>
+        <v>2.858197126943251</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.887175078150681</v>
+        <v>-3.857044440028555</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.162102825251868</v>
+        <v>1.174155080500719</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.286379331064927</v>
+        <v>0.2432700255893644</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.889156879464844</v>
+        <v>2.863291296179507</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.063512838273611</v>
+        <v>-4.033382200151484</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.090103702027368</v>
+        <v>1.102155957276219</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1100415709419976</v>
+        <v>0.06693226546643499</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.781890204215758</v>
+        <v>2.756024620930421</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.987090791841684</v>
+        <v>-3.956960153719558</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.119164138640067</v>
+        <v>1.131216393888918</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.1100415709419976</v>
+        <v>0.06693226546643499</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.780381822255687</v>
+        <v>2.754516238970349</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.942717660203115</v>
+        <v>-3.912587022080989</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.136776258730931</v>
+        <v>1.148828513979781</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.1544147025805662</v>
+        <v>0.1113053971050036</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.806868568674264</v>
+        <v>2.781002985388926</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.819883439315948</v>
+        <v>-3.789752801193822</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.180303741224388</v>
+        <v>1.192355996473239</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.1544147025805662</v>
+        <v>0.1113053971050036</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.801262362812855</v>
+        <v>2.775396779527517</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.772227708754892</v>
+        <v>-3.742097070632766</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.205747790476615</v>
+        <v>1.217800045725465</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.2020704331416218</v>
+        <v>0.1589611276660592</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.836237558177292</v>
+        <v>2.810371974891955</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.671709550256137</v>
+        <v>-3.641578912134011</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.250847427250841</v>
+        <v>1.262899682499692</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.3025885916403764</v>
+        <v>0.2594792861648138</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.90144082665127</v>
+        <v>2.875575243365932</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.732376140658527</v>
+        <v>-3.7022455025364</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.213335463565758</v>
+        <v>1.225387718814609</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.2208902749218427</v>
+        <v>0.1777809694462801</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.839176509096022</v>
+        <v>2.813310925810684</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.687537739050128</v>
+        <v>-3.657407100928002</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.235368526819746</v>
+        <v>1.247420782068597</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.2254337078667122</v>
+        <v>0.1823244023911496</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.846000271473572</v>
+        <v>2.820134688188235</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.788296374807127</v>
+        <v>-3.758165736685001</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.199226012148024</v>
+        <v>1.211278267396875</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.1366081391397068</v>
+        <v>0.09349883366414419</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.796865869868447</v>
+        <v>2.771000286583109</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.744093537721227</v>
+        <v>-3.7139628995991</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.222786749510222</v>
+        <v>1.234839004759072</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.1808109762256072</v>
+        <v>0.1377016707500446</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.829267174647824</v>
+        <v>2.803401591362487</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.78107256538467</v>
+        <v>-3.750941927262543</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.206405138914092</v>
+        <v>1.218457394162943</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.2177848780169377</v>
+        <v>0.1746755725413752</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84986151619187</v>
+        <v>2.823995932906533</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.80113064424951</v>
+        <v>-3.771000006127383</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.249629672551196</v>
+        <v>1.261681927800046</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.2177848780169377</v>
+        <v>0.1746755725413752</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.90110928137491</v>
+        <v>2.875243698089572</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.76119997107162</v>
+        <v>-3.731069332949493</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.264042646416605</v>
+        <v>1.276094901665455</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2577155511948281</v>
+        <v>0.2146062457192655</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923508389875897</v>
+        <v>2.89764280659056</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.710167878349091</v>
+        <v>-3.680037240226965</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.279403711743886</v>
+        <v>1.291455966992737</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.308747643917356</v>
+        <v>0.2656383384417935</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.949075873747684</v>
+        <v>2.923210290462346</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.644943697221886</v>
+        <v>-3.61481305909976</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.322680788287473</v>
+        <v>1.334733043536324</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3739718250445617</v>
+        <v>0.3308625195689991</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005397786516712</v>
+        <v>2.979532203231375</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.607516677150752</v>
+        <v>-3.577386039028626</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.333612568615207</v>
+        <v>1.345664823864058</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.3792233630737433</v>
+        <v>0.3361140575981807</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004509681633502</v>
+        <v>2.978644098348164</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.627628333185461</v>
+        <v>-3.597497695063334</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.326824698532564</v>
+        <v>1.338876953781415</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3902507080711625</v>
+        <v>0.3471414025955999</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.012382880963194</v>
+        <v>2.986517297677856</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.573883518758256</v>
+        <v>-3.543752880636129</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.508880395324657</v>
+        <v>1.520932650573507</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.4003140175116245</v>
+        <v>0.3572047120360619</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.178978637648681</v>
+        <v>3.153113054363344</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.550091950152114</v>
+        <v>-3.519961312029987</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.638509931984931</v>
+        <v>1.650562187233781</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.4241055861177668</v>
+        <v>0.3809962806422042</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.313366488030184</v>
+        <v>3.287500904744846</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.524007865888306</v>
+        <v>-3.493877227766179</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.640651541704313</v>
+        <v>1.652703796953164</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.4241055861177668</v>
+        <v>0.3809962806422042</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.305074464044043</v>
+        <v>3.279208880758705</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.445876685039359</v>
+        <v>-3.415746046917232</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.670097209627671</v>
+        <v>1.682149464876522</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.4982823970014514</v>
+        <v>0.4551730915258888</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.347773746158033</v>
+        <v>3.321908162872695</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.436984223646076</v>
+        <v>-3.406853585523949</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.691208599911776</v>
+        <v>1.703260855160627</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.4982823970014514</v>
+        <v>0.4551730915258888</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.365328151884825</v>
+        <v>3.339462568599487</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.605460340615954</v>
+        <v>-3.575329702493827</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.615673200528409</v>
+        <v>1.627725455777259</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.4703345612848706</v>
+        <v>0.427225255809308</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.34041449785946</v>
+        <v>3.314548914574122</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.90766081175437</v>
+        <v>-2.877530173632244</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.876062709260904</v>
+        <v>1.888114964509754</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.3999865019144599</v>
+        <v>0.3568771964388973</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.279475359425075</v>
+        <v>3.253609776139738</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.884939708071218</v>
+        <v>-2.854809069949091</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.875815173231069</v>
+        <v>1.88786742847992</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.3999865019144599</v>
+        <v>0.3568771964388973</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.27013938192198</v>
+        <v>3.244273798636642</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.883214664781174</v>
+        <v>-2.853084026659047</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.035411316398256</v>
+        <v>2.047463571647107</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.4017115452045036</v>
+        <v>0.358602239728941</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.430080533747175</v>
+        <v>3.404214950461838</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.037995671559429</v>
+        <v>-3.007865033437302</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.0105767361806</v>
+        <v>2.022628991429451</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3683438711500275</v>
+        <v>0.3252345656744649</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.447137751808136</v>
+        <v>3.421272168522798</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.986560338174769</v>
+        <v>-2.956429700052643</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.027826225524009</v>
+        <v>2.03987848077286</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.4197792045346872</v>
+        <v>0.3766698990591246</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.474674307828477</v>
+        <v>3.448808724543139</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.959609113848281</v>
+        <v>-2.929478475726155</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.048612868899347</v>
+        <v>2.060665124148197</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.4346595505624063</v>
+        <v>0.3915502450868437</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.49360866908985</v>
+        <v>3.467743085804512</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.095562121904598</v>
+        <v>-3.065431483782471</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.17833479782178</v>
+        <v>2.19038705307063</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.4346595505624063</v>
+        <v>0.3915502450868437</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.67771180123481</v>
+        <v>3.651846217949472</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.11797023970947</v>
+        <v>-3.087839601587343</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.161488245602824</v>
+        <v>2.173540500851674</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.4346595505624063</v>
+        <v>0.3915502450868437</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.669828496137803</v>
+        <v>3.643962912852465</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.265976007188869</v>
+        <v>-3.235845369066743</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.104339938160702</v>
+        <v>2.116392193409552</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.3479325416988649</v>
+        <v>0.3048232362233023</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.619846290369316</v>
+        <v>3.593980707083978</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.275416933077399</v>
+        <v>-3.245286294955273</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.156817285527136</v>
+        <v>2.168869540775987</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.4703596592422563</v>
+        <v>0.4272503537666937</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.749556278617197</v>
+        <v>3.72369069533186</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.274130169537843</v>
+        <v>-3.243999531415716</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.16022308548826</v>
+        <v>2.17227534073711</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.4716464227818129</v>
+        <v>0.4285371173062503</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.753219431286233</v>
+        <v>3.727353848000895</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.275687223527134</v>
+        <v>-3.245556585405008</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.157712076786319</v>
+        <v>2.169764332035169</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.4716464227818129</v>
+        <v>0.4285371173062503</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.751331244180008</v>
+        <v>3.72546566089467</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.282959109050599</v>
+        <v>-3.252828470928472</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.149623552179795</v>
+        <v>2.161675807428646</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4643745372583482</v>
+        <v>0.4212652317827855</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.741788342468791</v>
+        <v>3.715922759183453</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.281118089992348</v>
+        <v>-3.250987451870221</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.148793970013248</v>
+        <v>2.160846225262099</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4656427639298166</v>
+        <v>0.4225334584542539</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.740983288681824</v>
+        <v>3.715117705396487</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.288026795492028</v>
+        <v>-3.257896157369902</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.159103894679294</v>
+        <v>2.171156149928145</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4656427639298166</v>
+        <v>0.4225334584542539</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.754056695547743</v>
+        <v>3.728191112262405</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.289588438306888</v>
+        <v>-3.259457800184761</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.15847923755335</v>
+        <v>2.170531492802201</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4656427639298166</v>
+        <v>0.4225334584542539</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.754056695547743</v>
+        <v>3.728191112262405</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.317489225416361</v>
+        <v>-3.287358587294234</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.145842963836563</v>
+        <v>2.157895219085414</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4310458397868818</v>
+        <v>0.3879365343113191</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.731822582188984</v>
+        <v>3.705956998903646</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.320522222929035</v>
+        <v>-3.290391584806908</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.141394208808692</v>
+        <v>2.153446464057543</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4280128422742079</v>
+        <v>0.3849035367986453</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.726767227658578</v>
+        <v>3.700901644373241</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.340583544205542</v>
+        <v>-3.310452906083415</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.200075639888594</v>
+        <v>2.212127895137444</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4079515209977009</v>
+        <v>0.3648422155221382</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.781436394483178</v>
+        <v>3.755570811197841</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.47368904238518</v>
+        <v>-3.443558404263053</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.287145159618585</v>
+        <v>2.299197414867436</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.35432343566361</v>
+        <v>0.3112141301880474</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.889571262284571</v>
+        <v>3.863705678999233</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,13 +47942,13 @@
         <v>3.792349827964879</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.47368904238518</v>
+        <v>-3.443558404263053</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.287145159618585</v>
+        <v>2.299197414867436</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.35432343566361</v>
+        <v>0.3112141301880474</v>
       </c>
       <c r="G2017" t="n">
         <v>3.785413624951246</v>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.9%</t>
+          <t>-503.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-146.3%</t>
+          <t>-145.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-225.6%</t>
+          <t>-144.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.9%</t>
+          <t>-185.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-65.4%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.062918242124621</v>
+        <v>-3.918117718193352</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.024393477853064</v>
+        <v>1.082313687425571</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.02897367780055665</v>
+        <v>0.173774201731825</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667301405696994</v>
+        <v>2.754181720055755</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.1459195231499</v>
+        <v>-4.001118999218631</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8295486854436056</v>
+        <v>0.8874688950161129</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.1552033172046512</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.494514594981343</v>
+        <v>2.581394909340104</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.254533601593231</v>
+        <v>-4.109733077661962</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9062527147854789</v>
+        <v>0.9641729243579862</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.1552033172046512</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.614664255700548</v>
+        <v>2.701544570059309</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.219124563345088</v>
+        <v>-4.07432403941382</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9349293561870589</v>
+        <v>0.9928495657595662</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.1552033172046512</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.629177281802871</v>
+        <v>2.716057596161632</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.180740900786937</v>
+        <v>-4.035940376855669</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9477022625526881</v>
+        <v>1.005622472125195</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.1935869797628024</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.649626920680131</v>
+        <v>2.736507235038892</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.003624570751771</v>
+        <v>-3.858824046820502</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.015277823412057</v>
+        <v>1.073198032984564</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.1935869797628024</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.646355949525433</v>
+        <v>2.733236263884194</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.048716815585316</v>
+        <v>-3.903916291654048</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9979243172405516</v>
+        <v>1.055844526813059</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01310958733785572</v>
+        <v>0.1316909365934126</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609901715385712</v>
+        <v>2.696782029744473</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.869341394346549</v>
+        <v>-3.72454087041528</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.063461461042473</v>
+        <v>1.12138167061498</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.143667170832863</v>
+        <v>0.2884676947641313</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.697754745594558</v>
+        <v>2.784635059953319</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.914355607867155</v>
+        <v>-3.769555083935887</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.02626323096582</v>
+        <v>1.084183440538328</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1133182755182583</v>
+        <v>0.2581187994495267</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660352863737385</v>
+        <v>2.747233178096146</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.18136011813959</v>
+        <v>-4.036559594208322</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9251529891957919</v>
+        <v>0.9830731987682992</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08104476252469023</v>
+        <v>0.06375576140657813</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549426603250561</v>
+        <v>2.636306917609323</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.282557899576763</v>
+        <v>-4.137757375645495</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8838777985174242</v>
+        <v>0.9417980080899315</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1494535760700094</v>
+        <v>-0.004653052138741065</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.507585237019871</v>
+        <v>2.594465551378633</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.27604693296245</v>
+        <v>-4.131246409031182</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.884082146717466</v>
+        <v>0.9420023562899733</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1494535760700094</v>
+        <v>-0.004653052138741065</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.505185198574188</v>
+        <v>2.592065512932949</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.257008805255153</v>
+        <v>-4.112208281323885</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.88822211700863</v>
+        <v>0.9461423265811373</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.207637187401204</v>
+        <v>-0.06283666346993561</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.466799750983717</v>
+        <v>2.553680065342477</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.288135436405772</v>
+        <v>-4.143334912474503</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.053353333487063</v>
+        <v>1.11127354305957</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.207637187401204</v>
+        <v>-0.06283666346993561</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.644381619922397</v>
+        <v>2.731261934281158</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.176646056079591</v>
+        <v>-4.031845532148322</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.098782414603669</v>
+        <v>1.156702624176176</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.1693877506727122</v>
+        <v>-0.02458722674144381</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668164610945626</v>
+        <v>2.755044925304387</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.131841884539661</v>
+        <v>-3.987041360608393</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.122712613616567</v>
+        <v>1.180632823189074</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.1693877506727122</v>
+        <v>-0.02458722674144381</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674173141342552</v>
+        <v>2.761053455701313</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.984098914304659</v>
+        <v>-3.83929839037339</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.26096244950259</v>
+        <v>1.318882659075097</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.001580393437829009</v>
+        <v>0.1432201304934393</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854010203475503</v>
+        <v>2.940890517834264</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.086113596835879</v>
+        <v>-3.941313072904611</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.222950198021582</v>
+        <v>1.28087040759409</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.001580393437829009</v>
+        <v>0.1432201304934393</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.856803825006984</v>
+        <v>2.943684139365745</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.079960890783095</v>
+        <v>-3.935160366851827</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.226073628834354</v>
+        <v>1.283993838406862</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.004572312614955276</v>
+        <v>0.1493728365462236</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861157797030313</v>
+        <v>2.948038111389074</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.096770188933597</v>
+        <v>-3.951969665002328</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.218430386314264</v>
+        <v>1.276350595886771</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.01223698553554636</v>
+        <v>0.132563538395722</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.850152694880122</v>
+        <v>2.937033009238883</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.034472190157475</v>
+        <v>-3.889671666226207</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.309685139621534</v>
+        <v>1.367605349194041</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.01223698553554636</v>
+        <v>0.132563538395722</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916488248676943</v>
+        <v>3.003368563035704</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.832681992492317</v>
+        <v>-3.687881468561049</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.098982091076995</v>
+        <v>1.156902300649502</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.185781206633608</v>
+        <v>0.3305817305648764</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.743880036367834</v>
+        <v>2.830760350726595</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.75930389540358</v>
+        <v>-3.614503371472312</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.198623562234665</v>
+        <v>1.256543771807172</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2591593037223446</v>
+        <v>0.4039598276536129</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.858197126943251</v>
+        <v>2.945077441302012</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.857044440028555</v>
+        <v>-3.712243916097286</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.174155080500719</v>
+        <v>1.232075290073226</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2432700255893644</v>
+        <v>0.3880705495206327</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.863291296179507</v>
+        <v>2.950171610538268</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.033382200151484</v>
+        <v>-3.888581676220216</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.102155957276219</v>
+        <v>1.160076166848726</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.06693226546643499</v>
+        <v>0.2117327893977033</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.756024620930421</v>
+        <v>2.842904935289182</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.956960153719558</v>
+        <v>-3.812159629788289</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.131216393888918</v>
+        <v>1.189136603461425</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.06693226546643499</v>
+        <v>0.2117327893977033</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.754516238970349</v>
+        <v>2.84139655332911</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.912587022080989</v>
+        <v>-3.76778649814972</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.148828513979781</v>
+        <v>1.206748723552289</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.1113053971050036</v>
+        <v>0.2561059210362719</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.781002985388926</v>
+        <v>2.867883299747688</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789752801193822</v>
+        <v>-3.644952277262553</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.192355996473239</v>
+        <v>1.250276206045746</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.1113053971050036</v>
+        <v>0.2561059210362719</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.775396779527517</v>
+        <v>2.862277093886278</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742097070632766</v>
+        <v>-3.597296546701497</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.217800045725465</v>
+        <v>1.275720255297973</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.1589611276660592</v>
+        <v>0.3037616515973276</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.810371974891955</v>
+        <v>2.897252289250716</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.641578912134011</v>
+        <v>-3.496778388202743</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.262899682499692</v>
+        <v>1.320819892072199</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.2594792861648138</v>
+        <v>0.4042798100960822</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.875575243365932</v>
+        <v>2.962455557724693</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.7022455025364</v>
+        <v>-3.557444978605132</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.225387718814609</v>
+        <v>1.283307928387116</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1777809694462801</v>
+        <v>0.3225814933775485</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.813310925810684</v>
+        <v>2.900191240169445</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.657407100928002</v>
+        <v>-3.512606576996734</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.247420782068597</v>
+        <v>1.305340991641104</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1823244023911496</v>
+        <v>0.327124926322418</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.820134688188235</v>
+        <v>2.907015002546995</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.758165736685001</v>
+        <v>-3.613365212753732</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.211278267396875</v>
+        <v>1.269198476969382</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.09349883366414419</v>
+        <v>0.2382993575954125</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.771000286583109</v>
+        <v>2.85788060094187</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.7139628995991</v>
+        <v>-3.569162375667832</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.234839004759072</v>
+        <v>1.29275921433158</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.1377016707500446</v>
+        <v>0.282502194681313</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.803401591362487</v>
+        <v>2.890281905721248</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.750941927262543</v>
+        <v>-3.606141403331275</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.218457394162943</v>
+        <v>1.27637760373545</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.1746755725413752</v>
+        <v>0.3194760964726435</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.823995932906533</v>
+        <v>2.910876247265294</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.771000006127383</v>
+        <v>-3.626199482196115</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.261681927800046</v>
+        <v>1.319602137372553</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.1746755725413752</v>
+        <v>0.3194760964726435</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.875243698089572</v>
+        <v>2.962124012448333</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.731069332949493</v>
+        <v>-3.586268809018225</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.276094901665455</v>
+        <v>1.334015111237963</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2146062457192655</v>
+        <v>0.3594067696505339</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.89764280659056</v>
+        <v>2.984523120949321</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.680037240226965</v>
+        <v>-3.535236716295697</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.291455966992737</v>
+        <v>1.349376176565244</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.2656383384417935</v>
+        <v>0.4104388623730618</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.923210290462346</v>
+        <v>3.010090604821107</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.61481305909976</v>
+        <v>-3.470012535168491</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.334733043536324</v>
+        <v>1.392653253108831</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3308625195689991</v>
+        <v>0.4756630435002674</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.979532203231375</v>
+        <v>3.066412517590136</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.577386039028626</v>
+        <v>-3.432585515097358</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.345664823864058</v>
+        <v>1.403585033436565</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.3361140575981807</v>
+        <v>0.4809145815294491</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.978644098348164</v>
+        <v>3.065524412706925</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.597497695063334</v>
+        <v>-3.452697171132066</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.338876953781415</v>
+        <v>1.396797163353922</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3471414025955999</v>
+        <v>0.4919419265268683</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.986517297677856</v>
+        <v>3.073397612036617</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.543752880636129</v>
+        <v>-3.398952356704861</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.520932650573507</v>
+        <v>1.578852860146015</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.3572047120360619</v>
+        <v>0.5020052359673303</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.153113054363344</v>
+        <v>3.239993368722105</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.519961312029987</v>
+        <v>-3.375160788098719</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.650562187233781</v>
+        <v>1.708482396806289</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.3809962806422042</v>
+        <v>0.5257968045734726</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.287500904744846</v>
+        <v>3.374381219103607</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.493877227766179</v>
+        <v>-3.349076703834911</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.652703796953164</v>
+        <v>1.710624006525671</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.3809962806422042</v>
+        <v>0.5257968045734726</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.279208880758705</v>
+        <v>3.366089195117466</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.415746046917232</v>
+        <v>-3.270945522985964</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.682149464876522</v>
+        <v>1.740069674449029</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.4551730915258888</v>
+        <v>0.5999736154571571</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.321908162872695</v>
+        <v>3.408788477231457</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.406853585523949</v>
+        <v>-3.262053061592681</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.703260855160627</v>
+        <v>1.761181064733134</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.4551730915258888</v>
+        <v>0.5999736154571571</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.339462568599487</v>
+        <v>3.426342882958248</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.575329702493827</v>
+        <v>-3.430529178562559</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.627725455777259</v>
+        <v>1.685645665349766</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.427225255809308</v>
+        <v>0.5720257797405763</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.314548914574122</v>
+        <v>3.401429228932884</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.877530173632244</v>
+        <v>-2.732729649700976</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.888114964509754</v>
+        <v>1.946035174082262</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.3568771964388973</v>
+        <v>0.5016777203701657</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.253609776139738</v>
+        <v>3.340490090498499</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.854809069949091</v>
+        <v>-2.710008546017823</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.88786742847992</v>
+        <v>1.945787638052427</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.3568771964388973</v>
+        <v>0.5016777203701657</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.244273798636642</v>
+        <v>3.331154112995403</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.853084026659047</v>
+        <v>-2.708283502727779</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.047463571647107</v>
+        <v>2.105383781219614</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.358602239728941</v>
+        <v>0.5034027636602094</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.404214950461838</v>
+        <v>3.491095264820599</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.007865033437302</v>
+        <v>-2.863064509506034</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.022628991429451</v>
+        <v>2.080549201001959</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3252345656744649</v>
+        <v>0.4700350896057333</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.421272168522798</v>
+        <v>3.50815248288156</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.956429700052643</v>
+        <v>-2.811629176121375</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.03987848077286</v>
+        <v>2.097798690345368</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.3766698990591246</v>
+        <v>0.521470422990393</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.448808724543139</v>
+        <v>3.5356890389019</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.929478475726155</v>
+        <v>-2.784677951794887</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.060665124148197</v>
+        <v>2.118585333720704</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3915502450868437</v>
+        <v>0.5363507690181122</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.467743085804512</v>
+        <v>3.554623400163273</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.065431483782471</v>
+        <v>-2.920630959851203</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.19038705307063</v>
+        <v>2.248307262643137</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3915502450868437</v>
+        <v>0.5363507690181122</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.651846217949472</v>
+        <v>3.738726532308233</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.087839601587343</v>
+        <v>-2.943039077656075</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.173540500851674</v>
+        <v>2.231460710424182</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3915502450868437</v>
+        <v>0.5363507690181122</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.643962912852465</v>
+        <v>3.730843227211226</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.235845369066743</v>
+        <v>-3.091044845135475</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.116392193409552</v>
+        <v>2.174312402982059</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.3048232362233023</v>
+        <v>0.4496237601545707</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.593980707083978</v>
+        <v>3.680861021442739</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.245286294955273</v>
+        <v>-3.100485771024005</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.168869540775987</v>
+        <v>2.226789750348495</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.4272503537666937</v>
+        <v>0.5720508776979621</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.72369069533186</v>
+        <v>3.810571009690621</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.243999531415716</v>
+        <v>-3.099199007484448</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.17227534073711</v>
+        <v>2.230195550309618</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.4285371173062503</v>
+        <v>0.5733376412375187</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.727353848000895</v>
+        <v>3.814234162359656</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.245556585405008</v>
+        <v>-3.100756061473739</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.169764332035169</v>
+        <v>2.227684541607676</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.4285371173062503</v>
+        <v>0.5733376412375187</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.72546566089467</v>
+        <v>3.812345975253431</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.252828470928472</v>
+        <v>-3.108027946997204</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.161675807428646</v>
+        <v>2.219596017001153</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4212652317827855</v>
+        <v>0.566065755714054</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.715922759183453</v>
+        <v>3.802803073542214</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.250987451870221</v>
+        <v>-3.106186927938953</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.160846225262099</v>
+        <v>2.218766434834606</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4225334584542539</v>
+        <v>0.5673339823855225</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.715117705396487</v>
+        <v>3.801998019755248</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.257896157369902</v>
+        <v>-3.113095633438633</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.171156149928145</v>
+        <v>2.229076359500652</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4225334584542539</v>
+        <v>0.5673339823855225</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.728191112262405</v>
+        <v>3.815071426621166</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.259457800184761</v>
+        <v>-3.114657276253493</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.170531492802201</v>
+        <v>2.228451702374708</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4225334584542539</v>
+        <v>0.5673339823855225</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.728191112262405</v>
+        <v>3.815071426621166</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.287358587294234</v>
+        <v>-3.142558063362966</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.157895219085414</v>
+        <v>2.215815428657921</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3879365343113191</v>
+        <v>0.5327370582425877</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.705956998903646</v>
+        <v>3.792837313262408</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.290391584806908</v>
+        <v>-3.14559106087564</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.153446464057543</v>
+        <v>2.21136667363005</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3849035367986453</v>
+        <v>0.5297040607299137</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.700901644373241</v>
+        <v>3.787781958732002</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.310452906083415</v>
+        <v>-3.165652382152147</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.212127895137444</v>
+        <v>2.270048104709951</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3648422155221382</v>
+        <v>0.5096427394534067</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.755570811197841</v>
+        <v>3.842451125556602</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.443558404263053</v>
+        <v>-3.420364704985331</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.299197414867436</v>
+        <v>2.308474894578525</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3112141301880474</v>
+        <v>0.3805878571061867</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.863705678999233</v>
+        <v>3.905329915150117</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.811549600226988</v>
+        <v>3.811621041473477</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.792349827964879</v>
+        <v>3.812965930562898</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.443558404263053</v>
+        <v>-3.420364704985331</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.299197414867436</v>
+        <v>2.308474894578525</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3112141301880474</v>
+        <v>0.3805878571061867</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.785413624951246</v>
+        <v>3.806029727549265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-503.6%</t>
+          <t>-516.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-150.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.6%</t>
+          <t>-139.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-185.9%</t>
+          <t>-200.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-63.9%</t>
         </is>
       </c>
     </row>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.111789696197306</v>
+        <v>-6.114869821787153</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5117311352946952</v>
+        <v>0.5104990850587563</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.055326302669293</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.935897603729874</v>
+        <v>-5.938977729319721</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5856870958023168</v>
+        <v>0.584455045566378</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.055326302669293</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.76445114070741</v>
+        <v>-5.767531266297257</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6675931870658558</v>
+        <v>0.6663611368299174</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.8838798396468294</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.690161574969071</v>
+        <v>-5.693241700558918</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6963294909774884</v>
+        <v>0.69509744074155</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8095902739084901</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.626525832735137</v>
+        <v>-5.629605958324984</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7264785889253798</v>
+        <v>0.7252465386894409</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7459545316745556</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.515099073409217</v>
+        <v>-5.518179198999063</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7522435514395434</v>
+        <v>0.7510115012036045</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7459545316745556</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.274668576604356</v>
+        <v>-5.277748702194203</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8501588267863647</v>
+        <v>0.8489267765504263</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5055240348696953</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.202426008433162</v>
+        <v>-5.205506134023008</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8829851678896627</v>
+        <v>0.8817531176537243</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5055240348696953</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.149427686151774</v>
+        <v>-5.152507811741621</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9048630807195579</v>
+        <v>0.9036310304836195</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.4501877758677565</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.040622800672047</v>
+        <v>-5.043702926261894</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9453831061314424</v>
+        <v>0.9441510558955035</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.4501877758677565</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.820602002635036</v>
+        <v>-4.823682128224883</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.034970462356861</v>
+        <v>1.033738412120922</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3089679307997762</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.687734313571759</v>
+        <v>-4.690814439161605</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.104011720783995</v>
+        <v>1.102779670548056</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3089679307997762</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.56756123020726</v>
+        <v>-4.570641355797107</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.153226798570096</v>
+        <v>1.151994748334158</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1887948474352773</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.422889085107522</v>
+        <v>-4.425969210697369</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.221183759171431</v>
+        <v>1.219951708935493</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.04412270233553989</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.482763912465215</v>
+        <v>-4.485844038055061</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.18327131962978</v>
+        <v>1.182039269393842</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.103997529693232</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.362943681554378</v>
+        <v>-4.366023807144225</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246488581228324</v>
+        <v>1.245256530992385</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.103997529693232</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.365413388016184</v>
+        <v>-4.368493513606031</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153144897966043</v>
+        <v>1.151912847730104</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1064672361550382</v>
@@ -46079,10 +46079,10 @@
         <v>2.910673599960965</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.433783574340194</v>
+        <v>-4.436863699930041</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.13680374591114</v>
+        <v>1.135571695675202</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.09719153711882322</v>
@@ -46102,10 +46102,10 @@
         <v>2.901110308592857</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.447571627187241</v>
+        <v>-4.450651752777087</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.121725233404213</v>
+        <v>1.120493183168275</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.09719153711882322</v>
@@ -46125,10 +46125,10 @@
         <v>2.725819873633244</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.478564786515946</v>
+        <v>-4.481644912105793</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9340375347131178</v>
+        <v>0.9328054844771791</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.09719153711882322</v>
@@ -46148,10 +46148,10 @@
         <v>2.730387105625031</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.303090526723476</v>
+        <v>-4.306170652313323</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.008794470621893</v>
+        <v>1.007562420385955</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.09719153711882322</v>
@@ -46171,10 +46171,10 @@
         <v>2.706129134386238</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.414026779364725</v>
+        <v>-4.417106904954572</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.940161998326601</v>
+        <v>0.9389299480906623</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.09719153711882322</v>
@@ -46194,10 +46194,10 @@
         <v>2.709260519606144</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.380363233892443</v>
+        <v>-4.38344335948229</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9567588017354194</v>
+        <v>0.9555267514994807</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.06352799164654138</v>
@@ -46217,10 +46217,10 @@
         <v>2.719432906038276</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.32051061468872</v>
+        <v>-4.323590740278567</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9908722358490409</v>
+        <v>0.9896401856131023</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.06352799164654138</v>
@@ -46240,10 +46240,10 @@
         <v>2.714379176612137</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.234267151662342</v>
+        <v>-4.237347277252189</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.020315891633452</v>
+        <v>1.019083841397514</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.06352799164654138</v>
@@ -46263,10 +46263,10 @@
         <v>2.706154952056662</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.279573971061322</v>
+        <v>-4.282654096651169</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9939689393183859</v>
+        <v>0.9927368890824473</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1043381546557722</v>
@@ -46286,10 +46286,10 @@
         <v>2.706706825089764</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.308607075763623</v>
+        <v>-4.31168720135347</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9829075704705672</v>
+        <v>0.9816755202346283</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1043381546557722</v>
@@ -46309,10 +46309,10 @@
         <v>2.635979516981129</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.215796594312764</v>
+        <v>-4.21887671990261</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9493044549422767</v>
+        <v>0.948072404706338</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.01152767320491282</v>
@@ -46332,10 +46332,10 @@
         <v>2.63785299290573</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.260186063642191</v>
+        <v>-4.263266189232038</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9334221431351064</v>
+        <v>0.9321900928991678</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.05591714253434049</v>
@@ -46355,10 +46355,10 @@
         <v>2.632928701417453</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.147514845405941</v>
+        <v>-4.150594970995788</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9735663389413296</v>
+        <v>0.9723342887053907</v>
       </c>
       <c r="F1948" t="n">
         <v>0.05675407570190971</v>
@@ -46378,10 +46378,10 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.035137844223268</v>
+        <v>-4.038217969813115</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.024008435245066</v>
+        <v>1.022776385009127</v>
       </c>
       <c r="F1949" t="n">
         <v>0.05675407570190971</v>
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.918117718193352</v>
+        <v>-4.065998367714467</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.082313687425571</v>
+        <v>1.023161427617125</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.173774201731825</v>
+        <v>0.02897367780055665</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.754181720055755</v>
+        <v>2.667301405696994</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.001118999218631</v>
+        <v>-4.148999648739746</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8874688950161129</v>
+        <v>0.828316635207667</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.1552033172046512</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.581394909340104</v>
+        <v>2.494514594981343</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.109733077661962</v>
+        <v>-4.257613727183077</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9641729243579862</v>
+        <v>0.9050206645495402</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.1552033172046512</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.701544570059309</v>
+        <v>2.614664255700548</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.07432403941382</v>
+        <v>-4.222204688934935</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9928495657595662</v>
+        <v>0.9336973059511202</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.1552033172046512</v>
+        <v>0.01040279327338289</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.716057596161632</v>
+        <v>2.629177281802871</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.035940376855669</v>
+        <v>-4.183821026376783</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.005622472125195</v>
+        <v>0.9464702123167494</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.1935869797628024</v>
+        <v>0.04878645583153407</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.736507235038892</v>
+        <v>2.649626920680131</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.858824046820502</v>
+        <v>-4.006704696341617</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.073198032984564</v>
+        <v>1.014045773176118</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.1935869797628024</v>
+        <v>0.04878645583153407</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.733236263884194</v>
+        <v>2.646355949525433</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.903916291654048</v>
+        <v>-4.051796941175163</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.055844526813059</v>
+        <v>0.996692267004613</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.1316909365934126</v>
+        <v>-0.01310958733785572</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.696782029744473</v>
+        <v>2.609901715385712</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.72454087041528</v>
+        <v>-3.872421519936395</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.12138167061498</v>
+        <v>1.062229410806534</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.2884676947641313</v>
+        <v>0.143667170832863</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.784635059953319</v>
+        <v>2.697754745594558</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.769555083935887</v>
+        <v>-3.917435733457002</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.084183440538328</v>
+        <v>1.025031180729882</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.2581187994495267</v>
+        <v>0.1133182755182583</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.747233178096146</v>
+        <v>2.660352863737385</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.036559594208322</v>
+        <v>-4.184440243729437</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9830731987682992</v>
+        <v>0.9239209389598533</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.06375576140657813</v>
+        <v>-0.08104476252469023</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.636306917609323</v>
+        <v>2.549426603250561</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.137757375645495</v>
+        <v>-4.28563802516661</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9417980080899315</v>
+        <v>0.8826457482814856</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.004653052138741065</v>
+        <v>-0.1494535760700094</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.594465551378633</v>
+        <v>2.507585237019871</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.131246409031182</v>
+        <v>-4.279127058552297</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9420023562899733</v>
+        <v>0.8828500964815273</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.004653052138741065</v>
+        <v>-0.1494535760700094</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.592065512932949</v>
+        <v>2.505185198574188</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.112208281323885</v>
+        <v>-4.260088930845</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9461423265811373</v>
+        <v>0.8869900667726913</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.06283666346993561</v>
+        <v>-0.207637187401204</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.553680065342477</v>
+        <v>2.466799750983717</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.143334912474503</v>
+        <v>-4.291215561995618</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.11127354305957</v>
+        <v>1.052121283251124</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.06283666346993561</v>
+        <v>-0.207637187401204</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.731261934281158</v>
+        <v>2.644381619922397</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.031845532148322</v>
+        <v>-4.305082323329536</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.156702624176176</v>
+        <v>1.047407907703691</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.02458722674144381</v>
+        <v>-0.2454951041350269</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.755044925304387</v>
+        <v>2.622500198868237</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.987041360608393</v>
+        <v>-4.260278151789606</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.180632823189074</v>
+        <v>1.071338106716589</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.02458722674144381</v>
+        <v>-0.2454951041350269</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.761053455701313</v>
+        <v>2.628508729265163</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.83929839037339</v>
+        <v>-4.112535181554604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.318882659075097</v>
+        <v>1.209587942602612</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1432201304934393</v>
+        <v>-0.07768774690014374</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.940890517834264</v>
+        <v>2.808345791398114</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.941313072904611</v>
+        <v>-4.214549864085825</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.28087040759409</v>
+        <v>1.171575691121604</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1432201304934393</v>
+        <v>-0.07768774690014374</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.943684139365745</v>
+        <v>2.811139412929595</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.935160366851827</v>
+        <v>-4.208397158033041</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.283993838406862</v>
+        <v>1.174699121934376</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1493728365462236</v>
+        <v>-0.07153504084735945</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.948038111389074</v>
+        <v>2.815493384952924</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.951969665002328</v>
+        <v>-4.225206456183543</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.276350595886771</v>
+        <v>1.167055879414286</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.132563538395722</v>
+        <v>-0.08834433899786109</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.937033009238883</v>
+        <v>2.804488282802734</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.889671666226207</v>
+        <v>-4.16290845740742</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.367605349194041</v>
+        <v>1.258310632721555</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.132563538395722</v>
+        <v>-0.08834433899786109</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.003368563035704</v>
+        <v>2.870823836599555</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.687881468561049</v>
+        <v>-3.961118259742262</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.156902300649502</v>
+        <v>1.047607584177017</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3305817305648764</v>
+        <v>0.1096738531712933</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.830760350726595</v>
+        <v>2.698215624290445</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.614503371472312</v>
+        <v>-3.887740162653526</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.256543771807172</v>
+        <v>1.147249055334687</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4039598276536129</v>
+        <v>0.1830519502600298</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.945077441302012</v>
+        <v>2.812532714865863</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.712243916097286</v>
+        <v>-3.9854807072785</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.232075290073226</v>
+        <v>1.12278057360074</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3880705495206327</v>
+        <v>0.1671626721270497</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.950171610538268</v>
+        <v>2.817626884102118</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.888581676220216</v>
+        <v>-4.16181846740143</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.160076166848726</v>
+        <v>1.05078145037624</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2117327893977033</v>
+        <v>-0.009175087995879738</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.842904935289182</v>
+        <v>2.710360208853032</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.812159629788289</v>
+        <v>-4.085396420969503</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.189136603461425</v>
+        <v>1.079841886988939</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2117327893977033</v>
+        <v>-0.009175087995879738</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.84139655332911</v>
+        <v>2.70885182689296</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.76778649814972</v>
+        <v>-4.041023289330934</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.206748723552289</v>
+        <v>1.097454007079803</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2561059210362719</v>
+        <v>0.03519804364268886</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.867883299747688</v>
+        <v>2.735338573311538</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.644952277262553</v>
+        <v>-3.918189068443767</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.250276206045746</v>
+        <v>1.140981489573261</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2561059210362719</v>
+        <v>0.03519804364268886</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.862277093886278</v>
+        <v>2.729732367450128</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.597296546701497</v>
+        <v>-3.870533337882711</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.275720255297973</v>
+        <v>1.166425538825487</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3037616515973276</v>
+        <v>0.08285377420374451</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.897252289250716</v>
+        <v>2.764707562814566</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.496778388202743</v>
+        <v>-3.770015179383956</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.320819892072199</v>
+        <v>1.211525175599714</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4042798100960822</v>
+        <v>0.1833719327024991</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.962455557724693</v>
+        <v>2.829910831288543</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.557444978605132</v>
+        <v>-3.830681769786346</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.283307928387116</v>
+        <v>1.17401321191463</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3225814933775485</v>
+        <v>0.1016736159839654</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.900191240169445</v>
+        <v>2.767646513733296</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.512606576996734</v>
+        <v>-3.785843368177948</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.305340991641104</v>
+        <v>1.196046275168618</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.327124926322418</v>
+        <v>0.1062170489288349</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.907015002546995</v>
+        <v>2.774470276110846</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.613365212753732</v>
+        <v>-3.886602003934946</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.269198476969382</v>
+        <v>1.159903760496897</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.2382993575954125</v>
+        <v>0.01739148020182946</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.85788060094187</v>
+        <v>2.725335874505721</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.569162375667832</v>
+        <v>-3.842399166849046</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.29275921433158</v>
+        <v>1.183464497859094</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.282502194681313</v>
+        <v>0.0615943172877299</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.890281905721248</v>
+        <v>2.757737179285098</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.606141403331275</v>
+        <v>-3.879378194512489</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.27637760373545</v>
+        <v>1.167082887262964</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3194760964726435</v>
+        <v>0.09856821907906044</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.910876247265294</v>
+        <v>2.778331520829144</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.626199482196115</v>
+        <v>-3.899436273377329</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.319602137372553</v>
+        <v>1.210307420900068</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3194760964726435</v>
+        <v>0.09856821907906044</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.962124012448333</v>
+        <v>2.829579286012184</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.586268809018225</v>
+        <v>-3.859505600199439</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.334015111237963</v>
+        <v>1.224720394765477</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.3594067696505339</v>
+        <v>0.1384988922569508</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.984523120949321</v>
+        <v>2.851978394513171</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.535236716295697</v>
+        <v>-3.80847350747691</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.349376176565244</v>
+        <v>1.240081460092759</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.4104388623730618</v>
+        <v>0.1895309849794787</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.010090604821107</v>
+        <v>2.877545878384958</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.470012535168491</v>
+        <v>-3.743249326349705</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.392653253108831</v>
+        <v>1.283358536636346</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4756630435002674</v>
+        <v>0.2547551661066844</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.066412517590136</v>
+        <v>2.933867791153986</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.432585515097358</v>
+        <v>-3.705822306278571</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.403585033436565</v>
+        <v>1.29429031696408</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4809145815294491</v>
+        <v>0.260006704135866</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.065524412706925</v>
+        <v>2.932979686270775</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.452697171132066</v>
+        <v>-3.72593396231328</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.396797163353922</v>
+        <v>1.287502446881436</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.4919419265268683</v>
+        <v>0.2710340491332852</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.073397612036617</v>
+        <v>2.940852885600467</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.398952356704861</v>
+        <v>-3.672189147886075</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.578852860146015</v>
+        <v>1.469558143673529</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.5020052359673303</v>
+        <v>0.2810973585737472</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.239993368722105</v>
+        <v>3.107448642285955</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.375160788098719</v>
+        <v>-3.648397579279933</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.708482396806289</v>
+        <v>1.599187680333803</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.5257968045734726</v>
+        <v>0.3048889271798895</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.374381219103607</v>
+        <v>3.241836492667458</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.349076703834911</v>
+        <v>-3.622313495016125</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.710624006525671</v>
+        <v>1.601329290053185</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.5257968045734726</v>
+        <v>0.3048889271798895</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.366089195117466</v>
+        <v>3.233544468681317</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.270945522985964</v>
+        <v>-3.544182314167178</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.740069674449029</v>
+        <v>1.630774957976544</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5999736154571571</v>
+        <v>0.379065738063574</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.408788477231457</v>
+        <v>3.276243750795307</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.262053061592681</v>
+        <v>-3.535289852773895</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.761181064733134</v>
+        <v>1.651886348260648</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5999736154571571</v>
+        <v>0.379065738063574</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.426342882958248</v>
+        <v>3.293798156522098</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.430529178562559</v>
+        <v>-3.703765969743773</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.685645665349766</v>
+        <v>1.576350948877281</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5720257797405763</v>
+        <v>0.3511179023469932</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.401429228932884</v>
+        <v>3.268884502496733</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.732729649700976</v>
+        <v>-3.005966440882189</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.946035174082262</v>
+        <v>1.836740457609776</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5016777203701657</v>
+        <v>0.2807698429765825</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.340490090498499</v>
+        <v>3.207945364062349</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.710008546017823</v>
+        <v>-2.983245337199037</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.945787638052427</v>
+        <v>1.836492921579942</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5016777203701657</v>
+        <v>0.2807698429765825</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.331154112995403</v>
+        <v>3.198609386559253</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.708283502727779</v>
+        <v>-2.981520293908993</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.105383781219614</v>
+        <v>1.996089064747128</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.5034027636602094</v>
+        <v>0.2824948862666263</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.491095264820599</v>
+        <v>3.358550538384449</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.863064509506034</v>
+        <v>-3.136301300687248</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.080549201001959</v>
+        <v>1.971254484529473</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.4700350896057333</v>
+        <v>0.2491272122121502</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.50815248288156</v>
+        <v>3.37560775644541</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.811629176121375</v>
+        <v>-3.084865967302588</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.097798690345368</v>
+        <v>1.988503973872882</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.521470422990393</v>
+        <v>0.3005625455968098</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.5356890389019</v>
+        <v>3.403144312465751</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.784677951794887</v>
+        <v>-3.0579147429761</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.118585333720704</v>
+        <v>2.009290617248219</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.5363507690181122</v>
+        <v>0.315442891624529</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.554623400163273</v>
+        <v>3.422078673727124</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.920630959851203</v>
+        <v>-3.193867751032417</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.248307262643137</v>
+        <v>2.139012546170652</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.5363507690181122</v>
+        <v>0.315442891624529</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.738726532308233</v>
+        <v>3.606181805872084</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943039077656075</v>
+        <v>-3.216275868837289</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.231460710424182</v>
+        <v>2.122165993951696</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.5363507690181122</v>
+        <v>0.315442891624529</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.730843227211226</v>
+        <v>3.598298500775077</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.091044845135475</v>
+        <v>-3.364281636316688</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.174312402982059</v>
+        <v>2.065017686509574</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4496237601545707</v>
+        <v>0.2287158827609875</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.680861021442739</v>
+        <v>3.548316295006589</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.100485771024005</v>
+        <v>-3.373722562205218</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.226789750348495</v>
+        <v>2.117495033876009</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5720508776979621</v>
+        <v>0.3511430003043789</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.810571009690621</v>
+        <v>3.678026283254471</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.099199007484448</v>
+        <v>-3.372435798665662</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.230195550309618</v>
+        <v>2.120900833837132</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5733376412375187</v>
+        <v>0.3524297638439355</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.814234162359656</v>
+        <v>3.681689435923506</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.100756061473739</v>
+        <v>-3.373992852654953</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.227684541607676</v>
+        <v>2.118389825135191</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5733376412375187</v>
+        <v>0.3524297638439355</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.812345975253431</v>
+        <v>3.679801248817281</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.108027946997204</v>
+        <v>-3.381264738178418</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.219596017001153</v>
+        <v>2.110301300528667</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.566065755714054</v>
+        <v>0.3451578783204708</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.802803073542214</v>
+        <v>3.670258347106065</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.106186927938953</v>
+        <v>-3.379423719120167</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.218766434834606</v>
+        <v>2.10947171836212</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5673339823855225</v>
+        <v>0.3464261049919392</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.801998019755248</v>
+        <v>3.669453293319098</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.113095633438633</v>
+        <v>-3.386332424619847</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.229076359500652</v>
+        <v>2.119781643028166</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5673339823855225</v>
+        <v>0.3464261049919392</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.815071426621166</v>
+        <v>3.682526700185017</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.114657276253493</v>
+        <v>-3.387894067434707</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.228451702374708</v>
+        <v>2.119156985902223</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5673339823855225</v>
+        <v>0.3464261049919392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.815071426621166</v>
+        <v>3.682526700185017</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.142558063362966</v>
+        <v>-3.41579485454418</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.215815428657921</v>
+        <v>2.106520712185436</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5327370582425877</v>
+        <v>0.3118291808490044</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.792837313262408</v>
+        <v>3.660292586826258</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.14559106087564</v>
+        <v>-3.418827852056854</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.21136667363005</v>
+        <v>2.102071957157565</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5297040607299137</v>
+        <v>0.3087961833363305</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.787781958732002</v>
+        <v>3.655237232295852</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.165652382152147</v>
+        <v>-3.438889173333361</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.270048104709951</v>
+        <v>2.160753388237466</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5096427394534067</v>
+        <v>0.2887348620598235</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.842451125556602</v>
+        <v>3.709906399120452</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.420364704985331</v>
+        <v>-3.571994671512999</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.308474894578525</v>
+        <v>2.247822907967458</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3805878571061867</v>
+        <v>0.2351067767257327</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.905329915150117</v>
+        <v>3.818041266921844</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.811621041473477</v>
+        <v>3.379924989054393</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.812965930562898</v>
+        <v>3.680283232578866</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.420364704985331</v>
+        <v>-3.549013857119077</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.308474894578525</v>
+        <v>2.260321265417488</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3805878571061867</v>
+        <v>0.2351067767257327</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.806029727549265</v>
+        <v>3.821347298614306</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240706.xlsx
+++ b/tame_output/ON/bt/strategyON_20240706.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-659.5%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>460.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-516.5%</t>
+          <t>-513.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.2%</t>
+          <t>-149.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-278.6%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.5%</t>
+          <t>-121.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-200.5%</t>
+          <t>-185.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-167.6%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-54.9%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.837301804426076</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.381643121357687</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8007309565348886</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.597358841362798</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.203370531570728</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.228299929806275</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4346622293902359</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.370801904382455</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.411861313022413</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.165241906964369</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2261714479385515</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.266045725250213</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.659062497787635</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.074460183466849</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2463248014373639</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.286236487758069</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.151447525811732</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.878612564300943</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2460602265867328</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.991911862987343</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.536627916741804</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.723082946741777</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2460602265867328</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.990454401800207</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.786498596756386</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.624903798190561</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2097975067562696</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.013981157153101</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.993010373643407</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.53840514609201</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4163092836432911</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.886180149677146</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.312354448723909</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.412440442760069</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4163092836432911</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.887953076377405</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.744160241873696</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.226051012967558</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5527267800845581</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.792435465980049</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.978854236006248</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.120458190316628</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5463905128553029</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.784522001319693</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.314516883236701</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9847737230804121</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6143214983442078</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.742344001682315</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.678143128137014</v>
+        <v>-5.528909118410009</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8458107853545282</v>
+        <v>0.9055043892453303</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7125431352113336</v>
+        <v>-0.5633091254843285</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.689898579796282</v>
+        <v>2.779438985632484</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.043270510775761</v>
+        <v>-5.894036501048756</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6990143473048609</v>
+        <v>0.7587079511956629</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.008853919510346</v>
+        <v>-0.859619909783341</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.511366624222705</v>
+        <v>2.600907030058909</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.45185928795644</v>
+        <v>-6.302625278229435</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5343403804473486</v>
+        <v>0.5940339843381501</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.264974901929057</v>
+        <v>2.354515307765261</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.728435388272272</v>
+        <v>-6.579201378545267</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.418895372792476</v>
+        <v>0.478588976683278</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.260160334400518</v>
+        <v>2.349700740236721</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.14482726255927</v>
+        <v>-6.995593252832265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2503326736865543</v>
+        <v>0.3100262775773563</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.258154385009395</v>
+        <v>2.347694790845599</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.389098663286339</v>
+        <v>-7.239864653559335</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1628828040644055</v>
+        <v>0.2225764079552075</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.268413075678074</v>
+        <v>2.357953481514278</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.5943496825231</v>
+        <v>-7.445115672796095</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.07688196151539683</v>
+        <v>0.1365755654061984</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.264512640823769</v>
+        <v>2.354053046659972</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.757929560707483</v>
+        <v>-7.608695550980478</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.009854930296644415</v>
+        <v>0.069548534187446</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.417442696691025</v>
+        <v>-1.268208686964019</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.26291756087877</v>
+        <v>2.352457966714973</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.054590902517681</v>
+        <v>-7.905356892790675</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1050306304982267</v>
+        <v>-0.04533702660742467</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.225450655367651</v>
+        <v>2.314991061203854</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.241310610826984</v>
+        <v>-8.092076601099977</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.183744818356351</v>
+        <v>-0.1240512144655486</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.221424350833249</v>
+        <v>2.310964756669451</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.624311999569615</v>
+        <v>-8.475077989842609</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3370474751749875</v>
+        <v>-0.277353871284185</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.486185832424903</v>
+        <v>-1.336951822697898</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.221322249511664</v>
+        <v>2.310862655347867</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.80618179055465</v>
+        <v>-8.656947780827643</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4072238755975714</v>
+        <v>-0.3475302717067685</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.668055623409938</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.114771890892073</v>
+        <v>2.204312296728276</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.165712113058651</v>
+        <v>-9.016478103331645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5456857013011218</v>
+        <v>-0.4859920974103193</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.668055623409938</v>
+        <v>-1.518821613682933</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.120122194190123</v>
+        <v>2.209662600026327</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.216061176512873</v>
+        <v>-9.066827166785867</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5579093067256333</v>
+        <v>-0.4982157028348304</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.71840468686416</v>
+        <v>-1.569170677137155</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.097828776074768</v>
+        <v>2.187369181910971</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.313680453934269</v>
+        <v>-9.164446444207263</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5939152670724228</v>
+        <v>-0.5342216631816199</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.816023964285557</v>
+        <v>-1.666789954558552</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.042298960243699</v>
+        <v>2.131839366079902</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.461206541939912</v>
+        <v>-9.311972532212906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6500321459531078</v>
+        <v>-0.5903385420623048</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.9635500522912</v>
+        <v>-1.814316042564195</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.956676863761885</v>
+        <v>2.046217269598088</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.665464717269776</v>
+        <v>-9.516230707542769</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7262222189664107</v>
+        <v>-0.6665286150756082</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.091188996905189</v>
+        <v>-1.941954987178184</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.885606694112134</v>
+        <v>1.975147099948336</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.699117555778249</v>
+        <v>-9.549883546051243</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.735200799885364</v>
+        <v>-0.6755071959945615</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.191602364822227</v>
+        <v>-2.042368355095221</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.829841227846347</v>
+        <v>1.91938163368255</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.6256477241108</v>
+        <v>-9.476413714383794</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6904411657249634</v>
+        <v>-0.6307475618341609</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.118132533154778</v>
+        <v>-1.968898523427773</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.889294828340238</v>
+        <v>1.978835234176441</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.800772141497344</v>
+        <v>-9.651538131770337</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7459357119320638</v>
+        <v>-0.6862421080412613</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.293256950541322</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.798775398655828</v>
+        <v>1.888315804492031</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.03522423551183</v>
+        <v>-9.885990225784827</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8469357144394558</v>
+        <v>-0.7872421105486533</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.293256950541322</v>
+        <v>-2.144022940814317</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.791556233754232</v>
+        <v>1.881096639590435</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.13959896653828</v>
+        <v>-9.990364956811273</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8953577976240106</v>
+        <v>-0.8356641937332081</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.397631681567768</v>
+        <v>-2.248397671840763</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.722259204364389</v>
+        <v>1.811799610200591</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.19238512213861</v>
+        <v>-10.0431511124116</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9153564700255847</v>
+        <v>-0.8556628661347823</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.493307168150165</v>
+        <v>-2.34407315842316</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.665969702253507</v>
+        <v>1.75551010808971</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.3184219155069</v>
+        <v>-10.16918790577989</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9630774587437858</v>
+        <v>-0.9033838548529833</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.683814404568467</v>
+        <v>1.77335481040467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.26135014361097</v>
+        <v>-10.11211613388396</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9362584142990125</v>
+        <v>-0.87656481040821</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.687804740254867</v>
+        <v>1.777345146091071</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.40302198533509</v>
+        <v>-10.25378797560808</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9944023778874023</v>
+        <v>-0.9347087739965998</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.468055545340422</v>
+        <v>-2.318821535613417</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.686329513356126</v>
+        <v>1.775869919192329</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.35343114091025</v>
+        <v>-10.20419713118324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9595126299525965</v>
+        <v>-0.899819026061794</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.418464700915588</v>
+        <v>-2.269230691188584</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.731137430175898</v>
+        <v>1.820677836012101</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.34062374790548</v>
+        <v>-10.19138973817847</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9674408063973696</v>
+        <v>-0.9077472025065672</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.46732047592449</v>
+        <v>-2.318086466197485</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.688772831523875</v>
+        <v>1.778313237360078</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.11477859518607</v>
+        <v>-9.96554458545906</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8675236722733977</v>
+        <v>-0.8078300683825947</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.425393800337326</v>
+        <v>-2.276159790610321</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.723507909912382</v>
+        <v>1.813048315748585</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.990199938848475</v>
+        <v>-9.840965929121468</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8165530651823016</v>
+        <v>-0.7568594612914992</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.425393800337326</v>
+        <v>-2.276159790610321</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.72464705446844</v>
+        <v>1.814187460304644</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.04309522689276</v>
+        <v>-9.893861217165755</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8350774062379083</v>
+        <v>-0.7753838023471058</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.42043845424888</v>
+        <v>-2.271204444521875</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.730254036283616</v>
+        <v>1.819794442119819</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.97096205160488</v>
+        <v>-9.821728041877874</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8004904318841195</v>
+        <v>-0.740796827993317</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.42043845424888</v>
+        <v>-2.271204444521875</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.735987740522252</v>
+        <v>1.825528146358455</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.899595658995233</v>
+        <v>-9.750361649268227</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7816811372341261</v>
+        <v>-0.7219875333433232</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.349072061639232</v>
+        <v>-2.199838051912227</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.769070313694176</v>
+        <v>1.858610719530379</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.806136625010009</v>
+        <v>-9.656902615283002</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7541810049529438</v>
+        <v>-0.6944874010621409</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.349072061639232</v>
+        <v>-2.199838051912227</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.759186832381268</v>
+        <v>1.848727238217471</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.538894824141611</v>
+        <v>-9.389660814414604</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6491188451049585</v>
+        <v>-0.5894252412141556</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.349072061639232</v>
+        <v>-2.199838051912227</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.757352271881895</v>
+        <v>1.846892677718098</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.44098778546512</v>
+        <v>-9.291753775738114</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6102563446078229</v>
+        <v>-0.5505627407170204</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.281086311778675</v>
+        <v>-2.13185230205167</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.797843406824768</v>
+        <v>1.887383812660971</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.417034244489162</v>
+        <v>-9.267800234762156</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6000064220719463</v>
+        <v>-0.5403128181811434</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.257132770802718</v>
+        <v>-2.107898761075713</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.812884037555836</v>
+        <v>1.902424443392039</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.152974306166366</v>
+        <v>-9.003740296439359</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5076427629045797</v>
+        <v>-0.4479491590137767</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.993072832479921</v>
+        <v>-1.843838822752917</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.958059684387762</v>
+        <v>2.047600090223964</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.445894682661528</v>
+        <v>-8.296660672934522</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2275979471629457</v>
+        <v>-0.1679043432721428</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.993072832479921</v>
+        <v>-1.843838822752917</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.955272650727461</v>
+        <v>2.044813056563664</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.405710384295338</v>
+        <v>-8.256476374568331</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2111806039286281</v>
+        <v>-0.1514870000378252</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.952888534113731</v>
+        <v>-1.803654524386726</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.979726853635016</v>
+        <v>2.06926725947122</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.242310513355974</v>
+        <v>-8.093076503628968</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1464538343321258</v>
+        <v>-0.08676023044132286</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.789488663174368</v>
+        <v>-1.640254653447363</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.077133597419391</v>
+        <v>2.166674003255594</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.008829291126375</v>
+        <v>-7.859595281399369</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.04513691660243335</v>
+        <v>0.01455668728836867</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.55600744094477</v>
+        <v>-1.406773431217765</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.225146759595003</v>
+        <v>2.314687165431205</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.85916290011886</v>
+        <v>-7.709928890391854</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.01183742948761335</v>
+        <v>0.07153103337841582</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.463103949702234</v>
+        <v>-1.313869939975229</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.277996644027565</v>
+        <v>2.367537049863768</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.726887426487973</v>
+        <v>-7.577653416760968</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.06011510568699485</v>
+        <v>0.1198087095777973</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.330828476071347</v>
+        <v>-1.181594466344342</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.352729414953123</v>
+        <v>2.442269820789327</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.571149093928232</v>
+        <v>-7.421915084201226</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1252254993985282</v>
+        <v>0.1849191032893307</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.175090143511606</v>
+        <v>-1.025856133784601</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.448987475176605</v>
+        <v>2.538527881012808</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.322149295244651</v>
+        <v>-7.172915285517645</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2377317600956195</v>
+        <v>0.2974253639864219</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.175090143511606</v>
+        <v>-1.025856133784601</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.461893816400264</v>
+        <v>2.551434222236467</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.427739285017755</v>
+        <v>-7.278505275290749</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.06751983458715927</v>
+        <v>0.1272134384779613</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.28068013328471</v>
+        <v>-1.131446123557705</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.270563892937183</v>
+        <v>2.360104298773386</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.446474187136352</v>
+        <v>-7.297240177409346</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1085702156168065</v>
+        <v>0.1682638195076089</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.286276142944841</v>
+        <v>-1.137042133217836</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.31575062901819</v>
+        <v>2.405291034854393</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.298534145728753</v>
+        <v>-7.149300136001747</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.04786730949167861</v>
+        <v>0.1075609133824811</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.265955227036284</v>
+        <v>-1.116721217309279</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.208064255875157</v>
+        <v>2.29760466171136</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.245564623474764</v>
+        <v>-7.096330613747758</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.06034113213979619</v>
+        <v>0.1200347360305982</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.212985704782295</v>
+        <v>-1.06375169505529</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.231131982974072</v>
+        <v>2.320672388810275</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.202016216704074</v>
+        <v>-7.052782206977068</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.07079988275297922</v>
+        <v>0.1304934866437812</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.212985704782295</v>
+        <v>-1.06375169505529</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.224171370878979</v>
+        <v>2.313711776715182</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.959867823250216</v>
+        <v>-6.81063381352321</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1821215945156656</v>
+        <v>0.2418151984064676</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.212985704782295</v>
+        <v>-1.06375169505529</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.238633725260122</v>
+        <v>2.328174131096325</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.851608686127694</v>
+        <v>-6.702374676400688</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2199573698238693</v>
+        <v>0.2796509737146713</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.212985704782295</v>
+        <v>-1.06375169505529</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.233165845719317</v>
+        <v>2.32270625155552</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.728317551310563</v>
+        <v>-6.579083541583557</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2667719177612984</v>
+        <v>0.3264655216521004</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.089694569965165</v>
+        <v>-0.9404605602381596</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.304638620620172</v>
+        <v>2.394179026456375</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.70716835240712</v>
+        <v>-6.557934342680114</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2829325755600007</v>
+        <v>0.3426261794508032</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.068545371061721</v>
+        <v>-0.9193113613347162</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.325029118199564</v>
+        <v>2.414569524035767</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.463402910423675</v>
+        <v>-6.31416890069667</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3762194607004292</v>
+        <v>0.4359130645912317</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.068545371061721</v>
+        <v>-0.9193113613347162</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.320809826546614</v>
+        <v>2.410350232382817</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.361640090146381</v>
+        <v>-6.212406080419375</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4190489027313631</v>
+        <v>0.4787425066221656</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.9060922929422875</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.330865581502088</v>
+        <v>2.42040598733829</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.114869821787153</v>
+        <v>-5.9625556864703</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5104990850587563</v>
+        <v>0.5714247391854976</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.9060922929422875</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.32360765648579</v>
+        <v>2.413148062321993</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.938977729319721</v>
+        <v>-5.786663594002867</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.584455045566378</v>
+        <v>0.6453806996931193</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.055326302669293</v>
+        <v>-0.9060922929422875</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.327206780006438</v>
+        <v>2.416747185842641</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.767531266297257</v>
+        <v>-5.615217130980404</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6663611368299174</v>
+        <v>0.7272867909566587</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8838798396468294</v>
+        <v>-0.7346458299198244</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.44340216387447</v>
+        <v>2.532942569710673</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.693241700558918</v>
+        <v>-5.540927565242065</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.69509744074155</v>
+        <v>0.7560230948682913</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8095902739084901</v>
+        <v>-0.6603562641814851</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.48699638093377</v>
+        <v>2.576536786769974</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.629605958324984</v>
+        <v>-5.47729182300813</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7252465386894409</v>
+        <v>0.7861721928161822</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7459545316745556</v>
+        <v>-0.5967205219475505</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.529872627328448</v>
+        <v>2.619413033164652</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.518179198999063</v>
+        <v>-5.36586506368221</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7510115012036045</v>
+        <v>0.8119371553303458</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7459545316745556</v>
+        <v>-0.5967205219475505</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.511066886112244</v>
+        <v>2.600607291948447</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.277748702194203</v>
+        <v>-5.12543456687735</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8489267765504263</v>
+        <v>0.9098524306771676</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5055240348696953</v>
+        <v>-0.3562900251426903</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.657068260820038</v>
+        <v>2.746608666656241</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.205506134023008</v>
+        <v>-5.053191998706155</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8817531176537243</v>
+        <v>0.9426787717804657</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5055240348696953</v>
+        <v>-0.3562900251426903</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.660997574654858</v>
+        <v>2.750537980491061</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.152507811741621</v>
+        <v>-5.000193676424767</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9036310304836195</v>
+        <v>0.9645566846103606</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4501877758677565</v>
+        <v>-0.3009537661407514</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.694877913973361</v>
+        <v>2.784418319809564</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.043702926261894</v>
+        <v>-4.89138879094504</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9441510558955035</v>
+        <v>1.005076710022245</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4501877758677565</v>
+        <v>-0.3009537661407514</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.691875985193355</v>
+        <v>2.781416391029558</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.823682128224883</v>
+        <v>-4.67136799290803</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.033738412120922</v>
+        <v>1.094664066247663</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3089679307997762</v>
+        <v>-0.1597339210727712</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.778186929244757</v>
+        <v>2.86772733508096</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.690814439161605</v>
+        <v>-4.538500303844752</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.102779670548056</v>
+        <v>1.163705324674798</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3089679307997762</v>
+        <v>-0.1597339210727712</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.79408111204658</v>
+        <v>2.883621517882783</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.570641355797107</v>
+        <v>-4.418327220480253</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.151994748334158</v>
+        <v>1.212920402460899</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1887948474352773</v>
+        <v>-0.03956083770827223</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.867330806505581</v>
+        <v>2.956871212341785</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.425969210697369</v>
+        <v>-4.273655075380516</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.219951708935493</v>
+        <v>1.280877363062234</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.04412270233553989</v>
+        <v>0.1051113073914652</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.964222196126864</v>
+        <v>3.053762601963067</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.485844038055061</v>
+        <v>-4.333529902738208</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.182039269393842</v>
+        <v>1.242964923520583</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.103997529693232</v>
+        <v>0.04523648003377306</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.914334791113674</v>
+        <v>3.003875196949878</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.366023807144225</v>
+        <v>-4.213709671827371</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.245256530992385</v>
+        <v>1.306182185119126</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.103997529693232</v>
+        <v>0.04523648003377306</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.929623960347883</v>
+        <v>3.019164366184086</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.368493513606031</v>
+        <v>-4.216179378289177</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.151912847730104</v>
+        <v>1.212838501856845</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1064672361550382</v>
+        <v>0.0427667735719669</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.835786335793241</v>
+        <v>2.925326741629444</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.910673599960965</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.436863699930041</v>
+        <v>-4.284549564613187</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.135571695675202</v>
+        <v>1.196497349801943</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.05204247260818184</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.852358677689672</v>
+        <v>2.941899083525875</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.901110308592857</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.450651752777087</v>
+        <v>-4.298337617460234</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.120493183168275</v>
+        <v>1.181418837295016</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.05204247260818184</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.842795386321563</v>
+        <v>2.932335792157766</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.725819873633244</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.481644912105793</v>
+        <v>-4.32933077678894</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9328054844771791</v>
+        <v>0.9937311386039205</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.05204247260818184</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.66750495136195</v>
+        <v>2.757045357198153</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.730387105625031</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.306170652313323</v>
+        <v>-4.15385651699647</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.007562420385955</v>
+        <v>1.068488074512696</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.05204247260818184</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.672072183353738</v>
+        <v>2.761612589189941</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.706129134386238</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.417106904954572</v>
+        <v>-4.264792769637719</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9389299480906623</v>
+        <v>0.9998556022174037</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.09719153711882322</v>
+        <v>0.05204247260818184</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.647814212114945</v>
+        <v>2.737354617951148</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.709260519606144</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.38344335948229</v>
+        <v>-4.231129224165437</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9555267514994807</v>
+        <v>1.016452405626222</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.08570601808046369</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.671143724618219</v>
+        <v>2.760684130454422</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.719432906038276</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.323590740278567</v>
+        <v>-4.171276604961713</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9896401856131023</v>
+        <v>1.050565839739844</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.08570601808046369</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.681316111050352</v>
+        <v>2.770856516886555</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.714379176612137</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.237347277252189</v>
+        <v>-4.085033141935336</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.019083841397514</v>
+        <v>1.080009495524255</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.06352799164654138</v>
+        <v>0.08570601808046369</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.676262381624212</v>
+        <v>2.765802787460415</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.706154952056662</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.282654096651169</v>
+        <v>-4.130339961334315</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9927368890824473</v>
+        <v>1.053662543209189</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1043381546557722</v>
+        <v>0.04489585507123289</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.643552059263199</v>
+        <v>2.733092465099402</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.706706825089764</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.31168720135347</v>
+        <v>-4.159373066036617</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9816755202346283</v>
+        <v>1.04260117436137</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1043381546557722</v>
+        <v>0.04489585507123289</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.6441039322963</v>
+        <v>2.733644338132504</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.635979516981129</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.21887671990261</v>
+        <v>-4.066562584585757</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.948072404706338</v>
+        <v>1.008998058833079</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.01152767320491282</v>
+        <v>0.1377063365220922</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.629062913058182</v>
+        <v>2.718603318894385</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.63785299290573</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.263266189232038</v>
+        <v>-4.110952053915184</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9321900928991678</v>
+        <v>0.9931157470259091</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.05591714253434049</v>
+        <v>0.09331686719266458</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.604302707385126</v>
+        <v>2.693843113221329</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.632928701417453</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.150594970995788</v>
+        <v>-3.998280835678934</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9723342887053907</v>
+        <v>1.033259942832132</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.05675407570190971</v>
+        <v>0.2059880854289148</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.666981146838599</v>
+        <v>2.756521552674802</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.63841999724812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.038217969813115</v>
+        <v>-3.885903834496262</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.022776385009127</v>
+        <v>1.083702039135868</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.05675407570190971</v>
+        <v>0.2059880854289148</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.672472442669267</v>
+        <v>2.762012848505469</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.649917199016659</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.065998367714467</v>
+        <v>-3.913684232397615</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.023161427617125</v>
+        <v>1.084087081743866</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.02897367780055665</v>
+        <v>0.1782076875275617</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.667301405696994</v>
+        <v>2.756841811533197</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.488272919017313</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.148999648739746</v>
+        <v>-3.996685513422894</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.828316635207667</v>
+        <v>0.8892422893344079</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.159636803000388</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.494514594981343</v>
+        <v>2.584055000817546</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.608422579736518</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.257613727183077</v>
+        <v>-4.105299591866225</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9050206645495402</v>
+        <v>0.9659463186762811</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.159636803000388</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.614664255700548</v>
+        <v>2.704204661536751</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.622935605838841</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.222204688934935</v>
+        <v>-4.069890553618082</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9336973059511202</v>
+        <v>0.9946229600778613</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.01040279327338289</v>
+        <v>0.159636803000388</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.629177281802871</v>
+        <v>2.718717687639074</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.62035504718121</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.183821026376783</v>
+        <v>-4.031506891059931</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9464702123167494</v>
+        <v>1.00739586644349</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.1980204655585391</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.649626920680131</v>
+        <v>2.739167326516334</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.617084076026512</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.006704696341617</v>
+        <v>-3.854390561024765</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.014045773176118</v>
+        <v>1.074971427302859</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.04878645583153407</v>
+        <v>0.1980204655585391</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.646355949525433</v>
+        <v>2.735896355361636</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.617767467788426</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.051796941175163</v>
+        <v>-3.899482805858311</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.996692267004613</v>
+        <v>1.057617921131354</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01310958733785572</v>
+        <v>0.1361244223891493</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609901715385712</v>
+        <v>2.699442121221916</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.61155444309484</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.872421519936395</v>
+        <v>-3.720107384619543</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.062229410806534</v>
+        <v>1.123155064933275</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.143667170832863</v>
+        <v>0.292901180559868</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.697754745594558</v>
+        <v>2.787295151430761</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.59236189842643</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.917435733457002</v>
+        <v>-3.765121598140149</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.025031180729882</v>
+        <v>1.085956834856623</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1133182755182583</v>
+        <v>0.2625522852452634</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660352863737385</v>
+        <v>2.749893269573588</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.598053460765375</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.184440243729437</v>
+        <v>-4.032126108412585</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9239209389598533</v>
+        <v>0.9848465930865942</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08104476252469023</v>
+        <v>0.06818924720231484</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549426603250561</v>
+        <v>2.638967009086765</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.597257382661877</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.28563802516661</v>
+        <v>-4.133323889849757</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8826457482814856</v>
+        <v>0.9435714024082267</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1494535760700094</v>
+        <v>-0.0002195663430043515</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.507585237019871</v>
+        <v>2.597125642856074</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.594857344216194</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.279127058552297</v>
+        <v>-4.126812923235445</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8828500964815273</v>
+        <v>0.9437757506082685</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1494535760700094</v>
+        <v>-0.0002195663430043515</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.505185198574188</v>
+        <v>2.594725604410391</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.591382063424438</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.260088930845</v>
+        <v>-4.107774795528147</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8869900667726913</v>
+        <v>0.9479157208994322</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.207637187401204</v>
+        <v>-0.05840317767419889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.466799750983717</v>
+        <v>2.556340156819919</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.768963932363119</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.291215561995618</v>
+        <v>-4.138901426678766</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.052121283251124</v>
+        <v>1.113046937377865</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.207637187401204</v>
+        <v>-0.05840317767419889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.644381619922397</v>
+        <v>2.7339220257586</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.769797261349253</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.305082323329536</v>
+        <v>-4.152768188012684</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.047407907703691</v>
+        <v>1.108333561830432</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2454951041350269</v>
+        <v>-0.09626109440802183</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.622500198868237</v>
+        <v>2.71204060470444</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.775805791746178</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.260278151789606</v>
+        <v>-4.107964016472754</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.071338106716589</v>
+        <v>1.13226376084333</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2454951041350269</v>
+        <v>-0.09626109440802183</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.628508729265163</v>
+        <v>2.718049135101366</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.8549584395382</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.112535181554604</v>
+        <v>-3.960221046237752</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.209587942602612</v>
+        <v>1.270513596729352</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.07768774690014374</v>
+        <v>0.07154626282686133</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.808345791398114</v>
+        <v>2.897886197234318</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.857752061069681</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.214549864085825</v>
+        <v>-4.062235728768973</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.171575691121604</v>
+        <v>1.232501345248345</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.07768774690014374</v>
+        <v>0.07154626282686133</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.811139412929595</v>
+        <v>2.900679818765799</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.85841440946134</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.208397158033041</v>
+        <v>-4.056083022716188</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.174699121934376</v>
+        <v>1.235624776061117</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.07153504084735945</v>
+        <v>0.07769896887964561</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.815493384952924</v>
+        <v>2.905033790789127</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.85749488620145</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.225206456183543</v>
+        <v>-4.07289232086669</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.167055879414286</v>
+        <v>1.227981533541027</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.08834433899786109</v>
+        <v>0.06088967072914397</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.804488282802734</v>
+        <v>2.894028688638937</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.923830439998271</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.16290845740742</v>
+        <v>-4.010594322090568</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.258310632721555</v>
+        <v>1.319236286848297</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.08834433899786109</v>
+        <v>0.06088967072914397</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.870823836599555</v>
+        <v>2.960364242435757</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632411312387669</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.961118259742262</v>
+        <v>-3.80880412442541</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.047607584177017</v>
+        <v>1.108533238303758</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1096738531712933</v>
+        <v>0.2589078628982984</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.698215624290445</v>
+        <v>2.787756030126648</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702701544709844</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.887740162653526</v>
+        <v>-3.735426027336673</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.147249055334687</v>
+        <v>1.208174709461427</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1830519502600298</v>
+        <v>0.3322859599870349</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.812532714865863</v>
+        <v>2.902073120702065</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717329280825888</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.9854807072785</v>
+        <v>-3.833166571961648</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.12278057360074</v>
+        <v>1.183706227727481</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1671626721270497</v>
+        <v>0.3163966818540547</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.817626884102118</v>
+        <v>2.907167289938321</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.715865261650559</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.16181846740143</v>
+        <v>-4.009504332084577</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.05078145037624</v>
+        <v>1.111707104502981</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.009175087995879738</v>
+        <v>0.1400589217311253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.710360208853032</v>
+        <v>2.799900614689235</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714356879690488</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.085396420969503</v>
+        <v>-3.933082285652651</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.079841886988939</v>
+        <v>1.140767541115681</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.009175087995879738</v>
+        <v>0.1400589217311253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.70885182689296</v>
+        <v>2.798392232729163</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714219747125924</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.041023289330934</v>
+        <v>-3.888709154014082</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.097454007079803</v>
+        <v>1.158379661206544</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.03519804364268886</v>
+        <v>0.1844320533696939</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.735338573311538</v>
+        <v>2.824878979147741</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.708613541264515</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.918189068443767</v>
+        <v>-3.765874933126915</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.140981489573261</v>
+        <v>1.201907143700002</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.03519804364268886</v>
+        <v>0.1844320533696939</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.729732367450128</v>
+        <v>2.819272773286331</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.714995298292319</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.870533337882711</v>
+        <v>-3.718219202565859</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.166425538825487</v>
+        <v>1.227351192952228</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.08285377420374451</v>
+        <v>0.2320877839307496</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.764707562814566</v>
+        <v>2.854247968650769</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.719887671667044</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.770015179383956</v>
+        <v>-3.617701044067104</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.211525175599714</v>
+        <v>1.272450829726455</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1833719327024991</v>
+        <v>0.3326059424295041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.829910831288543</v>
+        <v>2.919451237124747</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706642344142916</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.830681769786346</v>
+        <v>-3.678367634469493</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.17401321191463</v>
+        <v>1.234938866041371</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1016736159839654</v>
+        <v>0.2509076257109705</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.767646513733296</v>
+        <v>2.857186919569498</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.710740046753545</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.785843368177948</v>
+        <v>-3.633529232861095</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.196046275168618</v>
+        <v>1.256971929295359</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1062170489288349</v>
+        <v>0.2554510586558399</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.774470276110846</v>
+        <v>2.864010681947049</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.714900986384623</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.886602003934946</v>
+        <v>-3.734287868618094</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.159903760496897</v>
+        <v>1.220829414623638</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.01739148020182946</v>
+        <v>0.1666254899288345</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.725335874505721</v>
+        <v>2.814876280341923</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.72078058891246</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.842399166849046</v>
+        <v>-3.690085031532193</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.183464497859094</v>
+        <v>1.244390151985835</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.0615943172877299</v>
+        <v>0.210828327014735</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.757737179285098</v>
+        <v>2.847277585121301</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719190589381707</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.879378194512489</v>
+        <v>-3.727064059195636</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.167082887262964</v>
+        <v>1.228008541389705</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.09856821907906044</v>
+        <v>0.2478022288060655</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.778331520829144</v>
+        <v>2.867871926665347</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770438354564747</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.899436273377329</v>
+        <v>-3.747122138060476</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210307420900068</v>
+        <v>1.271233075026809</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.09856821907906044</v>
+        <v>0.2478022288060655</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.829579286012184</v>
+        <v>2.919119691848386</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.768879059159</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.859505600199439</v>
+        <v>-3.707191464882586</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.224720394765477</v>
+        <v>1.285646048892218</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1384988922569508</v>
+        <v>0.2877329019839558</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.851978394513171</v>
+        <v>2.941518800349374</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.76382728739727</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.80847350747691</v>
+        <v>-3.656159372160058</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.240081460092759</v>
+        <v>1.301007114219499</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1895309849794787</v>
+        <v>0.3387649947064838</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.877545878384958</v>
+        <v>2.96708628422116</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781014691489975</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.743249326349705</v>
+        <v>-3.590935191032853</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.283358536636346</v>
+        <v>1.344284190763087</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2547551661066844</v>
+        <v>0.4039891758336894</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.933867791153986</v>
+        <v>3.023408196990189</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.776975663789255</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.705822306278571</v>
+        <v>-3.553508170961719</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.29429031696408</v>
+        <v>1.35521597109082</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.260006704135866</v>
+        <v>0.4092407138628711</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.932979686270775</v>
+        <v>3.022520092106978</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778232456120496</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.72593396231328</v>
+        <v>-3.573619826996427</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.287502446881436</v>
+        <v>1.348428101008178</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2710340491332852</v>
+        <v>0.4202680588602903</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.940852885600467</v>
+        <v>3.03039329143667</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938790227141706</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.672189147886075</v>
+        <v>-3.519875012569222</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.469558143673529</v>
+        <v>1.53048379780027</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2810973585737472</v>
+        <v>0.4303313683007522</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.107448642285955</v>
+        <v>3.196989048122158</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.058903136359524</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.648397579279933</v>
+        <v>-3.49608344396308</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.599187680333803</v>
+        <v>1.660113334460544</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.3048889271798895</v>
+        <v>0.4541229369068945</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.241836492667458</v>
+        <v>3.33137689850366</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050611112373383</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.622313495016125</v>
+        <v>-3.469999359699272</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.601329290053185</v>
+        <v>1.662254944179926</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.3048889271798895</v>
+        <v>0.4541229369068945</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.233544468681317</v>
+        <v>3.323084874517519</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.048804307957162</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.544182314167178</v>
+        <v>-3.391868178850325</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.630774957976544</v>
+        <v>1.691700612103285</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.379065738063574</v>
+        <v>0.5282997477905791</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.276243750795307</v>
+        <v>3.36578415663151</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066358713683953</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.535289852773895</v>
+        <v>-3.382975717457042</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.651886348260648</v>
+        <v>1.712812002387389</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.379065738063574</v>
+        <v>0.5282997477905791</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.293798156522098</v>
+        <v>3.383338562358301</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058213761088537</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.703765969743773</v>
+        <v>-3.55145183442692</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.576350948877281</v>
+        <v>1.637276603004022</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3511179023469932</v>
+        <v>0.5003519120739983</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.268884502496733</v>
+        <v>3.358424908332937</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039483458276399</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.005966440882189</v>
+        <v>-2.853652305565337</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.836740457609776</v>
+        <v>1.897666111736517</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2807698429765825</v>
+        <v>0.4300038527035876</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.207945364062349</v>
+        <v>3.297485769898552</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030147480773304</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.983245337199037</v>
+        <v>-2.830931201882184</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.836492921579942</v>
+        <v>1.897418575706683</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2807698429765825</v>
+        <v>0.4300038527035876</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.198609386559253</v>
+        <v>3.288149792395457</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189053606624473</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.981520293908993</v>
+        <v>-2.82920615859214</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.996089064747128</v>
+        <v>2.057014718873869</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2824948862666263</v>
+        <v>0.4317288959936313</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.358550538384449</v>
+        <v>3.448090944220652</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226131429118119</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.136301300687248</v>
+        <v>-2.983987165370396</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.971254484529473</v>
+        <v>2.032180138656214</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2491272122121502</v>
+        <v>0.3983612219391552</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.37560775644541</v>
+        <v>3.465148162281613</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.222806785107664</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.084865967302588</v>
+        <v>-2.932551831985736</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.988503973872882</v>
+        <v>2.049429627999623</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.3005625455968098</v>
+        <v>0.4497965553238149</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.403144312465751</v>
+        <v>3.492684718301954</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.232812938752406</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.0579147429761</v>
+        <v>-2.905600607659248</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.009290617248219</v>
+        <v>2.07021627137496</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.315442891624529</v>
+        <v>0.4646769013515341</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.422078673727124</v>
+        <v>3.511619079563327</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.416916070897366</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.193867751032417</v>
+        <v>-3.041553615715564</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.139012546170652</v>
+        <v>2.199938200297393</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.315442891624529</v>
+        <v>0.4646769013515341</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.606181805872084</v>
+        <v>3.695722211708286</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409032765800359</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.216275868837289</v>
+        <v>-3.063961733520436</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.122165993951696</v>
+        <v>2.183091648078437</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.315442891624529</v>
+        <v>0.4646769013515341</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.598298500775077</v>
+        <v>3.68783890661128</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411086765349996</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.364281636316688</v>
+        <v>-3.211967500999836</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.065017686509574</v>
+        <v>2.125943340636315</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2287158827609875</v>
+        <v>0.3779498924879926</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.548316295006589</v>
+        <v>3.637856700842792</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467340483071844</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.373722562205218</v>
+        <v>-3.221408426888366</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.117495033876009</v>
+        <v>2.17842068800275</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3511430003043789</v>
+        <v>0.500377010031384</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.678026283254471</v>
+        <v>3.767566689090674</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.470231577617144</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.372435798665662</v>
+        <v>-3.220121663348809</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.120900833837132</v>
+        <v>2.181826487963873</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3524297638439355</v>
+        <v>0.5016637735709406</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.681689435923506</v>
+        <v>3.771229841759709</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.46834339051092</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.373992852654953</v>
+        <v>-3.221678717338101</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118389825135191</v>
+        <v>2.179315479261932</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3524297638439355</v>
+        <v>0.5016637735709406</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.679801248817281</v>
+        <v>3.769341654653484</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463163620113782</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.381264738178418</v>
+        <v>-3.228950602861565</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.110301300528667</v>
+        <v>2.171226954655408</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3451578783204708</v>
+        <v>0.4943918880474758</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.670258347106065</v>
+        <v>3.759798752942268</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.461597630323934</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.379423719120167</v>
+        <v>-3.227109583803314</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.10947171836212</v>
+        <v>2.170397372488861</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.4956601147189442</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.669453293319098</v>
+        <v>3.758993699155301</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.386332424619847</v>
+        <v>-3.234018289302995</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.119781643028166</v>
+        <v>2.180707297154908</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.4956601147189442</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.682526700185017</v>
+        <v>3.77206710602122</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474671037189853</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.387894067434707</v>
+        <v>-3.235579932117854</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.119156985902223</v>
+        <v>2.180082640028964</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3464261049919392</v>
+        <v>0.4956601147189442</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.682526700185017</v>
+        <v>3.77206710602122</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.473195078316855</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.41579485454418</v>
+        <v>-3.263480719227327</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.106520712185436</v>
+        <v>2.167446366312177</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3118291808490044</v>
+        <v>0.4610631905760094</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.660292586826258</v>
+        <v>3.749832992662461</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.469959522294054</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.418827852056854</v>
+        <v>-3.266513716740001</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.102071957157565</v>
+        <v>2.162997611284306</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3087961833363305</v>
+        <v>0.4580301930633355</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.655237232295852</v>
+        <v>3.744777638132055</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536665481884557</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.438889173333361</v>
+        <v>-3.286575038016508</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.160753388237466</v>
+        <v>2.221679042364207</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2887348620598235</v>
+        <v>0.4379688717868285</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.709906399120452</v>
+        <v>3.799446804956655</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.676977200886404</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.571994671512999</v>
+        <v>-3.419680536196146</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.247822907967458</v>
+        <v>2.308748562094198</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2351067767257327</v>
+        <v>0.3843407864527377</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.818041266921844</v>
+        <v>3.907581672758047</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.379924989054393</v>
+        <v>3.765033016905488</v>
       </c>
       <c r="C2017" t="n">
         <v>3.680283232578866</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.549013857119077</v>
+        <v>-3.520983956089554</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.260321265417488</v>
+        <v>2.271533225829297</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2351067767257327</v>
+        <v>0.3843407864527377</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.821347298614306</v>
+        <v>3.910887704450508</v>
       </c>
     </row>
   </sheetData>
